--- a/Accounts 2026/Salaries Landco 2026/Landco Salaries 2026/01 Salary sheet for Landco.xlsx
+++ b/Accounts 2026/Salaries Landco 2026/Landco Salaries 2026/01 Salary sheet for Landco.xlsx
@@ -1,16 +1,16 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="29628"/>
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="29929"/>
   <workbookPr defaultThemeVersion="202300"/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\Andrisa\Dropbox\Andrisa\Landco\Accounts 2026\Salaries Landco 2026\Landco Salaries 2026\"/>
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="D:\landco\Accounts 2026\Salaries Landco 2026\Landco Salaries 2026\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{B8A9D6C9-3B12-4768-9532-DBD785EEA41B}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{735A9FD6-8CA0-4D95-8F11-76468EDA3FB6}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-108" yWindow="-108" windowWidth="23256" windowHeight="12456" tabRatio="499" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="0" yWindow="360" windowWidth="20730" windowHeight="11040" tabRatio="499" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="Folha de salarios" sheetId="1" r:id="rId1"/>
@@ -2197,44 +2197,44 @@
     <pageSetUpPr fitToPage="1"/>
   </sheetPr>
   <dimension ref="A4:JC42"/>
-  <sheetFormatPr defaultColWidth="9.109375" defaultRowHeight="22.8" x14ac:dyDescent="0.25"/>
+  <sheetFormatPr defaultColWidth="9.140625" defaultRowHeight="23.25" x14ac:dyDescent="0.2"/>
   <cols>
-    <col min="1" max="2" width="10.6640625" style="5" customWidth="1"/>
+    <col min="1" max="2" width="10.7109375" style="5" customWidth="1"/>
     <col min="3" max="3" width="81" style="6" customWidth="1"/>
-    <col min="4" max="5" width="21.44140625" style="236" hidden="1" customWidth="1"/>
-    <col min="6" max="6" width="34.6640625" style="6" hidden="1" customWidth="1"/>
-    <col min="7" max="7" width="39.21875" style="7" customWidth="1"/>
-    <col min="8" max="8" width="28.33203125" style="8" hidden="1" customWidth="1"/>
-    <col min="9" max="11" width="28.33203125" style="8" customWidth="1"/>
-    <col min="12" max="12" width="14.33203125" style="5" customWidth="1"/>
-    <col min="13" max="13" width="31.6640625" style="9" customWidth="1"/>
-    <col min="14" max="14" width="18.5546875" style="10" customWidth="1"/>
+    <col min="4" max="5" width="21.42578125" style="236" hidden="1" customWidth="1"/>
+    <col min="6" max="6" width="34.7109375" style="6" hidden="1" customWidth="1"/>
+    <col min="7" max="7" width="39.28515625" style="7" customWidth="1"/>
+    <col min="8" max="8" width="28.28515625" style="8" hidden="1" customWidth="1"/>
+    <col min="9" max="11" width="28.28515625" style="8" customWidth="1"/>
+    <col min="12" max="12" width="14.28515625" style="5" customWidth="1"/>
+    <col min="13" max="13" width="31.7109375" style="9" customWidth="1"/>
+    <col min="14" max="14" width="18.5703125" style="10" customWidth="1"/>
     <col min="15" max="15" width="25" style="8" customWidth="1"/>
-    <col min="16" max="16" width="14.33203125" style="11" customWidth="1"/>
+    <col min="16" max="16" width="14.28515625" style="11" customWidth="1"/>
     <col min="17" max="17" width="17" style="8" customWidth="1"/>
-    <col min="18" max="18" width="14.33203125" style="12" customWidth="1"/>
-    <col min="19" max="19" width="25.109375" style="8" customWidth="1"/>
-    <col min="20" max="20" width="16.88671875" style="6" hidden="1" customWidth="1"/>
-    <col min="21" max="21" width="16.44140625" style="6" customWidth="1"/>
-    <col min="22" max="22" width="14.33203125" style="6" customWidth="1"/>
-    <col min="23" max="23" width="24.109375" style="6" customWidth="1"/>
-    <col min="24" max="24" width="30.6640625" style="8" customWidth="1"/>
-    <col min="25" max="25" width="29.88671875" style="8" customWidth="1"/>
-    <col min="26" max="26" width="30.44140625" style="8" customWidth="1"/>
+    <col min="18" max="18" width="14.28515625" style="12" customWidth="1"/>
+    <col min="19" max="19" width="25.140625" style="8" customWidth="1"/>
+    <col min="20" max="20" width="16.85546875" style="6" hidden="1" customWidth="1"/>
+    <col min="21" max="21" width="16.42578125" style="6" customWidth="1"/>
+    <col min="22" max="22" width="14.28515625" style="6" customWidth="1"/>
+    <col min="23" max="23" width="24.140625" style="6" customWidth="1"/>
+    <col min="24" max="24" width="30.7109375" style="8" customWidth="1"/>
+    <col min="25" max="25" width="29.85546875" style="8" customWidth="1"/>
+    <col min="26" max="26" width="30.42578125" style="8" customWidth="1"/>
     <col min="27" max="27" width="12" style="6" customWidth="1"/>
-    <col min="28" max="28" width="27.5546875" style="8" customWidth="1"/>
-    <col min="29" max="29" width="27.44140625" style="8" customWidth="1"/>
-    <col min="30" max="30" width="27.5546875" style="8" customWidth="1"/>
-    <col min="31" max="31" width="31.44140625" style="8" customWidth="1"/>
-    <col min="32" max="32" width="53.88671875" style="6" customWidth="1"/>
-    <col min="33" max="34" width="30.6640625" style="8" customWidth="1"/>
-    <col min="35" max="35" width="40.5546875" style="123" customWidth="1"/>
+    <col min="28" max="28" width="27.5703125" style="8" customWidth="1"/>
+    <col min="29" max="29" width="27.42578125" style="8" customWidth="1"/>
+    <col min="30" max="30" width="27.5703125" style="8" customWidth="1"/>
+    <col min="31" max="31" width="31.42578125" style="8" customWidth="1"/>
+    <col min="32" max="32" width="53.85546875" style="6" customWidth="1"/>
+    <col min="33" max="34" width="30.7109375" style="8" customWidth="1"/>
+    <col min="35" max="35" width="40.5703125" style="123" customWidth="1"/>
     <col min="36" max="36" width="21" style="13" customWidth="1"/>
     <col min="37" max="37" width="23" style="14" customWidth="1"/>
-    <col min="39" max="263" width="9.109375" style="6"/>
+    <col min="39" max="263" width="9.140625" style="6"/>
   </cols>
   <sheetData>
-    <row r="4" spans="1:38" ht="28.2" x14ac:dyDescent="0.25">
+    <row r="4" spans="1:38" ht="27.75" x14ac:dyDescent="0.2">
       <c r="A4" s="244" t="s">
         <v>0</v>
       </c>
@@ -2274,7 +2274,7 @@
       </c>
       <c r="AH4" s="239"/>
     </row>
-    <row r="5" spans="1:38" ht="28.2" x14ac:dyDescent="0.25">
+    <row r="5" spans="1:38" ht="27.75" x14ac:dyDescent="0.2">
       <c r="A5" s="16"/>
       <c r="B5" s="16"/>
       <c r="C5" s="17"/>
@@ -2322,7 +2322,7 @@
       </c>
       <c r="AH5" s="38"/>
     </row>
-    <row r="6" spans="1:38" ht="33" x14ac:dyDescent="0.25">
+    <row r="6" spans="1:38" ht="33.75" x14ac:dyDescent="0.2">
       <c r="A6" s="31"/>
       <c r="B6" s="31"/>
       <c r="C6" s="32"/>
@@ -2372,7 +2372,7 @@
       </c>
       <c r="AH6" s="38"/>
     </row>
-    <row r="7" spans="1:38" ht="28.2" x14ac:dyDescent="0.25">
+    <row r="7" spans="1:38" ht="27.75" x14ac:dyDescent="0.2">
       <c r="A7" s="31"/>
       <c r="B7" s="31"/>
       <c r="C7" s="25"/>
@@ -2408,7 +2408,7 @@
       <c r="AG7" s="38"/>
       <c r="AH7" s="38"/>
     </row>
-    <row r="8" spans="1:38" s="6" customFormat="1" ht="30.75" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="8" spans="1:38" s="6" customFormat="1" ht="30.75" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A8" s="243" t="s">
         <v>11</v>
       </c>
@@ -2463,7 +2463,7 @@
       <c r="AJ8" s="13"/>
       <c r="AK8" s="14"/>
     </row>
-    <row r="9" spans="1:38" s="6" customFormat="1" ht="279.89999999999998" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="9" spans="1:38" s="6" customFormat="1" ht="279.95" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A9" s="243"/>
       <c r="B9" s="148"/>
       <c r="C9" s="243"/>
@@ -2546,7 +2546,7 @@
       <c r="AF9" s="158" t="s">
         <v>35</v>
       </c>
-      <c r="AG9" s="149" t="s">
+      <c r="AG9" s="158" t="s">
         <v>36</v>
       </c>
       <c r="AH9" s="240"/>
@@ -2554,7 +2554,7 @@
       <c r="AJ9" s="41"/>
       <c r="AK9" s="14"/>
     </row>
-    <row r="10" spans="1:38" s="50" customFormat="1" ht="55.5" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="10" spans="1:38" s="50" customFormat="1" ht="55.5" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A10" s="159">
         <v>1</v>
       </c>
@@ -2656,7 +2656,7 @@
       <c r="AK10" s="48"/>
       <c r="AL10" s="49"/>
     </row>
-    <row r="11" spans="1:38" s="54" customFormat="1" ht="55.5" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="11" spans="1:38" s="54" customFormat="1" ht="55.5" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A11" s="159">
         <f>+A10+1</f>
         <v>2</v>
@@ -2757,7 +2757,7 @@
       <c r="AK11" s="52"/>
       <c r="AL11" s="53"/>
     </row>
-    <row r="12" spans="1:38" s="50" customFormat="1" ht="55.5" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="12" spans="1:38" s="50" customFormat="1" ht="55.5" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A12" s="159">
         <f t="shared" ref="A12:A30" si="8">+A11+1</f>
         <v>3</v>
@@ -2858,7 +2858,7 @@
       <c r="AK12" s="48"/>
       <c r="AL12" s="49"/>
     </row>
-    <row r="13" spans="1:38" s="50" customFormat="1" ht="55.5" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="13" spans="1:38" s="50" customFormat="1" ht="55.5" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A13" s="159">
         <f t="shared" si="8"/>
         <v>4</v>
@@ -2958,7 +2958,7 @@
       <c r="AK13" s="48"/>
       <c r="AL13" s="49"/>
     </row>
-    <row r="14" spans="1:38" s="50" customFormat="1" ht="55.5" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="14" spans="1:38" s="50" customFormat="1" ht="55.5" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A14" s="159">
         <f t="shared" si="8"/>
         <v>5</v>
@@ -3054,7 +3054,7 @@
       <c r="AK14" s="48"/>
       <c r="AL14" s="49"/>
     </row>
-    <row r="15" spans="1:38" s="50" customFormat="1" ht="55.5" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="15" spans="1:38" s="50" customFormat="1" ht="55.5" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A15" s="159">
         <f t="shared" si="8"/>
         <v>6</v>
@@ -3150,7 +3150,7 @@
       <c r="AK15" s="48"/>
       <c r="AL15" s="49"/>
     </row>
-    <row r="16" spans="1:38" s="50" customFormat="1" ht="55.5" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="16" spans="1:38" s="50" customFormat="1" ht="55.5" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A16" s="159">
         <f t="shared" si="8"/>
         <v>7</v>
@@ -3248,7 +3248,7 @@
       <c r="AK16" s="48"/>
       <c r="AL16" s="49"/>
     </row>
-    <row r="17" spans="1:179" s="50" customFormat="1" ht="55.5" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="17" spans="1:179" s="50" customFormat="1" ht="55.5" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A17" s="159">
         <f t="shared" si="8"/>
         <v>8</v>
@@ -3347,7 +3347,7 @@
       <c r="AK17" s="48"/>
       <c r="AL17" s="49"/>
     </row>
-    <row r="18" spans="1:179" s="45" customFormat="1" ht="55.5" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="18" spans="1:179" s="45" customFormat="1" ht="55.5" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A18" s="159">
         <f t="shared" si="8"/>
         <v>9</v>
@@ -3590,7 +3590,7 @@
       <c r="FV18" s="50"/>
       <c r="FW18" s="50"/>
     </row>
-    <row r="19" spans="1:179" s="45" customFormat="1" ht="55.5" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="19" spans="1:179" s="45" customFormat="1" ht="55.5" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A19" s="159">
         <f t="shared" si="8"/>
         <v>10</v>
@@ -3824,7 +3824,7 @@
       <c r="FV19" s="50"/>
       <c r="FW19" s="50"/>
     </row>
-    <row r="20" spans="1:179" s="50" customFormat="1" ht="73.5" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="20" spans="1:179" s="50" customFormat="1" ht="73.5" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A20" s="159">
         <f t="shared" si="8"/>
         <v>11</v>
@@ -3917,7 +3917,7 @@
       <c r="AK20" s="48"/>
       <c r="AL20" s="49"/>
     </row>
-    <row r="21" spans="1:179" s="50" customFormat="1" ht="60.75" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="21" spans="1:179" s="50" customFormat="1" ht="60.75" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A21" s="159">
         <f t="shared" si="8"/>
         <v>12</v>
@@ -4016,7 +4016,7 @@
       <c r="AK21" s="48"/>
       <c r="AL21" s="49"/>
     </row>
-    <row r="22" spans="1:179" s="50" customFormat="1" ht="53.25" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="22" spans="1:179" s="50" customFormat="1" ht="53.25" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A22" s="159">
         <f t="shared" si="8"/>
         <v>13</v>
@@ -4109,7 +4109,7 @@
       <c r="AK22" s="48"/>
       <c r="AL22" s="49"/>
     </row>
-    <row r="23" spans="1:179" s="50" customFormat="1" ht="53.25" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="23" spans="1:179" s="50" customFormat="1" ht="53.25" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A23" s="159">
         <f t="shared" si="8"/>
         <v>14</v>
@@ -4202,7 +4202,7 @@
       <c r="AK23" s="48"/>
       <c r="AL23" s="49"/>
     </row>
-    <row r="24" spans="1:179" s="50" customFormat="1" ht="55.5" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="24" spans="1:179" s="50" customFormat="1" ht="55.5" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A24" s="159">
         <f t="shared" si="8"/>
         <v>15</v>
@@ -4299,7 +4299,7 @@
       <c r="AJ24" s="48"/>
       <c r="AK24" s="49"/>
     </row>
-    <row r="25" spans="1:179" s="50" customFormat="1" ht="55.5" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="25" spans="1:179" s="50" customFormat="1" ht="55.5" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A25" s="159">
         <f t="shared" si="8"/>
         <v>16</v>
@@ -4398,7 +4398,7 @@
       <c r="AK25" s="48"/>
       <c r="AL25" s="49"/>
     </row>
-    <row r="26" spans="1:179" s="50" customFormat="1" ht="55.5" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="26" spans="1:179" s="50" customFormat="1" ht="55.5" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A26" s="159">
         <f t="shared" si="8"/>
         <v>17</v>
@@ -4491,7 +4491,7 @@
       <c r="AK26" s="48"/>
       <c r="AL26" s="49"/>
     </row>
-    <row r="27" spans="1:179" s="50" customFormat="1" ht="55.5" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="27" spans="1:179" s="50" customFormat="1" ht="55.5" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A27" s="159">
         <f t="shared" si="8"/>
         <v>18</v>
@@ -4584,7 +4584,7 @@
       <c r="AK27" s="48"/>
       <c r="AL27" s="49"/>
     </row>
-    <row r="28" spans="1:179" s="50" customFormat="1" ht="55.5" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="28" spans="1:179" s="50" customFormat="1" ht="55.5" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A28" s="159">
         <f t="shared" si="8"/>
         <v>19</v>
@@ -4685,7 +4685,7 @@
       <c r="AK28" s="48"/>
       <c r="AL28" s="49"/>
     </row>
-    <row r="29" spans="1:179" s="50" customFormat="1" ht="55.5" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="29" spans="1:179" s="50" customFormat="1" ht="55.5" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A29" s="159">
         <f t="shared" si="8"/>
         <v>20</v>
@@ -4778,7 +4778,7 @@
       <c r="AK29" s="48"/>
       <c r="AL29" s="49"/>
     </row>
-    <row r="30" spans="1:179" s="50" customFormat="1" ht="66" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="30" spans="1:179" s="50" customFormat="1" ht="66" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A30" s="159">
         <f t="shared" si="8"/>
         <v>21</v>
@@ -4873,7 +4873,7 @@
       <c r="AK30" s="48"/>
       <c r="AL30" s="49"/>
     </row>
-    <row r="31" spans="1:179" s="70" customFormat="1" ht="55.5" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="31" spans="1:179" s="70" customFormat="1" ht="55.5" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A31" s="195"/>
       <c r="B31" s="195"/>
       <c r="C31" s="196"/>
@@ -4972,7 +4972,7 @@
       <c r="AJ31" s="48"/>
       <c r="AK31" s="69"/>
     </row>
-    <row r="32" spans="1:179" s="70" customFormat="1" ht="55.5" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="32" spans="1:179" s="70" customFormat="1" ht="55.5" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A32" s="200"/>
       <c r="B32" s="200"/>
       <c r="C32" s="201"/>
@@ -5021,7 +5021,7 @@
       <c r="AJ32" s="48"/>
       <c r="AK32" s="69"/>
     </row>
-    <row r="33" spans="1:38" s="70" customFormat="1" ht="55.5" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="33" spans="1:38" s="70" customFormat="1" ht="55.5" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A33" s="200"/>
       <c r="B33" s="200"/>
       <c r="C33" s="206"/>
@@ -5060,7 +5060,7 @@
       <c r="AJ33" s="48"/>
       <c r="AK33" s="69"/>
     </row>
-    <row r="34" spans="1:38" s="70" customFormat="1" ht="55.5" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="34" spans="1:38" s="70" customFormat="1" ht="55.5" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A34" s="200"/>
       <c r="B34" s="200"/>
       <c r="C34" s="201"/>
@@ -5108,7 +5108,7 @@
       <c r="AJ34" s="48"/>
       <c r="AK34" s="69"/>
     </row>
-    <row r="35" spans="1:38" s="87" customFormat="1" ht="28.5" customHeight="1" x14ac:dyDescent="0.5">
+    <row r="35" spans="1:38" s="87" customFormat="1" ht="28.5" customHeight="1" x14ac:dyDescent="0.4">
       <c r="A35" s="209"/>
       <c r="B35" s="210"/>
       <c r="C35" s="211"/>
@@ -5148,7 +5148,7 @@
       <c r="AK35" s="85"/>
       <c r="AL35" s="86"/>
     </row>
-    <row r="36" spans="1:38" s="87" customFormat="1" ht="28.5" customHeight="1" x14ac:dyDescent="0.5">
+    <row r="36" spans="1:38" s="87" customFormat="1" ht="28.5" customHeight="1" x14ac:dyDescent="0.4">
       <c r="A36" s="76"/>
       <c r="B36" s="77"/>
       <c r="C36" s="88"/>
@@ -5190,7 +5190,7 @@
       <c r="AK36" s="85"/>
       <c r="AL36" s="86"/>
     </row>
-    <row r="37" spans="1:38" s="87" customFormat="1" ht="28.5" customHeight="1" x14ac:dyDescent="0.5">
+    <row r="37" spans="1:38" s="87" customFormat="1" ht="28.5" customHeight="1" x14ac:dyDescent="0.4">
       <c r="A37" s="76" t="s">
         <v>72</v>
       </c>
@@ -5236,7 +5236,7 @@
       <c r="AK37" s="85"/>
       <c r="AL37" s="86"/>
     </row>
-    <row r="38" spans="1:38" s="87" customFormat="1" ht="28.5" customHeight="1" x14ac:dyDescent="0.5">
+    <row r="38" spans="1:38" s="87" customFormat="1" ht="28.5" customHeight="1" x14ac:dyDescent="0.4">
       <c r="A38" s="76" t="s">
         <v>75</v>
       </c>
@@ -5282,7 +5282,7 @@
       <c r="AK38" s="85"/>
       <c r="AL38" s="86"/>
     </row>
-    <row r="39" spans="1:38" s="87" customFormat="1" ht="28.5" customHeight="1" x14ac:dyDescent="0.5">
+    <row r="39" spans="1:38" s="87" customFormat="1" ht="28.5" customHeight="1" x14ac:dyDescent="0.4">
       <c r="A39" s="76" t="s">
         <v>79</v>
       </c>
@@ -5328,7 +5328,7 @@
       <c r="AK39" s="85"/>
       <c r="AL39" s="86"/>
     </row>
-    <row r="40" spans="1:38" s="87" customFormat="1" ht="28.5" customHeight="1" x14ac:dyDescent="0.5">
+    <row r="40" spans="1:38" s="87" customFormat="1" ht="28.5" customHeight="1" x14ac:dyDescent="0.4">
       <c r="A40" s="76" t="s">
         <v>82</v>
       </c>
@@ -5372,7 +5372,7 @@
       <c r="AK40" s="85"/>
       <c r="AL40" s="86"/>
     </row>
-    <row r="41" spans="1:38" s="87" customFormat="1" ht="28.5" customHeight="1" x14ac:dyDescent="0.5">
+    <row r="41" spans="1:38" s="87" customFormat="1" ht="28.5" customHeight="1" x14ac:dyDescent="0.4">
       <c r="A41" s="76"/>
       <c r="B41" s="77"/>
       <c r="C41" s="88"/>
@@ -5414,7 +5414,7 @@
       <c r="AK41" s="85"/>
       <c r="AL41" s="86"/>
     </row>
-    <row r="42" spans="1:38" s="87" customFormat="1" ht="28.5" customHeight="1" thickBot="1" x14ac:dyDescent="0.55000000000000004">
+    <row r="42" spans="1:38" s="87" customFormat="1" ht="28.5" customHeight="1" thickBot="1" x14ac:dyDescent="0.45">
       <c r="A42" s="111"/>
       <c r="B42" s="112"/>
       <c r="C42" s="113"/>
@@ -5472,7 +5472,7 @@
   </mergeCells>
   <printOptions horizontalCentered="1"/>
   <pageMargins left="0.23611111111111099" right="0" top="0.31527777777777799" bottom="0.31527777777777799" header="0.511811023622047" footer="0.511811023622047"/>
-  <pageSetup paperSize="9" scale="20" orientation="landscape" horizontalDpi="300" verticalDpi="300" r:id="rId1"/>
+  <pageSetup paperSize="9" scale="19" orientation="landscape" horizontalDpi="300" verticalDpi="300" r:id="rId1"/>
   <legacyDrawing r:id="rId2"/>
 </worksheet>
 </file>
@@ -5484,24 +5484,24 @@
     <pageSetUpPr fitToPage="1"/>
   </sheetPr>
   <dimension ref="A1:IW46"/>
-  <sheetFormatPr defaultColWidth="9.109375" defaultRowHeight="22.8" x14ac:dyDescent="0.25"/>
+  <sheetFormatPr defaultColWidth="9.140625" defaultRowHeight="23.25" x14ac:dyDescent="0.2"/>
   <cols>
-    <col min="1" max="2" width="10.6640625" style="5" customWidth="1"/>
+    <col min="1" max="2" width="10.7109375" style="5" customWidth="1"/>
     <col min="3" max="3" width="86" style="6" customWidth="1"/>
-    <col min="4" max="4" width="25.109375" style="8" customWidth="1"/>
+    <col min="4" max="4" width="25.140625" style="8" customWidth="1"/>
     <col min="5" max="5" width="21" style="8" customWidth="1"/>
-    <col min="6" max="6" width="21.109375" style="6" hidden="1" customWidth="1"/>
-    <col min="7" max="7" width="27.5546875" style="8" hidden="1" customWidth="1"/>
-    <col min="8" max="8" width="25.6640625" style="6" hidden="1" customWidth="1"/>
-    <col min="9" max="9" width="41.109375" style="6" hidden="1" customWidth="1"/>
-    <col min="10" max="10" width="30.6640625" style="8" hidden="1" customWidth="1"/>
-    <col min="11" max="11" width="40.5546875" style="13" customWidth="1"/>
+    <col min="6" max="6" width="21.140625" style="6" hidden="1" customWidth="1"/>
+    <col min="7" max="7" width="27.5703125" style="8" hidden="1" customWidth="1"/>
+    <col min="8" max="8" width="25.7109375" style="6" hidden="1" customWidth="1"/>
+    <col min="9" max="9" width="41.140625" style="6" hidden="1" customWidth="1"/>
+    <col min="10" max="10" width="30.7109375" style="8" hidden="1" customWidth="1"/>
+    <col min="11" max="11" width="40.5703125" style="13" customWidth="1"/>
     <col min="12" max="12" width="21" style="13" customWidth="1"/>
     <col min="13" max="13" width="23" style="14" customWidth="1"/>
-    <col min="15" max="257" width="9.109375" style="6"/>
+    <col min="15" max="257" width="9.140625" style="6"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:155" ht="28.2" x14ac:dyDescent="0.25">
+    <row r="1" spans="1:155" ht="27.75" x14ac:dyDescent="0.2">
       <c r="A1" s="244" t="s">
         <v>0</v>
       </c>
@@ -5517,7 +5517,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="2" spans="1:155" ht="28.2" x14ac:dyDescent="0.25">
+    <row r="2" spans="1:155" ht="27.75" x14ac:dyDescent="0.2">
       <c r="A2" s="16"/>
       <c r="B2" s="16"/>
       <c r="C2" s="17" t="s">
@@ -5534,7 +5534,7 @@
         <v>2024</v>
       </c>
     </row>
-    <row r="3" spans="1:155" ht="33" x14ac:dyDescent="0.25">
+    <row r="3" spans="1:155" ht="33.75" x14ac:dyDescent="0.2">
       <c r="A3" s="31"/>
       <c r="B3" s="31"/>
       <c r="C3" s="32"/>
@@ -5549,7 +5549,7 @@
         <v>88</v>
       </c>
     </row>
-    <row r="4" spans="1:155" ht="28.2" x14ac:dyDescent="0.25">
+    <row r="4" spans="1:155" ht="27.75" x14ac:dyDescent="0.2">
       <c r="A4" s="31"/>
       <c r="B4" s="31"/>
       <c r="C4" s="25"/>
@@ -5561,7 +5561,7 @@
       <c r="I4" s="17"/>
       <c r="J4" s="38"/>
     </row>
-    <row r="5" spans="1:155" s="6" customFormat="1" ht="30.75" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="5" spans="1:155" s="6" customFormat="1" ht="30.75" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A5" s="245" t="s">
         <v>11</v>
       </c>
@@ -5582,7 +5582,7 @@
       <c r="L5" s="13"/>
       <c r="M5" s="14"/>
     </row>
-    <row r="6" spans="1:155" s="6" customFormat="1" ht="279.89999999999998" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="6" spans="1:155" s="6" customFormat="1" ht="279.95" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A6" s="245"/>
       <c r="B6" s="3"/>
       <c r="C6" s="245"/>
@@ -5607,7 +5607,7 @@
       <c r="L6" s="41"/>
       <c r="M6" s="14"/>
     </row>
-    <row r="7" spans="1:155" s="50" customFormat="1" ht="55.5" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="7" spans="1:155" s="50" customFormat="1" ht="55.5" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A7" s="42">
         <v>1</v>
       </c>
@@ -5649,7 +5649,7 @@
       <c r="M7" s="48"/>
       <c r="N7" s="49"/>
     </row>
-    <row r="8" spans="1:155" s="50" customFormat="1" ht="55.5" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="8" spans="1:155" s="50" customFormat="1" ht="55.5" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A8" s="42">
         <f>+A7+1</f>
         <v>2</v>
@@ -5689,7 +5689,7 @@
       <c r="M8" s="48"/>
       <c r="N8" s="49"/>
     </row>
-    <row r="9" spans="1:155" s="50" customFormat="1" ht="55.5" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="9" spans="1:155" s="50" customFormat="1" ht="55.5" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A9" s="42">
         <f t="shared" ref="A9:A27" si="3">+A8+1</f>
         <v>3</v>
@@ -5729,7 +5729,7 @@
       <c r="M9" s="48"/>
       <c r="N9" s="49"/>
     </row>
-    <row r="10" spans="1:155" s="50" customFormat="1" ht="55.5" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="10" spans="1:155" s="50" customFormat="1" ht="55.5" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A10" s="42">
         <f t="shared" si="3"/>
         <v>4</v>
@@ -5769,7 +5769,7 @@
       <c r="M10" s="48"/>
       <c r="N10" s="49"/>
     </row>
-    <row r="11" spans="1:155" s="50" customFormat="1" ht="55.5" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="11" spans="1:155" s="50" customFormat="1" ht="55.5" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A11" s="42">
         <f t="shared" si="3"/>
         <v>5</v>
@@ -5809,7 +5809,7 @@
       <c r="M11" s="48"/>
       <c r="N11" s="49"/>
     </row>
-    <row r="12" spans="1:155" s="50" customFormat="1" ht="55.5" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="12" spans="1:155" s="50" customFormat="1" ht="55.5" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A12" s="42">
         <f t="shared" si="3"/>
         <v>6</v>
@@ -5849,7 +5849,7 @@
       <c r="M12" s="48"/>
       <c r="N12" s="49"/>
     </row>
-    <row r="13" spans="1:155" s="45" customFormat="1" ht="55.5" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="13" spans="1:155" s="45" customFormat="1" ht="55.5" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A13" s="42">
         <f t="shared" si="3"/>
         <v>7</v>
@@ -6030,7 +6030,7 @@
       <c r="EX13" s="50"/>
       <c r="EY13" s="50"/>
     </row>
-    <row r="14" spans="1:155" s="45" customFormat="1" ht="55.5" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="14" spans="1:155" s="45" customFormat="1" ht="55.5" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A14" s="42">
         <f t="shared" si="3"/>
         <v>8</v>
@@ -6198,7 +6198,7 @@
       <c r="EX14" s="50"/>
       <c r="EY14" s="50"/>
     </row>
-    <row r="15" spans="1:155" s="45" customFormat="1" ht="55.5" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="15" spans="1:155" s="45" customFormat="1" ht="55.5" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A15" s="42">
         <f t="shared" si="3"/>
         <v>9</v>
@@ -6382,7 +6382,7 @@
       <c r="EX15" s="50"/>
       <c r="EY15" s="50"/>
     </row>
-    <row r="16" spans="1:155" s="50" customFormat="1" ht="73.5" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="16" spans="1:155" s="50" customFormat="1" ht="73.5" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A16" s="42">
         <f t="shared" si="3"/>
         <v>10</v>
@@ -6422,7 +6422,7 @@
       <c r="M16" s="48"/>
       <c r="N16" s="49"/>
     </row>
-    <row r="17" spans="1:14" s="50" customFormat="1" ht="60.75" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="17" spans="1:14" s="50" customFormat="1" ht="60.75" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A17" s="42">
         <f t="shared" si="3"/>
         <v>11</v>
@@ -6462,7 +6462,7 @@
       <c r="M17" s="48"/>
       <c r="N17" s="49"/>
     </row>
-    <row r="18" spans="1:14" s="50" customFormat="1" ht="53.25" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="18" spans="1:14" s="50" customFormat="1" ht="53.25" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A18" s="42">
         <f t="shared" si="3"/>
         <v>12</v>
@@ -6505,7 +6505,7 @@
       <c r="M18" s="48"/>
       <c r="N18" s="49"/>
     </row>
-    <row r="19" spans="1:14" s="50" customFormat="1" ht="53.25" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="19" spans="1:14" s="50" customFormat="1" ht="53.25" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A19" s="42">
         <f t="shared" si="3"/>
         <v>13</v>
@@ -6545,7 +6545,7 @@
       <c r="M19" s="48"/>
       <c r="N19" s="49"/>
     </row>
-    <row r="20" spans="1:14" s="50" customFormat="1" ht="55.5" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="20" spans="1:14" s="50" customFormat="1" ht="55.5" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A20" s="42">
         <f t="shared" si="3"/>
         <v>14</v>
@@ -6584,7 +6584,7 @@
       <c r="L20" s="48"/>
       <c r="M20" s="49"/>
     </row>
-    <row r="21" spans="1:14" s="50" customFormat="1" ht="55.5" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="21" spans="1:14" s="50" customFormat="1" ht="55.5" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A21" s="42">
         <f t="shared" si="3"/>
         <v>15</v>
@@ -6624,7 +6624,7 @@
       <c r="M21" s="48"/>
       <c r="N21" s="49"/>
     </row>
-    <row r="22" spans="1:14" s="50" customFormat="1" ht="55.5" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="22" spans="1:14" s="50" customFormat="1" ht="55.5" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A22" s="42">
         <f t="shared" si="3"/>
         <v>16</v>
@@ -6667,7 +6667,7 @@
       <c r="M22" s="48"/>
       <c r="N22" s="49"/>
     </row>
-    <row r="23" spans="1:14" s="50" customFormat="1" ht="55.5" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="23" spans="1:14" s="50" customFormat="1" ht="55.5" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A23" s="42">
         <f t="shared" si="3"/>
         <v>17</v>
@@ -6707,7 +6707,7 @@
       <c r="M23" s="48"/>
       <c r="N23" s="49"/>
     </row>
-    <row r="24" spans="1:14" s="50" customFormat="1" ht="55.5" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="24" spans="1:14" s="50" customFormat="1" ht="55.5" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A24" s="42">
         <f t="shared" si="3"/>
         <v>18</v>
@@ -6747,7 +6747,7 @@
       <c r="M24" s="48"/>
       <c r="N24" s="49"/>
     </row>
-    <row r="25" spans="1:14" s="50" customFormat="1" ht="55.5" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="25" spans="1:14" s="50" customFormat="1" ht="55.5" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A25" s="42">
         <f t="shared" si="3"/>
         <v>19</v>
@@ -6790,7 +6790,7 @@
       <c r="M25" s="48"/>
       <c r="N25" s="49"/>
     </row>
-    <row r="26" spans="1:14" s="50" customFormat="1" ht="55.5" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="26" spans="1:14" s="50" customFormat="1" ht="55.5" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A26" s="42">
         <f t="shared" si="3"/>
         <v>20</v>
@@ -6830,7 +6830,7 @@
       <c r="M26" s="48"/>
       <c r="N26" s="49"/>
     </row>
-    <row r="27" spans="1:14" s="50" customFormat="1" ht="55.5" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="27" spans="1:14" s="50" customFormat="1" ht="55.5" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A27" s="42">
         <f t="shared" si="3"/>
         <v>21</v>
@@ -6870,7 +6870,7 @@
       <c r="M27" s="48"/>
       <c r="N27" s="49"/>
     </row>
-    <row r="28" spans="1:14" s="50" customFormat="1" ht="55.5" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="28" spans="1:14" s="50" customFormat="1" ht="55.5" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A28" s="141"/>
       <c r="B28" s="141"/>
       <c r="C28" s="142"/>
@@ -6886,7 +6886,7 @@
       <c r="M28" s="48"/>
       <c r="N28" s="49"/>
     </row>
-    <row r="29" spans="1:14" s="70" customFormat="1" ht="55.5" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="29" spans="1:14" s="70" customFormat="1" ht="55.5" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A29" s="65"/>
       <c r="B29" s="65"/>
       <c r="C29" s="1" t="s">
@@ -6921,7 +6921,7 @@
       <c r="L29" s="48"/>
       <c r="M29" s="69"/>
     </row>
-    <row r="30" spans="1:14" s="70" customFormat="1" ht="55.5" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="30" spans="1:14" s="70" customFormat="1" ht="55.5" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A30" s="71"/>
       <c r="B30" s="71"/>
       <c r="C30" s="72"/>
@@ -6936,7 +6936,7 @@
       <c r="L30" s="48"/>
       <c r="M30" s="69"/>
     </row>
-    <row r="31" spans="1:14" s="70" customFormat="1" ht="55.5" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="31" spans="1:14" s="70" customFormat="1" ht="55.5" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A31" s="71"/>
       <c r="B31" s="71"/>
       <c r="C31" s="72"/>
@@ -6951,7 +6951,7 @@
       <c r="L31" s="48"/>
       <c r="M31" s="69"/>
     </row>
-    <row r="32" spans="1:14" s="87" customFormat="1" ht="28.5" customHeight="1" x14ac:dyDescent="0.5">
+    <row r="32" spans="1:14" s="87" customFormat="1" ht="28.5" customHeight="1" x14ac:dyDescent="0.4">
       <c r="A32" s="76"/>
       <c r="B32" s="77"/>
       <c r="C32" s="78"/>
@@ -6967,7 +6967,7 @@
       <c r="M32" s="85"/>
       <c r="N32" s="86"/>
     </row>
-    <row r="33" spans="1:14" s="87" customFormat="1" ht="28.5" customHeight="1" x14ac:dyDescent="0.5">
+    <row r="33" spans="1:14" s="87" customFormat="1" ht="28.5" customHeight="1" x14ac:dyDescent="0.4">
       <c r="A33" s="76"/>
       <c r="B33" s="77"/>
       <c r="C33" s="88"/>
@@ -6985,7 +6985,7 @@
       <c r="M33" s="85"/>
       <c r="N33" s="86"/>
     </row>
-    <row r="34" spans="1:14" s="87" customFormat="1" ht="28.5" customHeight="1" x14ac:dyDescent="0.5">
+    <row r="34" spans="1:14" s="87" customFormat="1" ht="28.5" customHeight="1" x14ac:dyDescent="0.4">
       <c r="A34" s="76" t="s">
         <v>72</v>
       </c>
@@ -7005,7 +7005,7 @@
       <c r="M34" s="85"/>
       <c r="N34" s="86"/>
     </row>
-    <row r="35" spans="1:14" s="87" customFormat="1" ht="28.5" customHeight="1" x14ac:dyDescent="0.5">
+    <row r="35" spans="1:14" s="87" customFormat="1" ht="28.5" customHeight="1" x14ac:dyDescent="0.4">
       <c r="A35" s="76" t="s">
         <v>75</v>
       </c>
@@ -7027,7 +7027,7 @@
       <c r="M35" s="85"/>
       <c r="N35" s="86"/>
     </row>
-    <row r="36" spans="1:14" s="87" customFormat="1" ht="28.5" customHeight="1" x14ac:dyDescent="0.5">
+    <row r="36" spans="1:14" s="87" customFormat="1" ht="28.5" customHeight="1" x14ac:dyDescent="0.4">
       <c r="A36" s="76" t="s">
         <v>79</v>
       </c>
@@ -7047,7 +7047,7 @@
       <c r="M36" s="85"/>
       <c r="N36" s="86"/>
     </row>
-    <row r="37" spans="1:14" s="87" customFormat="1" ht="28.5" customHeight="1" x14ac:dyDescent="0.5">
+    <row r="37" spans="1:14" s="87" customFormat="1" ht="28.5" customHeight="1" x14ac:dyDescent="0.4">
       <c r="A37" s="76" t="s">
         <v>82</v>
       </c>
@@ -7069,7 +7069,7 @@
       <c r="M37" s="85"/>
       <c r="N37" s="86"/>
     </row>
-    <row r="38" spans="1:14" s="87" customFormat="1" ht="28.5" customHeight="1" x14ac:dyDescent="0.5">
+    <row r="38" spans="1:14" s="87" customFormat="1" ht="28.5" customHeight="1" x14ac:dyDescent="0.4">
       <c r="A38" s="76"/>
       <c r="B38" s="77"/>
       <c r="C38" s="88"/>
@@ -7085,7 +7085,7 @@
       <c r="M38" s="85"/>
       <c r="N38" s="86"/>
     </row>
-    <row r="39" spans="1:14" s="87" customFormat="1" ht="28.5" customHeight="1" x14ac:dyDescent="0.5">
+    <row r="39" spans="1:14" s="87" customFormat="1" ht="28.5" customHeight="1" x14ac:dyDescent="0.4">
       <c r="A39" s="111"/>
       <c r="B39" s="112"/>
       <c r="C39" s="113"/>
@@ -7101,7 +7101,7 @@
       <c r="M39" s="85"/>
       <c r="N39" s="86"/>
     </row>
-    <row r="40" spans="1:14" ht="28.5" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="40" spans="1:14" ht="28.5" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A40" s="121"/>
       <c r="B40" s="121"/>
       <c r="C40" s="122"/>
@@ -7113,21 +7113,21 @@
       <c r="I40" s="122"/>
       <c r="J40" s="123"/>
     </row>
-    <row r="41" spans="1:14" ht="28.5" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="42" spans="1:14" ht="28.5" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="41" spans="1:14" ht="28.5" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="42" spans="1:14" ht="28.5" customHeight="1" x14ac:dyDescent="0.2">
       <c r="H42" s="8" t="e">
         <f>#REF!</f>
         <v>#REF!</v>
       </c>
       <c r="I42" s="8"/>
     </row>
-    <row r="43" spans="1:14" ht="28.5" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="45" spans="1:14" x14ac:dyDescent="0.25">
+    <row r="43" spans="1:14" ht="28.5" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="45" spans="1:14" x14ac:dyDescent="0.2">
       <c r="D45" s="124" t="s">
         <v>86</v>
       </c>
     </row>
-    <row r="46" spans="1:14" x14ac:dyDescent="0.25">
+    <row r="46" spans="1:14" x14ac:dyDescent="0.2">
       <c r="D46" s="124">
         <f>+D29*7%</f>
         <v>24253.11</v>
@@ -7145,29 +7145,29 @@
   <phoneticPr fontId="31" type="noConversion"/>
   <printOptions horizontalCentered="1"/>
   <pageMargins left="0.23611111111111099" right="0" top="0.31527777777777799" bottom="0.31527777777777799" header="0.511811023622047" footer="0.511811023622047"/>
-  <pageSetup paperSize="9" scale="37" orientation="portrait" horizontalDpi="300" verticalDpi="300" r:id="rId1"/>
+  <pageSetup paperSize="9" scale="35" orientation="portrait" horizontalDpi="300" verticalDpi="300" r:id="rId1"/>
 </worksheet>
 </file>
 
 <file path=xl/worksheets/sheet3.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0300-000000000000}">
   <dimension ref="A1:O722"/>
-  <sheetFormatPr defaultColWidth="9" defaultRowHeight="13.2" x14ac:dyDescent="0.25"/>
+  <sheetFormatPr defaultColWidth="9" defaultRowHeight="12.75" x14ac:dyDescent="0.2"/>
   <cols>
-    <col min="1" max="1" width="0.88671875" customWidth="1"/>
-    <col min="2" max="2" width="10.6640625" customWidth="1"/>
-    <col min="3" max="5" width="9.6640625" customWidth="1"/>
-    <col min="6" max="6" width="8.6640625" customWidth="1"/>
-    <col min="7" max="7" width="10.6640625" customWidth="1"/>
-    <col min="8" max="8" width="5.88671875" customWidth="1"/>
-    <col min="9" max="9" width="18.33203125" customWidth="1"/>
-    <col min="10" max="10" width="10.6640625" customWidth="1"/>
-    <col min="11" max="13" width="9.6640625" customWidth="1"/>
-    <col min="14" max="14" width="8.6640625" customWidth="1"/>
-    <col min="15" max="15" width="10.6640625" customWidth="1"/>
+    <col min="1" max="1" width="0.85546875" customWidth="1"/>
+    <col min="2" max="2" width="10.7109375" customWidth="1"/>
+    <col min="3" max="5" width="9.7109375" customWidth="1"/>
+    <col min="6" max="6" width="8.7109375" customWidth="1"/>
+    <col min="7" max="7" width="10.7109375" customWidth="1"/>
+    <col min="8" max="8" width="5.85546875" customWidth="1"/>
+    <col min="9" max="9" width="18.28515625" customWidth="1"/>
+    <col min="10" max="10" width="10.7109375" customWidth="1"/>
+    <col min="11" max="13" width="9.7109375" customWidth="1"/>
+    <col min="14" max="14" width="8.7109375" customWidth="1"/>
+    <col min="15" max="15" width="10.7109375" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:15" ht="38.1" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="1" spans="1:15" ht="38.1" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A1" s="125"/>
       <c r="B1" s="247" t="s">
         <v>91</v>
@@ -7188,7 +7188,7 @@
       <c r="N1" s="247"/>
       <c r="O1" s="247"/>
     </row>
-    <row r="2" spans="1:15" ht="15" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="2" spans="1:15" ht="15" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A2" s="125"/>
       <c r="B2" s="126"/>
       <c r="C2" s="128"/>
@@ -7205,7 +7205,7 @@
       <c r="N2" s="128"/>
       <c r="O2" s="128"/>
     </row>
-    <row r="3" spans="1:15" ht="18.600000000000001" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="3" spans="1:15" ht="18.600000000000001" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A3" s="125"/>
       <c r="B3" s="248" t="s">
         <v>92</v>
@@ -7226,7 +7226,7 @@
       <c r="N3" s="248"/>
       <c r="O3" s="248"/>
     </row>
-    <row r="4" spans="1:15" ht="15" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="4" spans="1:15" ht="15" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A4" s="125"/>
       <c r="B4" s="131">
         <v>1</v>
@@ -7247,7 +7247,7 @@
       <c r="N4" s="132"/>
       <c r="O4" s="132"/>
     </row>
-    <row r="5" spans="1:15" ht="18.600000000000001" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="5" spans="1:15" ht="18.600000000000001" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A5" s="125"/>
       <c r="B5" s="133" t="s">
         <v>93</v>
@@ -7278,7 +7278,7 @@
       </c>
       <c r="O5" s="136"/>
     </row>
-    <row r="6" spans="1:15" ht="18.600000000000001" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="6" spans="1:15" ht="18.600000000000001" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A6" s="125"/>
       <c r="B6" s="133" t="s">
         <v>94</v>
@@ -7304,7 +7304,7 @@
       <c r="M6" s="135"/>
       <c r="O6" s="135"/>
     </row>
-    <row r="7" spans="1:15" ht="15.75" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="7" spans="1:15" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A7" s="125"/>
       <c r="B7" s="133" t="s">
         <v>95</v>
@@ -7331,7 +7331,7 @@
       <c r="N7" s="135"/>
       <c r="O7" s="135"/>
     </row>
-    <row r="8" spans="1:15" ht="15.75" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="8" spans="1:15" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A8" s="125"/>
       <c r="B8" s="133"/>
       <c r="C8" s="135"/>
@@ -7348,7 +7348,7 @@
       <c r="N8" s="135"/>
       <c r="O8" s="135"/>
     </row>
-    <row r="9" spans="1:15" ht="15.75" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="9" spans="1:15" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A9" s="125"/>
       <c r="B9" s="133" t="s">
         <v>96</v>
@@ -7375,7 +7375,7 @@
         <v>81000.000000000015</v>
       </c>
     </row>
-    <row r="10" spans="1:15" ht="15.75" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="10" spans="1:15" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A10" s="125"/>
       <c r="B10" s="133" t="s">
         <v>97</v>
@@ -7402,7 +7402,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="11" spans="1:15" ht="15.75" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="11" spans="1:15" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A11" s="125"/>
       <c r="B11" s="133" t="s">
         <v>98</v>
@@ -7428,7 +7428,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="12" spans="1:15" ht="15.75" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="12" spans="1:15" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A12" s="125"/>
       <c r="B12" s="133" t="s">
         <v>99</v>
@@ -7453,7 +7453,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="13" spans="1:15" ht="15.75" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="13" spans="1:15" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A13" s="125"/>
       <c r="B13" s="135"/>
       <c r="C13" s="135"/>
@@ -7480,7 +7480,7 @@
         <v>81000.000000000015</v>
       </c>
     </row>
-    <row r="14" spans="1:15" ht="15.75" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="14" spans="1:15" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A14" s="125"/>
       <c r="B14" s="135"/>
       <c r="C14" s="135"/>
@@ -7497,7 +7497,7 @@
       <c r="N14" s="135"/>
       <c r="O14" s="138"/>
     </row>
-    <row r="15" spans="1:15" ht="15.75" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="15" spans="1:15" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A15" s="125"/>
       <c r="B15" s="135"/>
       <c r="C15" s="133" t="s">
@@ -7517,7 +7517,7 @@
       <c r="N15" s="135"/>
       <c r="O15" s="138"/>
     </row>
-    <row r="16" spans="1:15" ht="15.75" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="16" spans="1:15" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A16" s="125"/>
       <c r="B16" s="135"/>
       <c r="C16" s="135"/>
@@ -7543,7 +7543,7 @@
         <v>10437.5</v>
       </c>
     </row>
-    <row r="17" spans="1:15" ht="15.75" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="17" spans="1:15" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A17" s="125"/>
       <c r="B17" s="135"/>
       <c r="C17" s="135"/>
@@ -7569,7 +7569,7 @@
         <v>2430.0000000000005</v>
       </c>
     </row>
-    <row r="18" spans="1:15" ht="15.75" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="18" spans="1:15" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A18" s="125"/>
       <c r="B18" s="135"/>
       <c r="C18" s="135"/>
@@ -7595,7 +7595,7 @@
         <v>810.00000000000011</v>
       </c>
     </row>
-    <row r="19" spans="1:15" ht="15.75" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="19" spans="1:15" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A19" s="125"/>
       <c r="B19" s="135"/>
       <c r="C19" s="135"/>
@@ -7618,7 +7618,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="20" spans="1:15" ht="15.75" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="20" spans="1:15" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A20" s="125"/>
       <c r="B20" s="135"/>
       <c r="C20" s="135"/>
@@ -7641,7 +7641,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="21" spans="1:15" ht="15.75" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="21" spans="1:15" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A21" s="125"/>
       <c r="B21" s="135"/>
       <c r="C21" s="135"/>
@@ -7664,7 +7664,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="22" spans="1:15" ht="15.75" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="22" spans="1:15" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A22" s="125"/>
       <c r="B22" s="135"/>
       <c r="C22" s="135"/>
@@ -7690,7 +7690,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="23" spans="1:15" ht="15.75" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="23" spans="1:15" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A23" s="125"/>
       <c r="B23" s="135"/>
       <c r="C23" s="135"/>
@@ -7716,7 +7716,7 @@
         <v>13677.5</v>
       </c>
     </row>
-    <row r="24" spans="1:15" ht="15.75" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="24" spans="1:15" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A24" s="125"/>
       <c r="B24" s="135"/>
       <c r="C24" s="135"/>
@@ -7732,7 +7732,7 @@
       <c r="N24" s="135"/>
       <c r="O24" s="138"/>
     </row>
-    <row r="25" spans="1:15" ht="15.75" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="25" spans="1:15" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A25" s="125"/>
       <c r="B25" s="135"/>
       <c r="C25" s="133" t="s">
@@ -7758,7 +7758,7 @@
         <v>67322.500000000015</v>
       </c>
     </row>
-    <row r="26" spans="1:15" ht="15.75" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="26" spans="1:15" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A26" s="125"/>
       <c r="B26" s="135"/>
       <c r="C26" s="133"/>
@@ -7775,7 +7775,7 @@
       <c r="N26" s="135"/>
       <c r="O26" s="138"/>
     </row>
-    <row r="27" spans="1:15" ht="15.75" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="27" spans="1:15" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A27" s="125"/>
       <c r="B27" s="135"/>
       <c r="C27" s="135"/>
@@ -7792,7 +7792,7 @@
       <c r="N27" s="135"/>
       <c r="O27" s="138"/>
     </row>
-    <row r="28" spans="1:15" ht="15.75" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="28" spans="1:15" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A28" s="125"/>
       <c r="B28" s="135"/>
       <c r="C28" s="135"/>
@@ -7813,7 +7813,7 @@
       <c r="N28" s="135"/>
       <c r="O28" s="138"/>
     </row>
-    <row r="29" spans="1:15" ht="15.75" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="29" spans="1:15" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A29" s="125"/>
       <c r="B29" s="135"/>
       <c r="C29" s="135"/>
@@ -7830,7 +7830,7 @@
       <c r="N29" s="135"/>
       <c r="O29" s="138"/>
     </row>
-    <row r="30" spans="1:15" ht="38.1" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="30" spans="1:15" ht="38.1" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A30" s="125"/>
       <c r="B30" s="247" t="s">
         <v>91</v>
@@ -7851,7 +7851,7 @@
       <c r="N30" s="247"/>
       <c r="O30" s="247"/>
     </row>
-    <row r="31" spans="1:15" ht="15" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="31" spans="1:15" ht="15" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A31" s="125"/>
       <c r="B31" s="126"/>
       <c r="C31" s="128"/>
@@ -7868,7 +7868,7 @@
       <c r="N31" s="128"/>
       <c r="O31" s="128"/>
     </row>
-    <row r="32" spans="1:15" ht="18.600000000000001" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="32" spans="1:15" ht="18.600000000000001" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A32" s="125"/>
       <c r="B32" s="248" t="s">
         <v>92</v>
@@ -7889,7 +7889,7 @@
       <c r="N32" s="248"/>
       <c r="O32" s="248"/>
     </row>
-    <row r="33" spans="1:15" ht="15" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="33" spans="1:15" ht="15" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A33" s="125"/>
       <c r="B33" s="131">
         <f>+B4+1</f>
@@ -7912,7 +7912,7 @@
       <c r="N33" s="132"/>
       <c r="O33" s="132"/>
     </row>
-    <row r="34" spans="1:15" ht="18.600000000000001" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="34" spans="1:15" ht="18.600000000000001" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A34" s="125"/>
       <c r="B34" s="133" t="s">
         <v>93</v>
@@ -7944,7 +7944,7 @@
       </c>
       <c r="O34" s="136"/>
     </row>
-    <row r="35" spans="1:15" ht="18.600000000000001" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="35" spans="1:15" ht="18.600000000000001" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A35" s="125"/>
       <c r="B35" s="133" t="s">
         <v>94</v>
@@ -7970,7 +7970,7 @@
       <c r="M35" s="135"/>
       <c r="O35" s="135"/>
     </row>
-    <row r="36" spans="1:15" ht="15.75" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="36" spans="1:15" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A36" s="125"/>
       <c r="B36" s="133" t="s">
         <v>95</v>
@@ -7997,7 +7997,7 @@
       <c r="N36" s="135"/>
       <c r="O36" s="135"/>
     </row>
-    <row r="37" spans="1:15" ht="15.75" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="37" spans="1:15" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A37" s="125"/>
       <c r="B37" s="133"/>
       <c r="C37" s="135"/>
@@ -8014,7 +8014,7 @@
       <c r="N37" s="135"/>
       <c r="O37" s="135"/>
     </row>
-    <row r="38" spans="1:15" ht="15.75" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="38" spans="1:15" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A38" s="125"/>
       <c r="B38" s="133" t="s">
         <v>96</v>
@@ -8041,7 +8041,7 @@
         <v>11336</v>
       </c>
     </row>
-    <row r="39" spans="1:15" ht="15.75" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="39" spans="1:15" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A39" s="125"/>
       <c r="B39" s="133" t="s">
         <v>97</v>
@@ -8068,7 +8068,7 @@
         <v>4251</v>
       </c>
     </row>
-    <row r="40" spans="1:15" ht="15.75" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="40" spans="1:15" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A40" s="125"/>
       <c r="B40" s="133" t="s">
         <v>98</v>
@@ -8094,7 +8094,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="41" spans="1:15" ht="15.75" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="41" spans="1:15" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A41" s="125"/>
       <c r="B41" s="133" t="s">
         <v>99</v>
@@ -8121,7 +8121,7 @@
         <v>1889.3333333333335</v>
       </c>
     </row>
-    <row r="42" spans="1:15" ht="15.75" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="42" spans="1:15" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A42" s="125"/>
       <c r="B42" s="135"/>
       <c r="C42" s="135"/>
@@ -8148,7 +8148,7 @@
         <v>17476.333333333332</v>
       </c>
     </row>
-    <row r="43" spans="1:15" ht="15.75" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="43" spans="1:15" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A43" s="125"/>
       <c r="B43" s="135"/>
       <c r="C43" s="135"/>
@@ -8165,7 +8165,7 @@
       <c r="N43" s="135"/>
       <c r="O43" s="138"/>
     </row>
-    <row r="44" spans="1:15" ht="15.75" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="44" spans="1:15" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A44" s="125"/>
       <c r="B44" s="135"/>
       <c r="C44" s="133" t="s">
@@ -8185,7 +8185,7 @@
       <c r="N44" s="135"/>
       <c r="O44" s="138"/>
     </row>
-    <row r="45" spans="1:15" ht="15.75" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="45" spans="1:15" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A45" s="125"/>
       <c r="B45" s="135"/>
       <c r="C45" s="135"/>
@@ -8211,7 +8211,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="46" spans="1:15" ht="15.75" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="46" spans="1:15" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A46" s="125"/>
       <c r="B46" s="135"/>
       <c r="C46" s="135"/>
@@ -8237,7 +8237,7 @@
         <v>524.29</v>
       </c>
     </row>
-    <row r="47" spans="1:15" ht="15.75" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="47" spans="1:15" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A47" s="125"/>
       <c r="B47" s="135"/>
       <c r="C47" s="135"/>
@@ -8263,7 +8263,7 @@
         <v>174.76333333333332</v>
       </c>
     </row>
-    <row r="48" spans="1:15" ht="15.75" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="48" spans="1:15" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A48" s="125"/>
       <c r="B48" s="135"/>
       <c r="C48" s="135"/>
@@ -8286,7 +8286,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="49" spans="1:15" ht="15.75" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="49" spans="1:15" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A49" s="125"/>
       <c r="B49" s="135"/>
       <c r="C49" s="135"/>
@@ -8309,7 +8309,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="50" spans="1:15" ht="15.75" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="50" spans="1:15" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A50" s="125"/>
       <c r="B50" s="135"/>
       <c r="C50" s="135"/>
@@ -8332,7 +8332,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="51" spans="1:15" ht="15.75" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="51" spans="1:15" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A51" s="125"/>
       <c r="B51" s="135"/>
       <c r="C51" s="135"/>
@@ -8358,7 +8358,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="52" spans="1:15" ht="15.75" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="52" spans="1:15" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A52" s="125"/>
       <c r="B52" s="135"/>
       <c r="C52" s="135"/>
@@ -8384,7 +8384,7 @@
         <v>699.05333333333328</v>
       </c>
     </row>
-    <row r="53" spans="1:15" ht="15.75" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="53" spans="1:15" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A53" s="125"/>
       <c r="B53" s="135"/>
       <c r="C53" s="135"/>
@@ -8401,7 +8401,7 @@
       <c r="N53" s="135"/>
       <c r="O53" s="138"/>
     </row>
-    <row r="54" spans="1:15" ht="15.75" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="54" spans="1:15" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A54" s="125"/>
       <c r="B54" s="135"/>
       <c r="C54" s="133" t="s">
@@ -8428,7 +8428,7 @@
         <v>16777.28</v>
       </c>
     </row>
-    <row r="55" spans="1:15" ht="15.75" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="55" spans="1:15" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A55" s="125"/>
       <c r="B55" s="135"/>
       <c r="C55" s="133"/>
@@ -8445,7 +8445,7 @@
       <c r="N55" s="135"/>
       <c r="O55" s="138"/>
     </row>
-    <row r="56" spans="1:15" ht="15.75" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="56" spans="1:15" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A56" s="125"/>
       <c r="B56" s="135"/>
       <c r="C56" s="135"/>
@@ -8462,7 +8462,7 @@
       <c r="N56" s="135"/>
       <c r="O56" s="138"/>
     </row>
-    <row r="57" spans="1:15" ht="15.75" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="57" spans="1:15" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A57" s="125"/>
       <c r="B57" s="135"/>
       <c r="C57" s="135"/>
@@ -8483,7 +8483,7 @@
       <c r="N57" s="135"/>
       <c r="O57" s="138"/>
     </row>
-    <row r="58" spans="1:15" ht="15.75" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="58" spans="1:15" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A58" s="125"/>
       <c r="B58" s="135"/>
       <c r="C58" s="135"/>
@@ -8500,7 +8500,7 @@
       <c r="N58" s="135"/>
       <c r="O58" s="138"/>
     </row>
-    <row r="59" spans="1:15" ht="38.1" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="59" spans="1:15" ht="38.1" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A59" s="125"/>
       <c r="B59" s="247" t="s">
         <v>91</v>
@@ -8521,7 +8521,7 @@
       <c r="N59" s="247"/>
       <c r="O59" s="247"/>
     </row>
-    <row r="60" spans="1:15" ht="15" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="60" spans="1:15" ht="15" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A60" s="125"/>
       <c r="B60" s="126"/>
       <c r="C60" s="128"/>
@@ -8538,7 +8538,7 @@
       <c r="N60" s="128"/>
       <c r="O60" s="128"/>
     </row>
-    <row r="61" spans="1:15" ht="18.600000000000001" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="61" spans="1:15" ht="18.600000000000001" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A61" s="125"/>
       <c r="B61" s="248" t="s">
         <v>92</v>
@@ -8559,7 +8559,7 @@
       <c r="N61" s="248"/>
       <c r="O61" s="248"/>
     </row>
-    <row r="62" spans="1:15" ht="15" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="62" spans="1:15" ht="15" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A62" s="125"/>
       <c r="B62" s="131">
         <f>+B33+1</f>
@@ -8582,7 +8582,7 @@
       <c r="N62" s="132"/>
       <c r="O62" s="132"/>
     </row>
-    <row r="63" spans="1:15" ht="18.600000000000001" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="63" spans="1:15" ht="18.600000000000001" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A63" s="125"/>
       <c r="B63" s="133" t="s">
         <v>93</v>
@@ -8614,7 +8614,7 @@
       </c>
       <c r="O63" s="136"/>
     </row>
-    <row r="64" spans="1:15" ht="18.600000000000001" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="64" spans="1:15" ht="18.600000000000001" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A64" s="125"/>
       <c r="B64" s="133" t="s">
         <v>94</v>
@@ -8640,7 +8640,7 @@
       <c r="M64" s="135"/>
       <c r="O64" s="135"/>
     </row>
-    <row r="65" spans="1:15" ht="15.75" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="65" spans="1:15" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A65" s="125"/>
       <c r="B65" s="133" t="s">
         <v>95</v>
@@ -8664,7 +8664,7 @@
       <c r="N65" s="135"/>
       <c r="O65" s="135"/>
     </row>
-    <row r="66" spans="1:15" ht="15.75" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="66" spans="1:15" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A66" s="125"/>
       <c r="B66" s="133"/>
       <c r="C66" s="135"/>
@@ -8681,7 +8681,7 @@
       <c r="N66" s="135"/>
       <c r="O66" s="135"/>
     </row>
-    <row r="67" spans="1:15" ht="15.75" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="67" spans="1:15" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A67" s="125"/>
       <c r="B67" s="133" t="s">
         <v>96</v>
@@ -8708,7 +8708,7 @@
         <v>11336</v>
       </c>
     </row>
-    <row r="68" spans="1:15" ht="15.75" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="68" spans="1:15" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A68" s="125"/>
       <c r="B68" s="133" t="s">
         <v>97</v>
@@ -8735,7 +8735,7 @@
         <v>4723.333333333333</v>
       </c>
     </row>
-    <row r="69" spans="1:15" ht="15.75" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="69" spans="1:15" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A69" s="125"/>
       <c r="B69" s="133" t="s">
         <v>98</v>
@@ -8761,7 +8761,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="70" spans="1:15" ht="15.75" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="70" spans="1:15" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A70" s="125"/>
       <c r="B70" s="133" t="s">
         <v>99</v>
@@ -8788,7 +8788,7 @@
         <v>1889.3333333333335</v>
       </c>
     </row>
-    <row r="71" spans="1:15" ht="15.75" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="71" spans="1:15" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A71" s="125"/>
       <c r="B71" s="135"/>
       <c r="C71" s="135"/>
@@ -8815,7 +8815,7 @@
         <v>17948.666666666664</v>
       </c>
     </row>
-    <row r="72" spans="1:15" ht="15.75" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="72" spans="1:15" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A72" s="125"/>
       <c r="B72" s="135"/>
       <c r="C72" s="135"/>
@@ -8832,7 +8832,7 @@
       <c r="N72" s="135"/>
       <c r="O72" s="138"/>
     </row>
-    <row r="73" spans="1:15" ht="15.75" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="73" spans="1:15" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A73" s="125"/>
       <c r="B73" s="135"/>
       <c r="C73" s="133" t="s">
@@ -8852,7 +8852,7 @@
       <c r="N73" s="135"/>
       <c r="O73" s="138"/>
     </row>
-    <row r="74" spans="1:15" ht="15.75" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="74" spans="1:15" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A74" s="125"/>
       <c r="B74" s="135"/>
       <c r="C74" s="135"/>
@@ -8878,7 +8878,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="75" spans="1:15" ht="15.75" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="75" spans="1:15" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A75" s="125"/>
       <c r="B75" s="135"/>
       <c r="C75" s="135"/>
@@ -8904,7 +8904,7 @@
         <v>538.45999999999992</v>
       </c>
     </row>
-    <row r="76" spans="1:15" ht="15.75" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="76" spans="1:15" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A76" s="125"/>
       <c r="B76" s="135"/>
       <c r="C76" s="135"/>
@@ -8930,7 +8930,7 @@
         <v>179.48666666666665</v>
       </c>
     </row>
-    <row r="77" spans="1:15" ht="15.75" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="77" spans="1:15" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A77" s="125"/>
       <c r="B77" s="135"/>
       <c r="C77" s="135"/>
@@ -8953,7 +8953,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="78" spans="1:15" ht="15.75" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="78" spans="1:15" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A78" s="125"/>
       <c r="B78" s="135"/>
       <c r="C78" s="135"/>
@@ -8976,7 +8976,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="79" spans="1:15" ht="15.75" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="79" spans="1:15" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A79" s="125"/>
       <c r="B79" s="135"/>
       <c r="C79" s="135"/>
@@ -8999,7 +8999,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="80" spans="1:15" ht="15.75" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="80" spans="1:15" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A80" s="125"/>
       <c r="B80" s="135"/>
       <c r="C80" s="135"/>
@@ -9026,7 +9026,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="81" spans="1:15" ht="15.75" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="81" spans="1:15" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A81" s="125"/>
       <c r="B81" s="135"/>
       <c r="C81" s="135"/>
@@ -9052,7 +9052,7 @@
         <v>717.9466666666666</v>
       </c>
     </row>
-    <row r="82" spans="1:15" ht="15.75" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="82" spans="1:15" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A82" s="125"/>
       <c r="B82" s="135"/>
       <c r="C82" s="135"/>
@@ -9069,7 +9069,7 @@
       <c r="N82" s="135"/>
       <c r="O82" s="138"/>
     </row>
-    <row r="83" spans="1:15" ht="15.75" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="83" spans="1:15" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A83" s="125"/>
       <c r="B83" s="135"/>
       <c r="C83" s="133" t="s">
@@ -9096,7 +9096,7 @@
         <v>17230.719999999998</v>
       </c>
     </row>
-    <row r="84" spans="1:15" ht="15.75" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="84" spans="1:15" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A84" s="125"/>
       <c r="B84" s="135"/>
       <c r="C84" s="133"/>
@@ -9113,7 +9113,7 @@
       <c r="N84" s="135"/>
       <c r="O84" s="138"/>
     </row>
-    <row r="85" spans="1:15" ht="15.75" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="85" spans="1:15" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A85" s="125"/>
       <c r="B85" s="135"/>
       <c r="C85" s="135"/>
@@ -9130,7 +9130,7 @@
       <c r="N85" s="135"/>
       <c r="O85" s="138"/>
     </row>
-    <row r="86" spans="1:15" ht="15.75" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="86" spans="1:15" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A86" s="125"/>
       <c r="B86" s="135"/>
       <c r="C86" s="135"/>
@@ -9151,7 +9151,7 @@
       <c r="N86" s="135"/>
       <c r="O86" s="138"/>
     </row>
-    <row r="87" spans="1:15" ht="15.75" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="87" spans="1:15" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A87" s="125"/>
       <c r="B87" s="135"/>
       <c r="C87" s="135"/>
@@ -9168,7 +9168,7 @@
       <c r="N87" s="135"/>
       <c r="O87" s="138"/>
     </row>
-    <row r="88" spans="1:15" ht="38.1" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="88" spans="1:15" ht="38.1" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A88" s="125"/>
       <c r="B88" s="247" t="s">
         <v>91</v>
@@ -9189,7 +9189,7 @@
       <c r="N88" s="247"/>
       <c r="O88" s="247"/>
     </row>
-    <row r="89" spans="1:15" ht="15" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="89" spans="1:15" ht="15" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A89" s="125"/>
       <c r="B89" s="126"/>
       <c r="C89" s="128"/>
@@ -9206,7 +9206,7 @@
       <c r="N89" s="128"/>
       <c r="O89" s="128"/>
     </row>
-    <row r="90" spans="1:15" ht="18.600000000000001" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="90" spans="1:15" ht="18.600000000000001" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A90" s="125"/>
       <c r="B90" s="248" t="s">
         <v>92</v>
@@ -9227,7 +9227,7 @@
       <c r="N90" s="248"/>
       <c r="O90" s="248"/>
     </row>
-    <row r="91" spans="1:15" ht="15" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="91" spans="1:15" ht="15" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A91" s="125"/>
       <c r="B91" s="131">
         <f>+B62+1</f>
@@ -9249,7 +9249,7 @@
       <c r="N91" s="132"/>
       <c r="O91" s="132"/>
     </row>
-    <row r="92" spans="1:15" ht="18.600000000000001" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="92" spans="1:15" ht="18.600000000000001" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A92" s="125"/>
       <c r="B92" s="133" t="s">
         <v>93</v>
@@ -9281,7 +9281,7 @@
       </c>
       <c r="O92" s="136"/>
     </row>
-    <row r="93" spans="1:15" ht="18.600000000000001" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="93" spans="1:15" ht="18.600000000000001" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A93" s="125"/>
       <c r="B93" s="133" t="s">
         <v>94</v>
@@ -9307,7 +9307,7 @@
       <c r="M93" s="135"/>
       <c r="O93" s="135"/>
     </row>
-    <row r="94" spans="1:15" ht="15.75" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="94" spans="1:15" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A94" s="125"/>
       <c r="B94" s="133" t="s">
         <v>95</v>
@@ -9334,7 +9334,7 @@
       <c r="N94" s="135"/>
       <c r="O94" s="135"/>
     </row>
-    <row r="95" spans="1:15" ht="15.75" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="95" spans="1:15" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A95" s="125"/>
       <c r="B95" s="133"/>
       <c r="C95" s="135"/>
@@ -9351,7 +9351,7 @@
       <c r="N95" s="135"/>
       <c r="O95" s="135"/>
     </row>
-    <row r="96" spans="1:15" ht="15.75" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="96" spans="1:15" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A96" s="125"/>
       <c r="B96" s="133" t="s">
         <v>96</v>
@@ -9378,7 +9378,7 @@
         <v>11336</v>
       </c>
     </row>
-    <row r="97" spans="1:15" ht="15.75" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="97" spans="1:15" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A97" s="125"/>
       <c r="B97" s="133" t="s">
         <v>97</v>
@@ -9405,7 +9405,7 @@
         <v>944.66666666666663</v>
       </c>
     </row>
-    <row r="98" spans="1:15" ht="15.75" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="98" spans="1:15" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A98" s="125"/>
       <c r="B98" s="133" t="s">
         <v>98</v>
@@ -9431,7 +9431,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="99" spans="1:15" ht="15.75" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="99" spans="1:15" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A99" s="125"/>
       <c r="B99" s="133" t="s">
         <v>99</v>
@@ -9458,7 +9458,7 @@
         <v>1889.3333333333335</v>
       </c>
     </row>
-    <row r="100" spans="1:15" ht="15.75" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="100" spans="1:15" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A100" s="125"/>
       <c r="B100" s="135"/>
       <c r="C100" s="135"/>
@@ -9485,7 +9485,7 @@
         <v>14170</v>
       </c>
     </row>
-    <row r="101" spans="1:15" ht="15.75" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="101" spans="1:15" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A101" s="125"/>
       <c r="B101" s="135"/>
       <c r="C101" s="135"/>
@@ -9502,7 +9502,7 @@
       <c r="N101" s="135"/>
       <c r="O101" s="138"/>
     </row>
-    <row r="102" spans="1:15" ht="15.75" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="102" spans="1:15" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A102" s="125"/>
       <c r="B102" s="135"/>
       <c r="C102" s="133" t="s">
@@ -9522,7 +9522,7 @@
       <c r="M102" s="135"/>
       <c r="O102" s="138"/>
     </row>
-    <row r="103" spans="1:15" ht="15.75" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="103" spans="1:15" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A103" s="125"/>
       <c r="B103" s="135"/>
       <c r="C103" s="135"/>
@@ -9548,7 +9548,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="104" spans="1:15" ht="15.75" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="104" spans="1:15" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A104" s="125"/>
       <c r="B104" s="135"/>
       <c r="C104" s="135"/>
@@ -9574,7 +9574,7 @@
         <v>425.09999999999997</v>
       </c>
     </row>
-    <row r="105" spans="1:15" ht="15.75" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="105" spans="1:15" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A105" s="125"/>
       <c r="B105" s="135"/>
       <c r="C105" s="135"/>
@@ -9600,7 +9600,7 @@
         <v>141.70000000000002</v>
       </c>
     </row>
-    <row r="106" spans="1:15" ht="15.75" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="106" spans="1:15" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A106" s="125"/>
       <c r="B106" s="135"/>
       <c r="C106" s="135"/>
@@ -9623,7 +9623,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="107" spans="1:15" ht="15.75" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="107" spans="1:15" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A107" s="125"/>
       <c r="B107" s="135"/>
       <c r="C107" s="135"/>
@@ -9646,7 +9646,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="108" spans="1:15" ht="15.75" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="108" spans="1:15" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A108" s="125"/>
       <c r="B108" s="135"/>
       <c r="C108" s="135"/>
@@ -9669,7 +9669,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="109" spans="1:15" ht="15.75" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="109" spans="1:15" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A109" s="125"/>
       <c r="B109" s="135"/>
       <c r="C109" s="135"/>
@@ -9696,7 +9696,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="110" spans="1:15" ht="15.75" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="110" spans="1:15" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A110" s="125"/>
       <c r="B110" s="135"/>
       <c r="C110" s="135"/>
@@ -9723,7 +9723,7 @@
         <v>566.79999999999995</v>
       </c>
     </row>
-    <row r="111" spans="1:15" ht="15.75" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="111" spans="1:15" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A111" s="125"/>
       <c r="B111" s="135"/>
       <c r="C111" s="135"/>
@@ -9740,7 +9740,7 @@
       <c r="N111" s="135"/>
       <c r="O111" s="138"/>
     </row>
-    <row r="112" spans="1:15" ht="15.75" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="112" spans="1:15" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A112" s="125"/>
       <c r="B112" s="135"/>
       <c r="C112" s="133" t="s">
@@ -9767,7 +9767,7 @@
         <v>13603.2</v>
       </c>
     </row>
-    <row r="113" spans="1:15" ht="15.75" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="113" spans="1:15" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A113" s="125"/>
       <c r="B113" s="135"/>
       <c r="C113" s="133"/>
@@ -9784,7 +9784,7 @@
       <c r="N113" s="135"/>
       <c r="O113" s="138"/>
     </row>
-    <row r="114" spans="1:15" ht="15.75" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="114" spans="1:15" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A114" s="125"/>
       <c r="B114" s="135"/>
       <c r="C114" s="135"/>
@@ -9801,7 +9801,7 @@
       <c r="N114" s="135"/>
       <c r="O114" s="138"/>
     </row>
-    <row r="115" spans="1:15" ht="15.75" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="115" spans="1:15" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A115" s="125"/>
       <c r="B115" s="135"/>
       <c r="C115" s="135"/>
@@ -9822,7 +9822,7 @@
       <c r="N115" s="135"/>
       <c r="O115" s="138"/>
     </row>
-    <row r="116" spans="1:15" ht="38.1" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="116" spans="1:15" ht="38.1" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A116" s="125"/>
       <c r="B116" s="247" t="s">
         <v>91</v>
@@ -9843,7 +9843,7 @@
       <c r="N116" s="247"/>
       <c r="O116" s="247"/>
     </row>
-    <row r="117" spans="1:15" ht="15" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="117" spans="1:15" ht="15" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A117" s="125"/>
       <c r="B117" s="126"/>
       <c r="C117" s="128"/>
@@ -9860,7 +9860,7 @@
       <c r="N117" s="128"/>
       <c r="O117" s="128"/>
     </row>
-    <row r="118" spans="1:15" ht="18.600000000000001" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="118" spans="1:15" ht="18.600000000000001" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A118" s="125"/>
       <c r="B118" s="248" t="s">
         <v>92</v>
@@ -9881,7 +9881,7 @@
       <c r="N118" s="248"/>
       <c r="O118" s="248"/>
     </row>
-    <row r="119" spans="1:15" ht="15" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="119" spans="1:15" ht="15" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A119" s="125"/>
       <c r="B119" s="131">
         <f>+B91+1</f>
@@ -9903,7 +9903,7 @@
       <c r="N119" s="132"/>
       <c r="O119" s="132"/>
     </row>
-    <row r="120" spans="1:15" ht="18.600000000000001" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="120" spans="1:15" ht="18.600000000000001" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A120" s="125"/>
       <c r="B120" s="133" t="s">
         <v>93</v>
@@ -9935,7 +9935,7 @@
       </c>
       <c r="O120" s="136"/>
     </row>
-    <row r="121" spans="1:15" ht="18.600000000000001" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="121" spans="1:15" ht="18.600000000000001" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A121" s="125"/>
       <c r="B121" s="133" t="s">
         <v>94</v>
@@ -9961,7 +9961,7 @@
       <c r="M121" s="135"/>
       <c r="O121" s="135"/>
     </row>
-    <row r="122" spans="1:15" ht="15.75" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="122" spans="1:15" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A122" s="125"/>
       <c r="B122" s="133" t="s">
         <v>95</v>
@@ -9988,7 +9988,7 @@
       <c r="N122" s="135"/>
       <c r="O122" s="135"/>
     </row>
-    <row r="123" spans="1:15" ht="15.75" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="123" spans="1:15" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A123" s="125"/>
       <c r="B123" s="133"/>
       <c r="C123" s="135"/>
@@ -10005,7 +10005,7 @@
       <c r="N123" s="135"/>
       <c r="O123" s="135"/>
     </row>
-    <row r="124" spans="1:15" ht="15.75" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="124" spans="1:15" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A124" s="125"/>
       <c r="B124" s="133" t="s">
         <v>96</v>
@@ -10032,7 +10032,7 @@
         <v>10900</v>
       </c>
     </row>
-    <row r="125" spans="1:15" ht="15.75" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="125" spans="1:15" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A125" s="125"/>
       <c r="B125" s="133" t="s">
         <v>97</v>
@@ -10059,7 +10059,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="126" spans="1:15" ht="15.75" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="126" spans="1:15" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A126" s="125"/>
       <c r="B126" s="133" t="s">
         <v>98</v>
@@ -10085,7 +10085,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="127" spans="1:15" ht="15.75" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="127" spans="1:15" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A127" s="125"/>
       <c r="B127" s="133" t="s">
         <v>99</v>
@@ -10110,7 +10110,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="128" spans="1:15" ht="15.75" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="128" spans="1:15" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A128" s="125"/>
       <c r="B128" s="135"/>
       <c r="C128" s="135"/>
@@ -10137,7 +10137,7 @@
         <v>10900</v>
       </c>
     </row>
-    <row r="129" spans="1:15" ht="15.75" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="129" spans="1:15" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A129" s="125"/>
       <c r="B129" s="135"/>
       <c r="C129" s="135"/>
@@ -10154,7 +10154,7 @@
       <c r="N129" s="135"/>
       <c r="O129" s="138"/>
     </row>
-    <row r="130" spans="1:15" ht="15.75" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="130" spans="1:15" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A130" s="125"/>
       <c r="B130" s="135"/>
       <c r="C130" s="133" t="s">
@@ -10174,7 +10174,7 @@
       <c r="N130" s="135"/>
       <c r="O130" s="138"/>
     </row>
-    <row r="131" spans="1:15" ht="15.75" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="131" spans="1:15" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A131" s="125"/>
       <c r="B131" s="135"/>
       <c r="C131" s="135"/>
@@ -10200,7 +10200,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="132" spans="1:15" ht="15.75" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="132" spans="1:15" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A132" s="125"/>
       <c r="B132" s="135"/>
       <c r="C132" s="135"/>
@@ -10226,7 +10226,7 @@
         <v>327</v>
       </c>
     </row>
-    <row r="133" spans="1:15" ht="15.75" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="133" spans="1:15" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A133" s="125"/>
       <c r="B133" s="135"/>
       <c r="C133" s="135"/>
@@ -10252,7 +10252,7 @@
         <v>109</v>
       </c>
     </row>
-    <row r="134" spans="1:15" ht="15.75" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="134" spans="1:15" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A134" s="125"/>
       <c r="B134" s="135"/>
       <c r="C134" s="135"/>
@@ -10275,7 +10275,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="135" spans="1:15" ht="15.75" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="135" spans="1:15" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A135" s="125"/>
       <c r="B135" s="135"/>
       <c r="C135" s="135"/>
@@ -10298,7 +10298,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="136" spans="1:15" ht="15.75" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="136" spans="1:15" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A136" s="125"/>
       <c r="B136" s="135"/>
       <c r="C136" s="135"/>
@@ -10321,7 +10321,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="137" spans="1:15" ht="15.75" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="137" spans="1:15" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A137" s="125"/>
       <c r="B137" s="135"/>
       <c r="C137" s="135"/>
@@ -10348,7 +10348,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="138" spans="1:15" ht="15.75" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="138" spans="1:15" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A138" s="125"/>
       <c r="B138" s="135"/>
       <c r="C138" s="135"/>
@@ -10369,7 +10369,7 @@
       <c r="N138" s="135"/>
       <c r="O138" s="138"/>
     </row>
-    <row r="139" spans="1:15" ht="15.75" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="139" spans="1:15" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A139" s="125"/>
       <c r="B139" s="135"/>
       <c r="C139" s="135"/>
@@ -10395,7 +10395,7 @@
         <v>436</v>
       </c>
     </row>
-    <row r="140" spans="1:15" ht="15.75" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="140" spans="1:15" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A140" s="125"/>
       <c r="B140" s="135"/>
       <c r="C140" s="135"/>
@@ -10412,7 +10412,7 @@
       <c r="N140" s="135"/>
       <c r="O140" s="138"/>
     </row>
-    <row r="141" spans="1:15" ht="15.75" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="141" spans="1:15" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A141" s="125"/>
       <c r="B141" s="135"/>
       <c r="C141" s="133" t="s">
@@ -10439,7 +10439,7 @@
         <v>10464</v>
       </c>
     </row>
-    <row r="142" spans="1:15" ht="15.75" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="142" spans="1:15" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A142" s="125"/>
       <c r="B142" s="135"/>
       <c r="C142" s="133"/>
@@ -10456,7 +10456,7 @@
       <c r="N142" s="135"/>
       <c r="O142" s="138"/>
     </row>
-    <row r="143" spans="1:15" ht="15.75" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="143" spans="1:15" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A143" s="125"/>
       <c r="B143" s="135"/>
       <c r="C143" s="135"/>
@@ -10473,7 +10473,7 @@
       <c r="N143" s="135"/>
       <c r="O143" s="138"/>
     </row>
-    <row r="144" spans="1:15" ht="15.75" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="144" spans="1:15" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A144" s="125"/>
       <c r="B144" s="135"/>
       <c r="C144" s="135"/>
@@ -10494,7 +10494,7 @@
       <c r="N144" s="135"/>
       <c r="O144" s="138"/>
     </row>
-    <row r="145" spans="1:15" ht="38.1" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="145" spans="1:15" ht="38.1" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A145" s="125"/>
       <c r="B145" s="247" t="s">
         <v>91</v>
@@ -10515,7 +10515,7 @@
       <c r="N145" s="247"/>
       <c r="O145" s="247"/>
     </row>
-    <row r="146" spans="1:15" ht="15" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="146" spans="1:15" ht="15" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A146" s="125"/>
       <c r="B146" s="126"/>
       <c r="C146" s="128"/>
@@ -10532,7 +10532,7 @@
       <c r="N146" s="128"/>
       <c r="O146" s="128"/>
     </row>
-    <row r="147" spans="1:15" ht="18.600000000000001" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="147" spans="1:15" ht="18.600000000000001" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A147" s="125"/>
       <c r="B147" s="248" t="s">
         <v>92</v>
@@ -10553,7 +10553,7 @@
       <c r="N147" s="248"/>
       <c r="O147" s="248"/>
     </row>
-    <row r="148" spans="1:15" ht="15" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="148" spans="1:15" ht="15" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A148" s="125"/>
       <c r="B148" s="131">
         <f>+B119+1</f>
@@ -10575,7 +10575,7 @@
       <c r="N148" s="132"/>
       <c r="O148" s="132"/>
     </row>
-    <row r="149" spans="1:15" ht="18.600000000000001" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="149" spans="1:15" ht="18.600000000000001" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A149" s="125"/>
       <c r="B149" s="133" t="s">
         <v>93</v>
@@ -10607,7 +10607,7 @@
       </c>
       <c r="O149" s="136"/>
     </row>
-    <row r="150" spans="1:15" ht="18.600000000000001" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="150" spans="1:15" ht="18.600000000000001" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A150" s="125"/>
       <c r="B150" s="133" t="s">
         <v>94</v>
@@ -10633,7 +10633,7 @@
       <c r="M150" s="135"/>
       <c r="O150" s="135"/>
     </row>
-    <row r="151" spans="1:15" ht="15.75" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="151" spans="1:15" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A151" s="125"/>
       <c r="B151" s="133" t="s">
         <v>95</v>
@@ -10660,7 +10660,7 @@
       <c r="N151" s="135"/>
       <c r="O151" s="135"/>
     </row>
-    <row r="152" spans="1:15" ht="15.75" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="152" spans="1:15" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A152" s="125"/>
       <c r="B152" s="133"/>
       <c r="C152" s="135"/>
@@ -10677,7 +10677,7 @@
       <c r="N152" s="135"/>
       <c r="O152" s="135"/>
     </row>
-    <row r="153" spans="1:15" ht="15.75" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="153" spans="1:15" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A153" s="125"/>
       <c r="B153" s="133" t="s">
         <v>96</v>
@@ -10704,7 +10704,7 @@
         <v>11445</v>
       </c>
     </row>
-    <row r="154" spans="1:15" ht="15.75" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="154" spans="1:15" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A154" s="125"/>
       <c r="B154" s="133" t="s">
         <v>97</v>
@@ -10731,7 +10731,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="155" spans="1:15" ht="15.75" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="155" spans="1:15" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A155" s="125"/>
       <c r="B155" s="133" t="s">
         <v>98</v>
@@ -10757,7 +10757,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="156" spans="1:15" ht="15.75" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="156" spans="1:15" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A156" s="125"/>
       <c r="B156" s="133" t="s">
         <v>99</v>
@@ -10782,7 +10782,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="157" spans="1:15" ht="15.75" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="157" spans="1:15" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A157" s="125"/>
       <c r="B157" s="135"/>
       <c r="C157" s="135"/>
@@ -10809,7 +10809,7 @@
         <v>11445</v>
       </c>
     </row>
-    <row r="158" spans="1:15" ht="15.75" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="158" spans="1:15" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A158" s="125"/>
       <c r="B158" s="135"/>
       <c r="C158" s="135"/>
@@ -10826,7 +10826,7 @@
       <c r="N158" s="135"/>
       <c r="O158" s="138"/>
     </row>
-    <row r="159" spans="1:15" ht="15.75" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="159" spans="1:15" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A159" s="125"/>
       <c r="B159" s="135"/>
       <c r="C159" s="133" t="s">
@@ -10846,7 +10846,7 @@
       <c r="N159" s="135"/>
       <c r="O159" s="138"/>
     </row>
-    <row r="160" spans="1:15" ht="15.75" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="160" spans="1:15" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A160" s="125"/>
       <c r="B160" s="135"/>
       <c r="C160" s="135"/>
@@ -10872,7 +10872,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="161" spans="1:15" ht="15.75" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="161" spans="1:15" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A161" s="125"/>
       <c r="B161" s="135"/>
       <c r="C161" s="135"/>
@@ -10898,7 +10898,7 @@
         <v>343.34999999999997</v>
       </c>
     </row>
-    <row r="162" spans="1:15" ht="15.75" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="162" spans="1:15" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A162" s="125"/>
       <c r="B162" s="135"/>
       <c r="C162" s="135"/>
@@ -10924,7 +10924,7 @@
         <v>114.45</v>
       </c>
     </row>
-    <row r="163" spans="1:15" ht="15.75" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="163" spans="1:15" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A163" s="125"/>
       <c r="B163" s="135"/>
       <c r="C163" s="135"/>
@@ -10947,7 +10947,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="164" spans="1:15" ht="15.75" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="164" spans="1:15" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A164" s="125"/>
       <c r="B164" s="135"/>
       <c r="C164" s="135"/>
@@ -10970,7 +10970,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="165" spans="1:15" ht="15.75" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="165" spans="1:15" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A165" s="125"/>
       <c r="B165" s="135"/>
       <c r="C165" s="135"/>
@@ -10993,7 +10993,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="166" spans="1:15" ht="15.75" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="166" spans="1:15" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A166" s="125"/>
       <c r="B166" s="135"/>
       <c r="C166" s="135"/>
@@ -11020,7 +11020,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="167" spans="1:15" ht="15.75" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="167" spans="1:15" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A167" s="125"/>
       <c r="B167" s="135"/>
       <c r="C167" s="135"/>
@@ -11046,7 +11046,7 @@
         <v>457.79999999999995</v>
       </c>
     </row>
-    <row r="168" spans="1:15" ht="15.75" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="168" spans="1:15" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A168" s="125"/>
       <c r="B168" s="135"/>
       <c r="C168" s="135"/>
@@ -11063,7 +11063,7 @@
       <c r="N168" s="135"/>
       <c r="O168" s="138"/>
     </row>
-    <row r="169" spans="1:15" ht="15.75" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="169" spans="1:15" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A169" s="125"/>
       <c r="B169" s="135"/>
       <c r="C169" s="133" t="s">
@@ -11090,7 +11090,7 @@
         <v>10987.2</v>
       </c>
     </row>
-    <row r="170" spans="1:15" ht="15.75" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="170" spans="1:15" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A170" s="125"/>
       <c r="B170" s="135"/>
       <c r="C170" s="133"/>
@@ -11107,7 +11107,7 @@
       <c r="N170" s="135"/>
       <c r="O170" s="138"/>
     </row>
-    <row r="171" spans="1:15" ht="15.75" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="171" spans="1:15" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A171" s="125"/>
       <c r="B171" s="135"/>
       <c r="C171" s="135"/>
@@ -11124,7 +11124,7 @@
       <c r="N171" s="135"/>
       <c r="O171" s="138"/>
     </row>
-    <row r="172" spans="1:15" ht="15.75" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="172" spans="1:15" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A172" s="125"/>
       <c r="B172" s="135"/>
       <c r="C172" s="135"/>
@@ -11145,7 +11145,7 @@
       <c r="N172" s="135"/>
       <c r="O172" s="138"/>
     </row>
-    <row r="173" spans="1:15" ht="38.1" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="173" spans="1:15" ht="38.1" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A173" s="125"/>
       <c r="B173" s="247" t="s">
         <v>91</v>
@@ -11166,7 +11166,7 @@
       <c r="N173" s="247"/>
       <c r="O173" s="247"/>
     </row>
-    <row r="174" spans="1:15" ht="15" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="174" spans="1:15" ht="15" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A174" s="125"/>
       <c r="B174" s="126"/>
       <c r="C174" s="128"/>
@@ -11183,7 +11183,7 @@
       <c r="N174" s="128"/>
       <c r="O174" s="128"/>
     </row>
-    <row r="175" spans="1:15" ht="18.600000000000001" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="175" spans="1:15" ht="18.600000000000001" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A175" s="125"/>
       <c r="B175" s="248" t="s">
         <v>92</v>
@@ -11204,7 +11204,7 @@
       <c r="N175" s="248"/>
       <c r="O175" s="248"/>
     </row>
-    <row r="176" spans="1:15" ht="15" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="176" spans="1:15" ht="15" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A176" s="125"/>
       <c r="B176" s="131">
         <f>+B148+1</f>
@@ -11227,7 +11227,7 @@
       <c r="N176" s="132"/>
       <c r="O176" s="132"/>
     </row>
-    <row r="177" spans="1:15" ht="18.600000000000001" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="177" spans="1:15" ht="18.600000000000001" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A177" s="125"/>
       <c r="B177" s="133" t="s">
         <v>93</v>
@@ -11259,7 +11259,7 @@
       </c>
       <c r="O177" s="136"/>
     </row>
-    <row r="178" spans="1:15" ht="18.600000000000001" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="178" spans="1:15" ht="18.600000000000001" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A178" s="125"/>
       <c r="B178" s="133" t="s">
         <v>94</v>
@@ -11285,7 +11285,7 @@
       <c r="M178" s="135"/>
       <c r="O178" s="135"/>
     </row>
-    <row r="179" spans="1:15" ht="15.75" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="179" spans="1:15" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A179" s="125"/>
       <c r="B179" s="133" t="s">
         <v>95</v>
@@ -11312,7 +11312,7 @@
       <c r="N179" s="135"/>
       <c r="O179" s="135"/>
     </row>
-    <row r="180" spans="1:15" ht="15.75" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="180" spans="1:15" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A180" s="125"/>
       <c r="B180" s="133"/>
       <c r="C180" s="135"/>
@@ -11329,7 +11329,7 @@
       <c r="N180" s="135"/>
       <c r="O180" s="135"/>
     </row>
-    <row r="181" spans="1:15" ht="15.75" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="181" spans="1:15" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A181" s="125"/>
       <c r="B181" s="133" t="s">
         <v>96</v>
@@ -11356,7 +11356,7 @@
         <v>10900</v>
       </c>
     </row>
-    <row r="182" spans="1:15" ht="15.75" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="182" spans="1:15" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A182" s="125"/>
       <c r="B182" s="133" t="s">
         <v>97</v>
@@ -11383,7 +11383,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="183" spans="1:15" ht="15.75" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="183" spans="1:15" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A183" s="125"/>
       <c r="B183" s="133" t="s">
         <v>98</v>
@@ -11409,7 +11409,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="184" spans="1:15" ht="15.75" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="184" spans="1:15" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A184" s="125"/>
       <c r="B184" s="133" t="s">
         <v>99</v>
@@ -11436,7 +11436,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="185" spans="1:15" ht="15.75" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="185" spans="1:15" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A185" s="125"/>
       <c r="B185" s="135"/>
       <c r="C185" s="135"/>
@@ -11463,7 +11463,7 @@
         <v>10900</v>
       </c>
     </row>
-    <row r="186" spans="1:15" ht="15.75" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="186" spans="1:15" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A186" s="125"/>
       <c r="B186" s="135"/>
       <c r="C186" s="135"/>
@@ -11480,7 +11480,7 @@
       <c r="N186" s="135"/>
       <c r="O186" s="138"/>
     </row>
-    <row r="187" spans="1:15" ht="15.75" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="187" spans="1:15" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A187" s="125"/>
       <c r="B187" s="135"/>
       <c r="C187" s="133" t="s">
@@ -11500,7 +11500,7 @@
       <c r="M187" s="135"/>
       <c r="O187" s="138"/>
     </row>
-    <row r="188" spans="1:15" ht="15.75" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="188" spans="1:15" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A188" s="125"/>
       <c r="B188" s="135"/>
       <c r="C188" s="135"/>
@@ -11526,7 +11526,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="189" spans="1:15" ht="15.75" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="189" spans="1:15" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A189" s="125"/>
       <c r="B189" s="135"/>
       <c r="C189" s="135"/>
@@ -11552,7 +11552,7 @@
         <v>327</v>
       </c>
     </row>
-    <row r="190" spans="1:15" ht="15.75" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="190" spans="1:15" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A190" s="125"/>
       <c r="B190" s="135"/>
       <c r="C190" s="135"/>
@@ -11578,7 +11578,7 @@
         <v>109</v>
       </c>
     </row>
-    <row r="191" spans="1:15" ht="15.75" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="191" spans="1:15" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A191" s="125"/>
       <c r="B191" s="135"/>
       <c r="C191" s="135"/>
@@ -11601,7 +11601,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="192" spans="1:15" ht="15.75" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="192" spans="1:15" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A192" s="125"/>
       <c r="B192" s="135"/>
       <c r="C192" s="135"/>
@@ -11624,7 +11624,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="193" spans="1:15" ht="15.75" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="193" spans="1:15" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A193" s="125"/>
       <c r="B193" s="135"/>
       <c r="C193" s="135"/>
@@ -11647,7 +11647,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="194" spans="1:15" ht="15.75" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="194" spans="1:15" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A194" s="125"/>
       <c r="B194" s="135"/>
       <c r="C194" s="135"/>
@@ -11674,7 +11674,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="195" spans="1:15" ht="15.75" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="195" spans="1:15" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A195" s="125"/>
       <c r="B195" s="135"/>
       <c r="C195" s="135"/>
@@ -11695,7 +11695,7 @@
       <c r="N195" s="135"/>
       <c r="O195" s="138"/>
     </row>
-    <row r="196" spans="1:15" ht="15.75" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="196" spans="1:15" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A196" s="125"/>
       <c r="B196" s="135"/>
       <c r="C196" s="135"/>
@@ -11722,7 +11722,7 @@
         <v>436</v>
       </c>
     </row>
-    <row r="197" spans="1:15" ht="15.75" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="197" spans="1:15" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A197" s="125"/>
       <c r="B197" s="135"/>
       <c r="C197" s="135"/>
@@ -11739,7 +11739,7 @@
       <c r="N197" s="135"/>
       <c r="O197" s="138"/>
     </row>
-    <row r="198" spans="1:15" ht="15.75" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="198" spans="1:15" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A198" s="125"/>
       <c r="B198" s="135"/>
       <c r="C198" s="133" t="s">
@@ -11766,7 +11766,7 @@
         <v>10464</v>
       </c>
     </row>
-    <row r="199" spans="1:15" ht="15.75" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="199" spans="1:15" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A199" s="125"/>
       <c r="B199" s="135"/>
       <c r="C199" s="133"/>
@@ -11783,7 +11783,7 @@
       <c r="N199" s="135"/>
       <c r="O199" s="138"/>
     </row>
-    <row r="200" spans="1:15" ht="15.75" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="200" spans="1:15" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A200" s="125"/>
       <c r="B200" s="135"/>
       <c r="C200" s="135"/>
@@ -11800,7 +11800,7 @@
       <c r="N200" s="135"/>
       <c r="O200" s="138"/>
     </row>
-    <row r="201" spans="1:15" ht="15.75" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="201" spans="1:15" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A201" s="125"/>
       <c r="B201" s="135"/>
       <c r="C201" s="135"/>
@@ -11821,7 +11821,7 @@
       <c r="N201" s="135"/>
       <c r="O201" s="138"/>
     </row>
-    <row r="202" spans="1:15" ht="38.1" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="202" spans="1:15" ht="38.1" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A202" s="125"/>
       <c r="B202" s="247" t="s">
         <v>91</v>
@@ -11842,7 +11842,7 @@
       <c r="N202" s="247"/>
       <c r="O202" s="247"/>
     </row>
-    <row r="203" spans="1:15" ht="15" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="203" spans="1:15" ht="15" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A203" s="125"/>
       <c r="B203" s="126"/>
       <c r="C203" s="128"/>
@@ -11859,7 +11859,7 @@
       <c r="N203" s="128"/>
       <c r="O203" s="128"/>
     </row>
-    <row r="204" spans="1:15" ht="18.600000000000001" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="204" spans="1:15" ht="18.600000000000001" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A204" s="125"/>
       <c r="B204" s="248" t="s">
         <v>92</v>
@@ -11880,7 +11880,7 @@
       <c r="N204" s="248"/>
       <c r="O204" s="248"/>
     </row>
-    <row r="205" spans="1:15" ht="15" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="205" spans="1:15" ht="15" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A205" s="125"/>
       <c r="B205" s="131">
         <f>+'Folha de salarios'!A17</f>
@@ -11903,7 +11903,7 @@
       <c r="N205" s="132"/>
       <c r="O205" s="132"/>
     </row>
-    <row r="206" spans="1:15" ht="18.600000000000001" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="206" spans="1:15" ht="18.600000000000001" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A206" s="125"/>
       <c r="B206" s="133" t="s">
         <v>93</v>
@@ -11935,7 +11935,7 @@
       </c>
       <c r="O206" s="136"/>
     </row>
-    <row r="207" spans="1:15" ht="18.600000000000001" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="207" spans="1:15" ht="18.600000000000001" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A207" s="125"/>
       <c r="B207" s="133" t="s">
         <v>94</v>
@@ -11961,7 +11961,7 @@
       <c r="M207" s="135"/>
       <c r="O207" s="135"/>
     </row>
-    <row r="208" spans="1:15" ht="15.75" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="208" spans="1:15" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A208" s="125"/>
       <c r="B208" s="133" t="s">
         <v>95</v>
@@ -11988,7 +11988,7 @@
       <c r="N208" s="135"/>
       <c r="O208" s="135"/>
     </row>
-    <row r="209" spans="1:15" ht="15.75" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="209" spans="1:15" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A209" s="125"/>
       <c r="B209" s="133"/>
       <c r="C209" s="135"/>
@@ -12005,7 +12005,7 @@
       <c r="N209" s="135"/>
       <c r="O209" s="135"/>
     </row>
-    <row r="210" spans="1:15" ht="15.75" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="210" spans="1:15" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A210" s="125"/>
       <c r="B210" s="133" t="s">
         <v>96</v>
@@ -12032,7 +12032,7 @@
         <v>10900</v>
       </c>
     </row>
-    <row r="211" spans="1:15" ht="15.75" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="211" spans="1:15" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A211" s="125"/>
       <c r="B211" s="133" t="s">
         <v>97</v>
@@ -12059,7 +12059,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="212" spans="1:15" ht="15.75" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="212" spans="1:15" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A212" s="125"/>
       <c r="B212" s="133" t="s">
         <v>98</v>
@@ -12085,7 +12085,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="213" spans="1:15" ht="15.75" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="213" spans="1:15" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A213" s="125"/>
       <c r="B213" s="133" t="s">
         <v>99</v>
@@ -12112,7 +12112,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="214" spans="1:15" ht="15.75" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="214" spans="1:15" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A214" s="125"/>
       <c r="B214" s="135"/>
       <c r="C214" s="135"/>
@@ -12139,7 +12139,7 @@
         <v>10900</v>
       </c>
     </row>
-    <row r="215" spans="1:15" ht="15.75" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="215" spans="1:15" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A215" s="125"/>
       <c r="B215" s="135"/>
       <c r="C215" s="135"/>
@@ -12156,7 +12156,7 @@
       <c r="N215" s="135"/>
       <c r="O215" s="138"/>
     </row>
-    <row r="216" spans="1:15" ht="15.75" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="216" spans="1:15" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A216" s="125"/>
       <c r="B216" s="135"/>
       <c r="C216" s="133" t="s">
@@ -12176,7 +12176,7 @@
       <c r="N216" s="135"/>
       <c r="O216" s="138"/>
     </row>
-    <row r="217" spans="1:15" ht="15.75" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="217" spans="1:15" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A217" s="125"/>
       <c r="B217" s="135"/>
       <c r="C217" s="135"/>
@@ -12202,7 +12202,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="218" spans="1:15" ht="15.75" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="218" spans="1:15" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A218" s="125"/>
       <c r="B218" s="135"/>
       <c r="C218" s="135"/>
@@ -12228,7 +12228,7 @@
         <v>327</v>
       </c>
     </row>
-    <row r="219" spans="1:15" ht="15.75" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="219" spans="1:15" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A219" s="125"/>
       <c r="B219" s="135"/>
       <c r="C219" s="135"/>
@@ -12254,7 +12254,7 @@
         <v>109</v>
       </c>
     </row>
-    <row r="220" spans="1:15" ht="15.75" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="220" spans="1:15" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A220" s="125"/>
       <c r="B220" s="135"/>
       <c r="C220" s="135"/>
@@ -12277,7 +12277,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="221" spans="1:15" ht="15.75" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="221" spans="1:15" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A221" s="125"/>
       <c r="B221" s="135"/>
       <c r="C221" s="135"/>
@@ -12300,7 +12300,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="222" spans="1:15" ht="15.75" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="222" spans="1:15" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A222" s="125"/>
       <c r="B222" s="135"/>
       <c r="C222" s="135"/>
@@ -12323,7 +12323,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="223" spans="1:15" ht="15.75" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="223" spans="1:15" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A223" s="125"/>
       <c r="B223" s="135"/>
       <c r="C223" s="135"/>
@@ -12350,7 +12350,7 @@
         <v>5500</v>
       </c>
     </row>
-    <row r="224" spans="1:15" ht="15.75" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="224" spans="1:15" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A224" s="125"/>
       <c r="B224" s="135"/>
       <c r="C224" s="135"/>
@@ -12371,7 +12371,7 @@
       <c r="N224" s="135"/>
       <c r="O224" s="138"/>
     </row>
-    <row r="225" spans="1:15" ht="15.75" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="225" spans="1:15" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A225" s="125"/>
       <c r="B225" s="135"/>
       <c r="C225" s="135"/>
@@ -12398,7 +12398,7 @@
         <v>5936</v>
       </c>
     </row>
-    <row r="226" spans="1:15" ht="15.75" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="226" spans="1:15" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A226" s="125"/>
       <c r="B226" s="135"/>
       <c r="C226" s="135"/>
@@ -12415,7 +12415,7 @@
       <c r="N226" s="135"/>
       <c r="O226" s="138"/>
     </row>
-    <row r="227" spans="1:15" ht="15.75" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="227" spans="1:15" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A227" s="125"/>
       <c r="B227" s="135"/>
       <c r="C227" s="133" t="s">
@@ -12442,7 +12442,7 @@
         <v>4964</v>
       </c>
     </row>
-    <row r="228" spans="1:15" ht="15.75" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="228" spans="1:15" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A228" s="125"/>
       <c r="B228" s="135"/>
       <c r="C228" s="133"/>
@@ -12459,7 +12459,7 @@
       <c r="N228" s="135"/>
       <c r="O228" s="138"/>
     </row>
-    <row r="229" spans="1:15" ht="15.75" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="229" spans="1:15" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A229" s="125"/>
       <c r="B229" s="135"/>
       <c r="C229" s="135"/>
@@ -12476,7 +12476,7 @@
       <c r="N229" s="135"/>
       <c r="O229" s="138"/>
     </row>
-    <row r="230" spans="1:15" ht="15.75" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="230" spans="1:15" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A230" s="125"/>
       <c r="B230" s="135"/>
       <c r="C230" s="135"/>
@@ -12497,7 +12497,7 @@
       <c r="N230" s="135"/>
       <c r="O230" s="138"/>
     </row>
-    <row r="231" spans="1:15" ht="38.1" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="231" spans="1:15" ht="38.1" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A231" s="125"/>
       <c r="B231" s="247" t="s">
         <v>91</v>
@@ -12518,7 +12518,7 @@
       <c r="N231" s="247"/>
       <c r="O231" s="247"/>
     </row>
-    <row r="232" spans="1:15" ht="15" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="232" spans="1:15" ht="15" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A232" s="125"/>
       <c r="B232" s="126"/>
       <c r="C232" s="128"/>
@@ -12535,7 +12535,7 @@
       <c r="N232" s="128"/>
       <c r="O232" s="128"/>
     </row>
-    <row r="233" spans="1:15" ht="18.600000000000001" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="233" spans="1:15" ht="18.600000000000001" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A233" s="125"/>
       <c r="B233" s="248" t="s">
         <v>92</v>
@@ -12556,7 +12556,7 @@
       <c r="N233" s="248"/>
       <c r="O233" s="248"/>
     </row>
-    <row r="234" spans="1:15" ht="15" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="234" spans="1:15" ht="15" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A234" s="125"/>
       <c r="B234" s="131">
         <f>+'Folha de salarios'!A18</f>
@@ -12579,7 +12579,7 @@
       <c r="N234" s="132"/>
       <c r="O234" s="132"/>
     </row>
-    <row r="235" spans="1:15" ht="18.600000000000001" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="235" spans="1:15" ht="18.600000000000001" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A235" s="125"/>
       <c r="B235" s="133" t="s">
         <v>93</v>
@@ -12611,7 +12611,7 @@
       </c>
       <c r="O235" s="136"/>
     </row>
-    <row r="236" spans="1:15" ht="18.600000000000001" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="236" spans="1:15" ht="18.600000000000001" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A236" s="125"/>
       <c r="B236" s="133" t="s">
         <v>94</v>
@@ -12637,7 +12637,7 @@
       <c r="M236" s="135"/>
       <c r="O236" s="135"/>
     </row>
-    <row r="237" spans="1:15" ht="15.75" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="237" spans="1:15" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A237" s="125"/>
       <c r="B237" s="133" t="s">
         <v>95</v>
@@ -12663,7 +12663,7 @@
       <c r="N237" s="135"/>
       <c r="O237" s="135"/>
     </row>
-    <row r="238" spans="1:15" ht="15.75" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="238" spans="1:15" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A238" s="125"/>
       <c r="B238" s="133"/>
       <c r="C238" s="135"/>
@@ -12680,7 +12680,7 @@
       <c r="N238" s="135"/>
       <c r="O238" s="135"/>
     </row>
-    <row r="239" spans="1:15" ht="15.75" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="239" spans="1:15" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A239" s="125"/>
       <c r="B239" s="133" t="s">
         <v>96</v>
@@ -12707,7 +12707,7 @@
         <v>10955</v>
       </c>
     </row>
-    <row r="240" spans="1:15" ht="15.75" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="240" spans="1:15" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A240" s="125"/>
       <c r="B240" s="133" t="s">
         <v>97</v>
@@ -12734,7 +12734,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="241" spans="1:15" ht="15.75" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="241" spans="1:15" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A241" s="125"/>
       <c r="B241" s="133" t="s">
         <v>98</v>
@@ -12758,7 +12758,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="242" spans="1:15" ht="15.75" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="242" spans="1:15" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A242" s="125"/>
       <c r="B242" s="133" t="s">
         <v>99</v>
@@ -12784,7 +12784,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="243" spans="1:15" ht="15.75" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="243" spans="1:15" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A243" s="125"/>
       <c r="B243" s="135"/>
       <c r="C243" s="135"/>
@@ -12811,7 +12811,7 @@
         <v>10955</v>
       </c>
     </row>
-    <row r="244" spans="1:15" ht="15.75" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="244" spans="1:15" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A244" s="125"/>
       <c r="B244" s="135"/>
       <c r="C244" s="135"/>
@@ -12828,7 +12828,7 @@
       <c r="N244" s="135"/>
       <c r="O244" s="138"/>
     </row>
-    <row r="245" spans="1:15" ht="15.75" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="245" spans="1:15" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A245" s="125"/>
       <c r="B245" s="135"/>
       <c r="C245" s="133" t="s">
@@ -12848,7 +12848,7 @@
       <c r="M245" s="135"/>
       <c r="O245" s="138"/>
     </row>
-    <row r="246" spans="1:15" ht="15.75" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="246" spans="1:15" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A246" s="125"/>
       <c r="B246" s="135"/>
       <c r="C246" s="135"/>
@@ -12874,7 +12874,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="247" spans="1:15" ht="15.75" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="247" spans="1:15" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A247" s="125"/>
       <c r="B247" s="135"/>
       <c r="C247" s="135"/>
@@ -12900,7 +12900,7 @@
         <v>328.65</v>
       </c>
     </row>
-    <row r="248" spans="1:15" ht="15.75" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="248" spans="1:15" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A248" s="125"/>
       <c r="B248" s="135"/>
       <c r="C248" s="135"/>
@@ -12926,7 +12926,7 @@
         <v>109.55</v>
       </c>
     </row>
-    <row r="249" spans="1:15" ht="15.75" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="249" spans="1:15" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A249" s="125"/>
       <c r="B249" s="135"/>
       <c r="C249" s="135"/>
@@ -12949,7 +12949,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="250" spans="1:15" ht="15.75" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="250" spans="1:15" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A250" s="125"/>
       <c r="B250" s="135"/>
       <c r="C250" s="135"/>
@@ -12972,7 +12972,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="251" spans="1:15" ht="15.75" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="251" spans="1:15" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A251" s="125"/>
       <c r="B251" s="135"/>
       <c r="C251" s="135"/>
@@ -12995,7 +12995,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="252" spans="1:15" ht="15.75" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="252" spans="1:15" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A252" s="125"/>
       <c r="B252" s="135"/>
       <c r="C252" s="135"/>
@@ -13022,7 +13022,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="253" spans="1:15" ht="15.75" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="253" spans="1:15" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A253" s="125"/>
       <c r="B253" s="135"/>
       <c r="C253" s="135"/>
@@ -13048,7 +13048,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="254" spans="1:15" ht="15.75" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="254" spans="1:15" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A254" s="125"/>
       <c r="B254" s="135"/>
       <c r="C254" s="135"/>
@@ -13075,7 +13075,7 @@
         <v>438.2</v>
       </c>
     </row>
-    <row r="255" spans="1:15" ht="15.75" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="255" spans="1:15" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A255" s="125"/>
       <c r="B255" s="135"/>
       <c r="C255" s="135"/>
@@ -13092,7 +13092,7 @@
       <c r="N255" s="135"/>
       <c r="O255" s="138"/>
     </row>
-    <row r="256" spans="1:15" ht="15.75" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="256" spans="1:15" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A256" s="125"/>
       <c r="B256" s="135"/>
       <c r="C256" s="133" t="s">
@@ -13119,7 +13119,7 @@
         <v>10516.8</v>
       </c>
     </row>
-    <row r="257" spans="1:15" ht="15.75" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="257" spans="1:15" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A257" s="125"/>
       <c r="B257" s="135"/>
       <c r="C257" s="133"/>
@@ -13136,7 +13136,7 @@
       <c r="N257" s="135"/>
       <c r="O257" s="138"/>
     </row>
-    <row r="258" spans="1:15" ht="15.75" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="258" spans="1:15" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A258" s="125"/>
       <c r="B258" s="135"/>
       <c r="C258" s="135"/>
@@ -13153,7 +13153,7 @@
       <c r="N258" s="135"/>
       <c r="O258" s="138"/>
     </row>
-    <row r="259" spans="1:15" ht="15.75" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="259" spans="1:15" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A259" s="125"/>
       <c r="B259" s="135"/>
       <c r="C259" s="135"/>
@@ -13174,7 +13174,7 @@
       <c r="N259" s="135"/>
       <c r="O259" s="138"/>
     </row>
-    <row r="260" spans="1:15" ht="38.1" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="260" spans="1:15" ht="38.1" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A260" s="125"/>
       <c r="B260" s="247" t="s">
         <v>91</v>
@@ -13195,7 +13195,7 @@
       <c r="N260" s="247"/>
       <c r="O260" s="247"/>
     </row>
-    <row r="261" spans="1:15" ht="15" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="261" spans="1:15" ht="15" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A261" s="125"/>
       <c r="B261" s="126"/>
       <c r="C261" s="128"/>
@@ -13212,7 +13212,7 @@
       <c r="N261" s="128"/>
       <c r="O261" s="128"/>
     </row>
-    <row r="262" spans="1:15" ht="18.600000000000001" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="262" spans="1:15" ht="18.600000000000001" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A262" s="125"/>
       <c r="B262" s="248" t="s">
         <v>92</v>
@@ -13233,7 +13233,7 @@
       <c r="N262" s="248"/>
       <c r="O262" s="248"/>
     </row>
-    <row r="263" spans="1:15" ht="15" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="263" spans="1:15" ht="15" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A263" s="125"/>
       <c r="B263" s="131">
         <f>+'Folha de salarios'!A19</f>
@@ -13256,7 +13256,7 @@
       <c r="N263" s="132"/>
       <c r="O263" s="132"/>
     </row>
-    <row r="264" spans="1:15" ht="18.600000000000001" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="264" spans="1:15" ht="18.600000000000001" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A264" s="125"/>
       <c r="B264" s="133" t="s">
         <v>93</v>
@@ -13288,7 +13288,7 @@
       </c>
       <c r="O264" s="136"/>
     </row>
-    <row r="265" spans="1:15" ht="18.600000000000001" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="265" spans="1:15" ht="18.600000000000001" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A265" s="125"/>
       <c r="B265" s="133" t="s">
         <v>94</v>
@@ -13314,7 +13314,7 @@
       <c r="M265" s="135"/>
       <c r="O265" s="135"/>
     </row>
-    <row r="266" spans="1:15" ht="15.75" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="266" spans="1:15" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A266" s="125"/>
       <c r="B266" s="133" t="s">
         <v>95</v>
@@ -13341,7 +13341,7 @@
       <c r="N266" s="135"/>
       <c r="O266" s="135"/>
     </row>
-    <row r="267" spans="1:15" ht="15.75" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="267" spans="1:15" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A267" s="125"/>
       <c r="B267" s="133"/>
       <c r="C267" s="135"/>
@@ -13358,7 +13358,7 @@
       <c r="N267" s="135"/>
       <c r="O267" s="135"/>
     </row>
-    <row r="268" spans="1:15" ht="15.75" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="268" spans="1:15" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A268" s="125"/>
       <c r="B268" s="133" t="s">
         <v>96</v>
@@ -13385,7 +13385,7 @@
         <v>14824.000000000002</v>
       </c>
     </row>
-    <row r="269" spans="1:15" ht="15.75" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="269" spans="1:15" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A269" s="125"/>
       <c r="B269" s="133" t="s">
         <v>97</v>
@@ -13412,7 +13412,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="270" spans="1:15" ht="15.75" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="270" spans="1:15" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A270" s="125"/>
       <c r="B270" s="133" t="s">
         <v>98</v>
@@ -13438,7 +13438,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="271" spans="1:15" ht="15.75" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="271" spans="1:15" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A271" s="125"/>
       <c r="B271" s="133" t="s">
         <v>99</v>
@@ -13465,7 +13465,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="272" spans="1:15" ht="15.75" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="272" spans="1:15" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A272" s="125"/>
       <c r="B272" s="135"/>
       <c r="C272" s="135"/>
@@ -13492,7 +13492,7 @@
         <v>14824.000000000002</v>
       </c>
     </row>
-    <row r="273" spans="1:15" ht="15.75" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="273" spans="1:15" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A273" s="125"/>
       <c r="B273" s="135"/>
       <c r="C273" s="135"/>
@@ -13509,7 +13509,7 @@
       <c r="N273" s="135"/>
       <c r="O273" s="138"/>
     </row>
-    <row r="274" spans="1:15" ht="15.75" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="274" spans="1:15" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A274" s="125"/>
       <c r="B274" s="135"/>
       <c r="C274" s="133" t="s">
@@ -13529,7 +13529,7 @@
       <c r="M274" s="135"/>
       <c r="O274" s="138"/>
     </row>
-    <row r="275" spans="1:15" ht="15.75" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="275" spans="1:15" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A275" s="125"/>
       <c r="B275" s="135"/>
       <c r="C275" s="135"/>
@@ -13555,7 +13555,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="276" spans="1:15" ht="15.75" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="276" spans="1:15" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A276" s="125"/>
       <c r="B276" s="135"/>
       <c r="C276" s="135"/>
@@ -13581,7 +13581,7 @@
         <v>444.72</v>
       </c>
     </row>
-    <row r="277" spans="1:15" ht="15.75" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="277" spans="1:15" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A277" s="125"/>
       <c r="B277" s="135"/>
       <c r="C277" s="135"/>
@@ -13607,7 +13607,7 @@
         <v>148.24</v>
       </c>
     </row>
-    <row r="278" spans="1:15" ht="15.75" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="278" spans="1:15" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A278" s="125"/>
       <c r="B278" s="135"/>
       <c r="C278" s="135"/>
@@ -13630,7 +13630,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="279" spans="1:15" ht="15.75" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="279" spans="1:15" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A279" s="125"/>
       <c r="B279" s="135"/>
       <c r="C279" s="135"/>
@@ -13653,7 +13653,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="280" spans="1:15" ht="15.75" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="280" spans="1:15" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A280" s="125"/>
       <c r="B280" s="135"/>
       <c r="C280" s="135"/>
@@ -13676,7 +13676,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="281" spans="1:15" ht="15.75" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="281" spans="1:15" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A281" s="125"/>
       <c r="B281" s="135"/>
       <c r="C281" s="135"/>
@@ -13703,7 +13703,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="282" spans="1:15" ht="15.75" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="282" spans="1:15" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A282" s="125"/>
       <c r="B282" s="135"/>
       <c r="C282" s="135"/>
@@ -13727,7 +13727,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="283" spans="1:15" ht="15.75" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="283" spans="1:15" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A283" s="125"/>
       <c r="B283" s="135"/>
       <c r="C283" s="135"/>
@@ -13754,7 +13754,7 @@
         <v>592.96</v>
       </c>
     </row>
-    <row r="284" spans="1:15" ht="15.75" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="284" spans="1:15" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A284" s="125"/>
       <c r="B284" s="135"/>
       <c r="C284" s="135"/>
@@ -13771,7 +13771,7 @@
       <c r="N284" s="135"/>
       <c r="O284" s="138"/>
     </row>
-    <row r="285" spans="1:15" ht="15.75" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="285" spans="1:15" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A285" s="125"/>
       <c r="B285" s="135"/>
       <c r="C285" s="133" t="s">
@@ -13798,7 +13798,7 @@
         <v>14231.04</v>
       </c>
     </row>
-    <row r="286" spans="1:15" ht="15.75" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="286" spans="1:15" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A286" s="125"/>
       <c r="B286" s="135"/>
       <c r="C286" s="133"/>
@@ -13815,7 +13815,7 @@
       <c r="N286" s="135"/>
       <c r="O286" s="138"/>
     </row>
-    <row r="287" spans="1:15" ht="15.75" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="287" spans="1:15" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A287" s="125"/>
       <c r="B287" s="135"/>
       <c r="C287" s="135"/>
@@ -13832,7 +13832,7 @@
       <c r="N287" s="135"/>
       <c r="O287" s="138"/>
     </row>
-    <row r="288" spans="1:15" ht="15.75" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="288" spans="1:15" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A288" s="125"/>
       <c r="B288" s="135"/>
       <c r="C288" s="135"/>
@@ -13853,7 +13853,7 @@
       <c r="N288" s="135"/>
       <c r="O288" s="138"/>
     </row>
-    <row r="289" spans="1:15" ht="38.1" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="289" spans="1:15" ht="38.1" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A289" s="125"/>
       <c r="B289" s="247" t="s">
         <v>91</v>
@@ -13874,7 +13874,7 @@
       <c r="N289" s="247"/>
       <c r="O289" s="247"/>
     </row>
-    <row r="290" spans="1:15" ht="15" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="290" spans="1:15" ht="15" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A290" s="125"/>
       <c r="B290" s="126"/>
       <c r="C290" s="128"/>
@@ -13891,7 +13891,7 @@
       <c r="N290" s="128"/>
       <c r="O290" s="128"/>
     </row>
-    <row r="291" spans="1:15" ht="18.600000000000001" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="291" spans="1:15" ht="18.600000000000001" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A291" s="125"/>
       <c r="B291" s="248" t="s">
         <v>92</v>
@@ -13912,7 +13912,7 @@
       <c r="N291" s="248"/>
       <c r="O291" s="248"/>
     </row>
-    <row r="292" spans="1:15" ht="15" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="292" spans="1:15" ht="15" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A292" s="125"/>
       <c r="B292" s="131">
         <f>+B263+1</f>
@@ -13934,7 +13934,7 @@
       <c r="N292" s="132"/>
       <c r="O292" s="132"/>
     </row>
-    <row r="293" spans="1:15" ht="18.600000000000001" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="293" spans="1:15" ht="18.600000000000001" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A293" s="125"/>
       <c r="B293" s="133" t="s">
         <v>93</v>
@@ -13966,7 +13966,7 @@
       </c>
       <c r="O293" s="136"/>
     </row>
-    <row r="294" spans="1:15" ht="18.600000000000001" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="294" spans="1:15" ht="18.600000000000001" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A294" s="125"/>
       <c r="B294" s="133" t="s">
         <v>94</v>
@@ -13992,7 +13992,7 @@
       <c r="M294" s="135"/>
       <c r="O294" s="135"/>
     </row>
-    <row r="295" spans="1:15" ht="15.75" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="295" spans="1:15" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A295" s="125"/>
       <c r="B295" s="133" t="s">
         <v>95</v>
@@ -14019,7 +14019,7 @@
       <c r="N295" s="135"/>
       <c r="O295" s="135"/>
     </row>
-    <row r="296" spans="1:15" ht="15.75" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="296" spans="1:15" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A296" s="125"/>
       <c r="B296" s="133"/>
       <c r="C296" s="135"/>
@@ -14036,7 +14036,7 @@
       <c r="N296" s="135"/>
       <c r="O296" s="135"/>
     </row>
-    <row r="297" spans="1:15" ht="15.75" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="297" spans="1:15" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A297" s="125"/>
       <c r="B297" s="133" t="s">
         <v>96</v>
@@ -14063,7 +14063,7 @@
         <v>14170.000000000002</v>
       </c>
     </row>
-    <row r="298" spans="1:15" ht="15.75" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="298" spans="1:15" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A298" s="125"/>
       <c r="B298" s="133" t="s">
         <v>97</v>
@@ -14090,7 +14090,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="299" spans="1:15" ht="15.75" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="299" spans="1:15" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A299" s="125"/>
       <c r="B299" s="133" t="s">
         <v>98</v>
@@ -14116,7 +14116,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="300" spans="1:15" ht="15.75" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="300" spans="1:15" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A300" s="125"/>
       <c r="B300" s="133" t="s">
         <v>99</v>
@@ -14141,7 +14141,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="301" spans="1:15" ht="15.75" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="301" spans="1:15" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A301" s="125"/>
       <c r="B301" s="135"/>
       <c r="C301" s="135"/>
@@ -14168,7 +14168,7 @@
         <v>14170.000000000002</v>
       </c>
     </row>
-    <row r="302" spans="1:15" ht="15.75" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="302" spans="1:15" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A302" s="125"/>
       <c r="B302" s="135"/>
       <c r="C302" s="135"/>
@@ -14185,7 +14185,7 @@
       <c r="N302" s="135"/>
       <c r="O302" s="138"/>
     </row>
-    <row r="303" spans="1:15" ht="15.75" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="303" spans="1:15" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A303" s="125"/>
       <c r="B303" s="135"/>
       <c r="C303" s="133" t="s">
@@ -14205,7 +14205,7 @@
       <c r="M303" s="135"/>
       <c r="O303" s="138"/>
     </row>
-    <row r="304" spans="1:15" ht="15.75" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="304" spans="1:15" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A304" s="125"/>
       <c r="B304" s="135"/>
       <c r="C304" s="135"/>
@@ -14231,7 +14231,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="305" spans="1:15" ht="15.75" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="305" spans="1:15" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A305" s="125"/>
       <c r="B305" s="135"/>
       <c r="C305" s="135"/>
@@ -14257,7 +14257,7 @@
         <v>425.1</v>
       </c>
     </row>
-    <row r="306" spans="1:15" ht="15.75" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="306" spans="1:15" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A306" s="125"/>
       <c r="B306" s="135"/>
       <c r="C306" s="135"/>
@@ -14283,7 +14283,7 @@
         <v>141.70000000000002</v>
       </c>
     </row>
-    <row r="307" spans="1:15" ht="15.75" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="307" spans="1:15" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A307" s="125"/>
       <c r="B307" s="135"/>
       <c r="C307" s="135"/>
@@ -14306,7 +14306,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="308" spans="1:15" ht="15.75" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="308" spans="1:15" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A308" s="125"/>
       <c r="B308" s="135"/>
       <c r="C308" s="135"/>
@@ -14329,7 +14329,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="309" spans="1:15" ht="15.75" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="309" spans="1:15" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A309" s="125"/>
       <c r="B309" s="135"/>
       <c r="C309" s="135"/>
@@ -14352,7 +14352,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="310" spans="1:15" ht="15.75" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="310" spans="1:15" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A310" s="125"/>
       <c r="B310" s="135"/>
       <c r="C310" s="135"/>
@@ -14379,7 +14379,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="311" spans="1:15" ht="15.75" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="311" spans="1:15" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A311" s="125"/>
       <c r="B311" s="135"/>
       <c r="C311" s="135"/>
@@ -14403,7 +14403,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="312" spans="1:15" ht="15.75" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="312" spans="1:15" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A312" s="125"/>
       <c r="B312" s="135"/>
       <c r="C312" s="135"/>
@@ -14430,7 +14430,7 @@
         <v>566.80000000000007</v>
       </c>
     </row>
-    <row r="313" spans="1:15" ht="15.75" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="313" spans="1:15" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A313" s="125"/>
       <c r="B313" s="135"/>
       <c r="C313" s="135"/>
@@ -14447,7 +14447,7 @@
       <c r="N313" s="135"/>
       <c r="O313" s="138"/>
     </row>
-    <row r="314" spans="1:15" ht="15.75" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="314" spans="1:15" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A314" s="125"/>
       <c r="B314" s="135"/>
       <c r="C314" s="133" t="s">
@@ -14474,7 +14474,7 @@
         <v>13603.200000000003</v>
       </c>
     </row>
-    <row r="315" spans="1:15" ht="15.75" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="315" spans="1:15" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A315" s="125"/>
       <c r="B315" s="135"/>
       <c r="C315" s="133"/>
@@ -14491,7 +14491,7 @@
       <c r="N315" s="135"/>
       <c r="O315" s="138"/>
     </row>
-    <row r="316" spans="1:15" ht="15.75" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="316" spans="1:15" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A316" s="125"/>
       <c r="B316" s="135"/>
       <c r="C316" s="135"/>
@@ -14508,7 +14508,7 @@
       <c r="N316" s="135"/>
       <c r="O316" s="138"/>
     </row>
-    <row r="317" spans="1:15" ht="15.75" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="317" spans="1:15" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A317" s="125"/>
       <c r="B317" s="135"/>
       <c r="C317" s="135"/>
@@ -14529,7 +14529,7 @@
       <c r="N317" s="135"/>
       <c r="O317" s="138"/>
     </row>
-    <row r="318" spans="1:15" ht="38.1" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="318" spans="1:15" ht="38.1" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A318" s="125"/>
       <c r="B318" s="247" t="s">
         <v>91</v>
@@ -14550,7 +14550,7 @@
       <c r="N318" s="247"/>
       <c r="O318" s="247"/>
     </row>
-    <row r="319" spans="1:15" ht="15" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="319" spans="1:15" ht="15" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A319" s="125"/>
       <c r="B319" s="126"/>
       <c r="C319" s="128"/>
@@ -14567,7 +14567,7 @@
       <c r="N319" s="128"/>
       <c r="O319" s="128"/>
     </row>
-    <row r="320" spans="1:15" ht="18.600000000000001" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="320" spans="1:15" ht="18.600000000000001" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A320" s="125"/>
       <c r="B320" s="248" t="s">
         <v>92</v>
@@ -14588,7 +14588,7 @@
       <c r="N320" s="248"/>
       <c r="O320" s="248"/>
     </row>
-    <row r="321" spans="1:15" ht="15" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="321" spans="1:15" ht="15" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A321" s="125"/>
       <c r="B321" s="131">
         <f>+B292+1</f>
@@ -14610,7 +14610,7 @@
       <c r="N321" s="132"/>
       <c r="O321" s="132"/>
     </row>
-    <row r="322" spans="1:15" ht="18.600000000000001" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="322" spans="1:15" ht="18.600000000000001" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A322" s="125"/>
       <c r="B322" s="133" t="s">
         <v>93</v>
@@ -14642,7 +14642,7 @@
       </c>
       <c r="O322" s="136"/>
     </row>
-    <row r="323" spans="1:15" ht="18.600000000000001" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="323" spans="1:15" ht="18.600000000000001" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A323" s="125"/>
       <c r="B323" s="133" t="s">
         <v>94</v>
@@ -14668,7 +14668,7 @@
       <c r="M323" s="135"/>
       <c r="O323" s="135"/>
     </row>
-    <row r="324" spans="1:15" ht="15.75" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="324" spans="1:15" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A324" s="125"/>
       <c r="B324" s="133" t="s">
         <v>95</v>
@@ -14695,7 +14695,7 @@
       <c r="N324" s="135"/>
       <c r="O324" s="135"/>
     </row>
-    <row r="325" spans="1:15" ht="15.75" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="325" spans="1:15" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A325" s="125"/>
       <c r="B325" s="133"/>
       <c r="C325" s="135"/>
@@ -14712,7 +14712,7 @@
       <c r="N325" s="135"/>
       <c r="O325" s="135"/>
     </row>
-    <row r="326" spans="1:15" ht="15.75" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="326" spans="1:15" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A326" s="125"/>
       <c r="B326" s="133" t="s">
         <v>96</v>
@@ -14739,7 +14739,7 @@
         <v>14879.000000000002</v>
       </c>
     </row>
-    <row r="327" spans="1:15" ht="15.75" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="327" spans="1:15" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A327" s="125"/>
       <c r="B327" s="133" t="s">
         <v>97</v>
@@ -14766,7 +14766,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="328" spans="1:15" ht="15.75" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="328" spans="1:15" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A328" s="125"/>
       <c r="B328" s="133" t="s">
         <v>98</v>
@@ -14792,7 +14792,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="329" spans="1:15" ht="15.75" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="329" spans="1:15" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A329" s="125"/>
       <c r="B329" s="133" t="s">
         <v>99</v>
@@ -14817,7 +14817,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="330" spans="1:15" ht="15.75" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="330" spans="1:15" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A330" s="125"/>
       <c r="B330" s="135"/>
       <c r="C330" s="135"/>
@@ -14844,7 +14844,7 @@
         <v>14879.000000000002</v>
       </c>
     </row>
-    <row r="331" spans="1:15" ht="15.75" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="331" spans="1:15" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A331" s="125"/>
       <c r="B331" s="135"/>
       <c r="C331" s="135"/>
@@ -14861,7 +14861,7 @@
       <c r="N331" s="135"/>
       <c r="O331" s="138"/>
     </row>
-    <row r="332" spans="1:15" ht="15.75" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="332" spans="1:15" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A332" s="125"/>
       <c r="B332" s="135"/>
       <c r="C332" s="133" t="s">
@@ -14881,7 +14881,7 @@
       <c r="M332" s="135"/>
       <c r="O332" s="138"/>
     </row>
-    <row r="333" spans="1:15" ht="15.75" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="333" spans="1:15" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A333" s="125"/>
       <c r="B333" s="135"/>
       <c r="C333" s="135"/>
@@ -14907,7 +14907,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="334" spans="1:15" ht="15.75" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="334" spans="1:15" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A334" s="125"/>
       <c r="B334" s="135"/>
       <c r="C334" s="135"/>
@@ -14933,7 +14933,7 @@
         <v>446.37000000000006</v>
       </c>
     </row>
-    <row r="335" spans="1:15" ht="15.75" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="335" spans="1:15" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A335" s="125"/>
       <c r="B335" s="135"/>
       <c r="C335" s="135"/>
@@ -14959,7 +14959,7 @@
         <v>148.79000000000002</v>
       </c>
     </row>
-    <row r="336" spans="1:15" ht="15.75" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="336" spans="1:15" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A336" s="125"/>
       <c r="B336" s="135"/>
       <c r="C336" s="135"/>
@@ -14982,7 +14982,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="337" spans="1:15" ht="15.75" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="337" spans="1:15" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A337" s="125"/>
       <c r="B337" s="135"/>
       <c r="C337" s="135"/>
@@ -15005,7 +15005,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="338" spans="1:15" ht="15.75" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="338" spans="1:15" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A338" s="125"/>
       <c r="B338" s="135"/>
       <c r="C338" s="135"/>
@@ -15028,7 +15028,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="339" spans="1:15" ht="15.75" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="339" spans="1:15" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A339" s="125"/>
       <c r="B339" s="135"/>
       <c r="C339" s="135"/>
@@ -15055,7 +15055,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="340" spans="1:15" ht="15.75" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="340" spans="1:15" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A340" s="125"/>
       <c r="B340" s="135"/>
       <c r="C340" s="135"/>
@@ -15079,7 +15079,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="341" spans="1:15" ht="15.75" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="341" spans="1:15" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A341" s="125"/>
       <c r="B341" s="135"/>
       <c r="C341" s="135"/>
@@ -15106,7 +15106,7 @@
         <v>595.16000000000008</v>
       </c>
     </row>
-    <row r="342" spans="1:15" ht="15.75" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="342" spans="1:15" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A342" s="125"/>
       <c r="B342" s="135"/>
       <c r="C342" s="135"/>
@@ -15123,7 +15123,7 @@
       <c r="N342" s="135"/>
       <c r="O342" s="138"/>
     </row>
-    <row r="343" spans="1:15" ht="15.75" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="343" spans="1:15" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A343" s="125"/>
       <c r="B343" s="135"/>
       <c r="C343" s="133" t="s">
@@ -15150,7 +15150,7 @@
         <v>14283.840000000002</v>
       </c>
     </row>
-    <row r="344" spans="1:15" ht="15.75" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="344" spans="1:15" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A344" s="125"/>
       <c r="B344" s="135"/>
       <c r="C344" s="133"/>
@@ -15167,7 +15167,7 @@
       <c r="N344" s="135"/>
       <c r="O344" s="138"/>
     </row>
-    <row r="345" spans="1:15" ht="15.75" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="345" spans="1:15" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A345" s="125"/>
       <c r="B345" s="135"/>
       <c r="C345" s="135"/>
@@ -15184,7 +15184,7 @@
       <c r="N345" s="135"/>
       <c r="O345" s="138"/>
     </row>
-    <row r="346" spans="1:15" ht="15.75" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="346" spans="1:15" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A346" s="125"/>
       <c r="B346" s="135"/>
       <c r="C346" s="135"/>
@@ -15205,7 +15205,7 @@
       <c r="N346" s="135"/>
       <c r="O346" s="138"/>
     </row>
-    <row r="347" spans="1:15" ht="38.1" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="347" spans="1:15" ht="38.1" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A347" s="125"/>
       <c r="B347" s="247" t="s">
         <v>91</v>
@@ -15226,7 +15226,7 @@
       <c r="N347" s="247"/>
       <c r="O347" s="247"/>
     </row>
-    <row r="348" spans="1:15" ht="15" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="348" spans="1:15" ht="15" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A348" s="125"/>
       <c r="B348" s="126"/>
       <c r="C348" s="128"/>
@@ -15243,7 +15243,7 @@
       <c r="N348" s="128"/>
       <c r="O348" s="128"/>
     </row>
-    <row r="349" spans="1:15" ht="18.600000000000001" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="349" spans="1:15" ht="18.600000000000001" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A349" s="125"/>
       <c r="B349" s="248" t="s">
         <v>92</v>
@@ -15264,7 +15264,7 @@
       <c r="N349" s="248"/>
       <c r="O349" s="248"/>
     </row>
-    <row r="350" spans="1:15" ht="15" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="350" spans="1:15" ht="15" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A350" s="125"/>
       <c r="B350" s="131">
         <f>+B321+1</f>
@@ -15287,7 +15287,7 @@
       <c r="N350" s="132"/>
       <c r="O350" s="132"/>
     </row>
-    <row r="351" spans="1:15" ht="18.600000000000001" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="351" spans="1:15" ht="18.600000000000001" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A351" s="125"/>
       <c r="B351" s="133" t="s">
         <v>93</v>
@@ -15319,7 +15319,7 @@
       </c>
       <c r="O351" s="136"/>
     </row>
-    <row r="352" spans="1:15" ht="18.600000000000001" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="352" spans="1:15" ht="18.600000000000001" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A352" s="125"/>
       <c r="B352" s="133" t="s">
         <v>94</v>
@@ -15345,7 +15345,7 @@
       <c r="M352" s="135"/>
       <c r="O352" s="135"/>
     </row>
-    <row r="353" spans="1:15" ht="15.75" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="353" spans="1:15" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A353" s="125"/>
       <c r="B353" s="133" t="s">
         <v>95</v>
@@ -15372,7 +15372,7 @@
       <c r="N353" s="135"/>
       <c r="O353" s="135"/>
     </row>
-    <row r="354" spans="1:15" ht="15.75" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="354" spans="1:15" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A354" s="125"/>
       <c r="B354" s="133"/>
       <c r="C354" s="135"/>
@@ -15389,7 +15389,7 @@
       <c r="N354" s="135"/>
       <c r="O354" s="135"/>
     </row>
-    <row r="355" spans="1:15" ht="15.75" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="355" spans="1:15" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A355" s="125"/>
       <c r="B355" s="133" t="s">
         <v>96</v>
@@ -15416,7 +15416,7 @@
         <v>10955</v>
       </c>
     </row>
-    <row r="356" spans="1:15" ht="15.75" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="356" spans="1:15" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A356" s="125"/>
       <c r="B356" s="133" t="s">
         <v>97</v>
@@ -15443,7 +15443,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="357" spans="1:15" ht="15.75" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="357" spans="1:15" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A357" s="125"/>
       <c r="B357" s="133" t="s">
         <v>98</v>
@@ -15469,7 +15469,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="358" spans="1:15" ht="15.75" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="358" spans="1:15" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A358" s="125"/>
       <c r="B358" s="133" t="s">
         <v>99</v>
@@ -15495,7 +15495,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="359" spans="1:15" ht="15.75" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="359" spans="1:15" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A359" s="125"/>
       <c r="B359" s="135"/>
       <c r="C359" s="135"/>
@@ -15522,7 +15522,7 @@
         <v>10955</v>
       </c>
     </row>
-    <row r="360" spans="1:15" ht="15.75" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="360" spans="1:15" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A360" s="125"/>
       <c r="B360" s="135"/>
       <c r="C360" s="135"/>
@@ -15539,7 +15539,7 @@
       <c r="N360" s="135"/>
       <c r="O360" s="138"/>
     </row>
-    <row r="361" spans="1:15" ht="15.75" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="361" spans="1:15" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A361" s="125"/>
       <c r="B361" s="135"/>
       <c r="C361" s="133" t="s">
@@ -15560,7 +15560,7 @@
       <c r="N361" s="135"/>
       <c r="O361" s="138"/>
     </row>
-    <row r="362" spans="1:15" ht="15.75" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="362" spans="1:15" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A362" s="125"/>
       <c r="B362" s="135"/>
       <c r="C362" s="135"/>
@@ -15587,7 +15587,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="363" spans="1:15" ht="15.75" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="363" spans="1:15" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A363" s="125"/>
       <c r="B363" s="135"/>
       <c r="C363" s="135"/>
@@ -15614,7 +15614,7 @@
         <v>328.65</v>
       </c>
     </row>
-    <row r="364" spans="1:15" ht="15.75" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="364" spans="1:15" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A364" s="125"/>
       <c r="B364" s="135"/>
       <c r="C364" s="135"/>
@@ -15641,7 +15641,7 @@
         <v>109.55</v>
       </c>
     </row>
-    <row r="365" spans="1:15" ht="15.75" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="365" spans="1:15" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A365" s="125"/>
       <c r="B365" s="135"/>
       <c r="C365" s="135"/>
@@ -15665,7 +15665,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="366" spans="1:15" ht="15.75" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="366" spans="1:15" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A366" s="125"/>
       <c r="B366" s="135"/>
       <c r="C366" s="135"/>
@@ -15689,7 +15689,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="367" spans="1:15" ht="15.75" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="367" spans="1:15" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A367" s="125"/>
       <c r="B367" s="135"/>
       <c r="C367" s="135"/>
@@ -15713,7 +15713,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="368" spans="1:15" ht="15.75" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="368" spans="1:15" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A368" s="125"/>
       <c r="B368" s="135"/>
       <c r="C368" s="135"/>
@@ -15740,7 +15740,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="369" spans="1:15" ht="15.75" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="369" spans="1:15" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A369" s="125"/>
       <c r="B369" s="135"/>
       <c r="C369" s="135"/>
@@ -15766,7 +15766,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="370" spans="1:15" ht="15.75" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="370" spans="1:15" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A370" s="125"/>
       <c r="B370" s="135"/>
       <c r="C370" s="135"/>
@@ -15793,7 +15793,7 @@
         <v>438.2</v>
       </c>
     </row>
-    <row r="371" spans="1:15" ht="15.75" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="371" spans="1:15" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A371" s="125"/>
       <c r="B371" s="135"/>
       <c r="C371" s="135"/>
@@ -15810,7 +15810,7 @@
       <c r="N371" s="135"/>
       <c r="O371" s="138"/>
     </row>
-    <row r="372" spans="1:15" ht="15.75" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="372" spans="1:15" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A372" s="125"/>
       <c r="B372" s="135"/>
       <c r="C372" s="133" t="s">
@@ -15837,7 +15837,7 @@
         <v>10516.8</v>
       </c>
     </row>
-    <row r="373" spans="1:15" ht="15.75" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="373" spans="1:15" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A373" s="125"/>
       <c r="B373" s="135"/>
       <c r="C373" s="133"/>
@@ -15854,7 +15854,7 @@
       <c r="N373" s="135"/>
       <c r="O373" s="138"/>
     </row>
-    <row r="374" spans="1:15" ht="15.75" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="374" spans="1:15" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A374" s="125"/>
       <c r="B374" s="135"/>
       <c r="C374" s="135"/>
@@ -15871,7 +15871,7 @@
       <c r="N374" s="135"/>
       <c r="O374" s="138"/>
     </row>
-    <row r="375" spans="1:15" ht="15.75" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="375" spans="1:15" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A375" s="125"/>
       <c r="B375" s="135"/>
       <c r="C375" s="135"/>
@@ -15892,7 +15892,7 @@
       <c r="N375" s="135"/>
       <c r="O375" s="138"/>
     </row>
-    <row r="376" spans="1:15" ht="38.1" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="376" spans="1:15" ht="38.1" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A376" s="125"/>
       <c r="B376" s="247" t="s">
         <v>91</v>
@@ -15913,7 +15913,7 @@
       <c r="N376" s="247"/>
       <c r="O376" s="247"/>
     </row>
-    <row r="377" spans="1:15" ht="15" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="377" spans="1:15" ht="15" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A377" s="125"/>
       <c r="B377" s="126"/>
       <c r="C377" s="128"/>
@@ -15930,7 +15930,7 @@
       <c r="N377" s="128"/>
       <c r="O377" s="128"/>
     </row>
-    <row r="378" spans="1:15" ht="18.600000000000001" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="378" spans="1:15" ht="18.600000000000001" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A378" s="125"/>
       <c r="B378" s="248" t="s">
         <v>92</v>
@@ -15951,7 +15951,7 @@
       <c r="N378" s="248"/>
       <c r="O378" s="248"/>
     </row>
-    <row r="379" spans="1:15" ht="15" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="379" spans="1:15" ht="15" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A379" s="125"/>
       <c r="B379" s="131">
         <f>+B350+1</f>
@@ -15974,7 +15974,7 @@
       <c r="N379" s="132"/>
       <c r="O379" s="132"/>
     </row>
-    <row r="380" spans="1:15" ht="18.600000000000001" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="380" spans="1:15" ht="18.600000000000001" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A380" s="125"/>
       <c r="B380" s="133" t="s">
         <v>93</v>
@@ -16006,7 +16006,7 @@
       </c>
       <c r="O380" s="136"/>
     </row>
-    <row r="381" spans="1:15" ht="18.600000000000001" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="381" spans="1:15" ht="18.600000000000001" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A381" s="125"/>
       <c r="B381" s="133" t="s">
         <v>94</v>
@@ -16032,7 +16032,7 @@
       <c r="M381" s="135"/>
       <c r="O381" s="135"/>
     </row>
-    <row r="382" spans="1:15" ht="15.75" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="382" spans="1:15" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A382" s="125"/>
       <c r="B382" s="133" t="s">
         <v>95</v>
@@ -16056,7 +16056,7 @@
       <c r="N382" s="135"/>
       <c r="O382" s="135"/>
     </row>
-    <row r="383" spans="1:15" ht="15.75" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="383" spans="1:15" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A383" s="125"/>
       <c r="B383" s="133"/>
       <c r="C383" s="135"/>
@@ -16073,7 +16073,7 @@
       <c r="N383" s="135"/>
       <c r="O383" s="135"/>
     </row>
-    <row r="384" spans="1:15" ht="15.75" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="384" spans="1:15" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A384" s="125"/>
       <c r="B384" s="133" t="s">
         <v>96</v>
@@ -16100,7 +16100,7 @@
         <v>16350.000000000004</v>
       </c>
     </row>
-    <row r="385" spans="1:15" ht="15.75" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="385" spans="1:15" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A385" s="125"/>
       <c r="B385" s="133" t="s">
         <v>97</v>
@@ -16127,7 +16127,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="386" spans="1:15" ht="15.75" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="386" spans="1:15" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A386" s="125"/>
       <c r="B386" s="133" t="s">
         <v>98</v>
@@ -16153,7 +16153,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="387" spans="1:15" ht="15.75" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="387" spans="1:15" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A387" s="125"/>
       <c r="B387" s="133" t="s">
         <v>99</v>
@@ -16179,7 +16179,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="388" spans="1:15" ht="15.75" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="388" spans="1:15" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A388" s="125"/>
       <c r="B388" s="135"/>
       <c r="C388" s="135"/>
@@ -16206,7 +16206,7 @@
         <v>16350.000000000004</v>
       </c>
     </row>
-    <row r="389" spans="1:15" ht="15.75" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="389" spans="1:15" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A389" s="125"/>
       <c r="B389" s="135"/>
       <c r="C389" s="135"/>
@@ -16223,7 +16223,7 @@
       <c r="N389" s="135"/>
       <c r="O389" s="138"/>
     </row>
-    <row r="390" spans="1:15" ht="15.75" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="390" spans="1:15" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A390" s="125"/>
       <c r="B390" s="135"/>
       <c r="C390" s="133" t="s">
@@ -16243,7 +16243,7 @@
       <c r="N390" s="135"/>
       <c r="O390" s="138"/>
     </row>
-    <row r="391" spans="1:15" ht="15.75" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="391" spans="1:15" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A391" s="125"/>
       <c r="B391" s="135"/>
       <c r="C391" s="135"/>
@@ -16269,7 +16269,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="392" spans="1:15" ht="15.75" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="392" spans="1:15" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A392" s="125"/>
       <c r="B392" s="135"/>
       <c r="C392" s="135"/>
@@ -16295,7 +16295,7 @@
         <v>490.50000000000011</v>
       </c>
     </row>
-    <row r="393" spans="1:15" ht="15.75" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="393" spans="1:15" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A393" s="125"/>
       <c r="B393" s="135"/>
       <c r="C393" s="135"/>
@@ -16321,7 +16321,7 @@
         <v>163.50000000000003</v>
       </c>
     </row>
-    <row r="394" spans="1:15" ht="15.75" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="394" spans="1:15" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A394" s="125"/>
       <c r="B394" s="135"/>
       <c r="C394" s="135"/>
@@ -16344,7 +16344,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="395" spans="1:15" ht="15.75" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="395" spans="1:15" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A395" s="125"/>
       <c r="B395" s="135"/>
       <c r="C395" s="135"/>
@@ -16367,7 +16367,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="396" spans="1:15" ht="15.75" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="396" spans="1:15" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A396" s="125"/>
       <c r="B396" s="135"/>
       <c r="C396" s="135"/>
@@ -16390,7 +16390,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="397" spans="1:15" ht="15.75" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="397" spans="1:15" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A397" s="125"/>
       <c r="B397" s="135"/>
       <c r="C397" s="135"/>
@@ -16417,7 +16417,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="398" spans="1:15" ht="15.75" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="398" spans="1:15" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A398" s="125"/>
       <c r="B398" s="135"/>
       <c r="C398" s="135"/>
@@ -16443,7 +16443,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="399" spans="1:15" ht="15.75" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="399" spans="1:15" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A399" s="125"/>
       <c r="B399" s="135"/>
       <c r="C399" s="135"/>
@@ -16470,7 +16470,7 @@
         <v>654.00000000000011</v>
       </c>
     </row>
-    <row r="400" spans="1:15" ht="15.75" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="400" spans="1:15" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A400" s="125"/>
       <c r="B400" s="135"/>
       <c r="C400" s="135"/>
@@ -16487,7 +16487,7 @@
       <c r="N400" s="135"/>
       <c r="O400" s="138"/>
     </row>
-    <row r="401" spans="1:15" ht="15.75" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="401" spans="1:15" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A401" s="125"/>
       <c r="B401" s="135"/>
       <c r="C401" s="133" t="s">
@@ -16514,7 +16514,7 @@
         <v>15696.000000000004</v>
       </c>
     </row>
-    <row r="402" spans="1:15" ht="15.75" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="402" spans="1:15" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A402" s="125"/>
       <c r="B402" s="135"/>
       <c r="C402" s="133"/>
@@ -16531,7 +16531,7 @@
       <c r="N402" s="135"/>
       <c r="O402" s="138"/>
     </row>
-    <row r="403" spans="1:15" ht="15.75" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="403" spans="1:15" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A403" s="125"/>
       <c r="B403" s="135"/>
       <c r="C403" s="135"/>
@@ -16548,7 +16548,7 @@
       <c r="N403" s="135"/>
       <c r="O403" s="138"/>
     </row>
-    <row r="404" spans="1:15" ht="15.75" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="404" spans="1:15" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A404" s="125"/>
       <c r="B404" s="135"/>
       <c r="C404" s="135"/>
@@ -16569,7 +16569,7 @@
       <c r="N404" s="135"/>
       <c r="O404" s="138"/>
     </row>
-    <row r="405" spans="1:15" ht="38.1" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="405" spans="1:15" ht="38.1" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A405" s="125"/>
       <c r="B405" s="247" t="s">
         <v>91</v>
@@ -16590,7 +16590,7 @@
       <c r="N405" s="247"/>
       <c r="O405" s="247"/>
     </row>
-    <row r="406" spans="1:15" ht="15" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="406" spans="1:15" ht="15" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A406" s="125"/>
       <c r="B406" s="126"/>
       <c r="C406" s="128"/>
@@ -16607,7 +16607,7 @@
       <c r="N406" s="128"/>
       <c r="O406" s="128"/>
     </row>
-    <row r="407" spans="1:15" ht="18.600000000000001" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="407" spans="1:15" ht="18.600000000000001" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A407" s="125"/>
       <c r="B407" s="248" t="s">
         <v>92</v>
@@ -16628,7 +16628,7 @@
       <c r="N407" s="248"/>
       <c r="O407" s="248"/>
     </row>
-    <row r="408" spans="1:15" ht="15" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="408" spans="1:15" ht="15" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A408" s="125"/>
       <c r="B408" s="131">
         <f>+B379+1</f>
@@ -16651,7 +16651,7 @@
       <c r="N408" s="132"/>
       <c r="O408" s="132"/>
     </row>
-    <row r="409" spans="1:15" ht="18.600000000000001" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="409" spans="1:15" ht="18.600000000000001" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A409" s="125"/>
       <c r="B409" s="133" t="s">
         <v>93</v>
@@ -16683,7 +16683,7 @@
       </c>
       <c r="O409" s="136"/>
     </row>
-    <row r="410" spans="1:15" ht="18.600000000000001" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="410" spans="1:15" ht="18.600000000000001" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A410" s="125"/>
       <c r="B410" s="133" t="s">
         <v>94</v>
@@ -16709,7 +16709,7 @@
       <c r="M410" s="135"/>
       <c r="O410" s="135"/>
     </row>
-    <row r="411" spans="1:15" ht="15.75" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="411" spans="1:15" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A411" s="125"/>
       <c r="B411" s="133" t="s">
         <v>95</v>
@@ -16736,7 +16736,7 @@
       <c r="N411" s="135"/>
       <c r="O411" s="135"/>
     </row>
-    <row r="412" spans="1:15" ht="15.75" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="412" spans="1:15" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A412" s="125"/>
       <c r="B412" s="133"/>
       <c r="C412" s="135"/>
@@ -16753,7 +16753,7 @@
       <c r="N412" s="135"/>
       <c r="O412" s="135"/>
     </row>
-    <row r="413" spans="1:15" ht="15.75" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="413" spans="1:15" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A413" s="125"/>
       <c r="B413" s="133" t="s">
         <v>96</v>
@@ -16780,7 +16780,7 @@
         <v>16350.000000000004</v>
       </c>
     </row>
-    <row r="414" spans="1:15" ht="15.75" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="414" spans="1:15" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A414" s="125"/>
       <c r="B414" s="133" t="s">
         <v>97</v>
@@ -16807,7 +16807,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="415" spans="1:15" ht="15.75" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="415" spans="1:15" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A415" s="125"/>
       <c r="B415" s="133" t="s">
         <v>98</v>
@@ -16833,7 +16833,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="416" spans="1:15" ht="15.75" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="416" spans="1:15" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A416" s="125"/>
       <c r="B416" s="133" t="s">
         <v>99</v>
@@ -16860,7 +16860,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="417" spans="1:15" ht="15.75" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="417" spans="1:15" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A417" s="125"/>
       <c r="B417" s="135"/>
       <c r="C417" s="135"/>
@@ -16887,7 +16887,7 @@
         <v>16350.000000000004</v>
       </c>
     </row>
-    <row r="418" spans="1:15" ht="15.75" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="418" spans="1:15" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A418" s="125"/>
       <c r="B418" s="135"/>
       <c r="C418" s="135"/>
@@ -16904,7 +16904,7 @@
       <c r="N418" s="135"/>
       <c r="O418" s="138"/>
     </row>
-    <row r="419" spans="1:15" ht="15.75" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="419" spans="1:15" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A419" s="125"/>
       <c r="B419" s="135"/>
       <c r="C419" s="133" t="s">
@@ -16924,7 +16924,7 @@
       <c r="M419" s="135"/>
       <c r="O419" s="138"/>
     </row>
-    <row r="420" spans="1:15" ht="15.75" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="420" spans="1:15" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A420" s="125"/>
       <c r="B420" s="135"/>
       <c r="C420" s="135"/>
@@ -16950,7 +16950,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="421" spans="1:15" ht="15.75" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="421" spans="1:15" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A421" s="125"/>
       <c r="B421" s="135"/>
       <c r="C421" s="135"/>
@@ -16976,7 +16976,7 @@
         <v>490.50000000000011</v>
       </c>
     </row>
-    <row r="422" spans="1:15" ht="15.75" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="422" spans="1:15" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A422" s="125"/>
       <c r="B422" s="135"/>
       <c r="C422" s="135"/>
@@ -17002,7 +17002,7 @@
         <v>163.50000000000003</v>
       </c>
     </row>
-    <row r="423" spans="1:15" ht="15.75" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="423" spans="1:15" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A423" s="125"/>
       <c r="B423" s="135"/>
       <c r="C423" s="135"/>
@@ -17025,7 +17025,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="424" spans="1:15" ht="15.75" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="424" spans="1:15" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A424" s="125"/>
       <c r="B424" s="135"/>
       <c r="C424" s="135"/>
@@ -17048,7 +17048,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="425" spans="1:15" ht="15.75" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="425" spans="1:15" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A425" s="125"/>
       <c r="B425" s="135"/>
       <c r="C425" s="135"/>
@@ -17071,7 +17071,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="426" spans="1:15" ht="15.75" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="426" spans="1:15" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A426" s="125"/>
       <c r="B426" s="135"/>
       <c r="C426" s="135"/>
@@ -17098,7 +17098,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="427" spans="1:15" ht="15.75" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="427" spans="1:15" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A427" s="125"/>
       <c r="B427" s="135"/>
       <c r="C427" s="135"/>
@@ -17124,7 +17124,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="428" spans="1:15" ht="15.75" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="428" spans="1:15" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A428" s="125"/>
       <c r="B428" s="135"/>
       <c r="C428" s="135"/>
@@ -17151,7 +17151,7 @@
         <v>654.00000000000011</v>
       </c>
     </row>
-    <row r="429" spans="1:15" ht="15.75" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="429" spans="1:15" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A429" s="125"/>
       <c r="B429" s="135"/>
       <c r="C429" s="135"/>
@@ -17168,7 +17168,7 @@
       <c r="N429" s="135"/>
       <c r="O429" s="138"/>
     </row>
-    <row r="430" spans="1:15" ht="15.75" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="430" spans="1:15" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A430" s="125"/>
       <c r="B430" s="135"/>
       <c r="C430" s="133" t="s">
@@ -17195,7 +17195,7 @@
         <v>15696.000000000004</v>
       </c>
     </row>
-    <row r="431" spans="1:15" ht="15.75" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="431" spans="1:15" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A431" s="125"/>
       <c r="B431" s="135"/>
       <c r="C431" s="133"/>
@@ -17212,7 +17212,7 @@
       <c r="N431" s="135"/>
       <c r="O431" s="138"/>
     </row>
-    <row r="432" spans="1:15" ht="15.75" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="432" spans="1:15" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A432" s="125"/>
       <c r="B432" s="135"/>
       <c r="C432" s="135"/>
@@ -17229,7 +17229,7 @@
       <c r="N432" s="135"/>
       <c r="O432" s="138"/>
     </row>
-    <row r="433" spans="1:15" ht="15.75" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="433" spans="1:15" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A433" s="125"/>
       <c r="B433" s="135"/>
       <c r="C433" s="135"/>
@@ -17250,7 +17250,7 @@
       <c r="N433" s="135"/>
       <c r="O433" s="138"/>
     </row>
-    <row r="434" spans="1:15" ht="38.1" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="434" spans="1:15" ht="38.1" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A434" s="125"/>
       <c r="B434" s="247" t="s">
         <v>91</v>
@@ -17271,7 +17271,7 @@
       <c r="N434" s="247"/>
       <c r="O434" s="247"/>
     </row>
-    <row r="435" spans="1:15" ht="15" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="435" spans="1:15" ht="15" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A435" s="125"/>
       <c r="B435" s="126"/>
       <c r="C435" s="128"/>
@@ -17288,7 +17288,7 @@
       <c r="N435" s="128"/>
       <c r="O435" s="128"/>
     </row>
-    <row r="436" spans="1:15" ht="18.600000000000001" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="436" spans="1:15" ht="18.600000000000001" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A436" s="125"/>
       <c r="B436" s="248" t="s">
         <v>92</v>
@@ -17309,7 +17309,7 @@
       <c r="N436" s="248"/>
       <c r="O436" s="248"/>
     </row>
-    <row r="437" spans="1:15" ht="15" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="437" spans="1:15" ht="15" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A437" s="125"/>
       <c r="B437" s="131">
         <f>+B408+1</f>
@@ -17331,7 +17331,7 @@
       <c r="N437" s="132"/>
       <c r="O437" s="132"/>
     </row>
-    <row r="438" spans="1:15" ht="18.600000000000001" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="438" spans="1:15" ht="18.600000000000001" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A438" s="125"/>
       <c r="B438" s="133" t="s">
         <v>93</v>
@@ -17363,7 +17363,7 @@
       </c>
       <c r="O438" s="136"/>
     </row>
-    <row r="439" spans="1:15" ht="18.600000000000001" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="439" spans="1:15" ht="18.600000000000001" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A439" s="125"/>
       <c r="B439" s="133" t="s">
         <v>94</v>
@@ -17389,7 +17389,7 @@
       <c r="M439" s="135"/>
       <c r="O439" s="135"/>
     </row>
-    <row r="440" spans="1:15" ht="15.75" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="440" spans="1:15" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A440" s="125"/>
       <c r="B440" s="133" t="s">
         <v>95</v>
@@ -17416,7 +17416,7 @@
       <c r="N440" s="135"/>
       <c r="O440" s="135"/>
     </row>
-    <row r="441" spans="1:15" ht="15.75" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="441" spans="1:15" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A441" s="125"/>
       <c r="B441" s="133"/>
       <c r="C441" s="135"/>
@@ -17433,7 +17433,7 @@
       <c r="N441" s="135"/>
       <c r="O441" s="135"/>
     </row>
-    <row r="442" spans="1:15" ht="15.75" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="442" spans="1:15" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A442" s="125"/>
       <c r="B442" s="133" t="s">
         <v>96</v>
@@ -17460,7 +17460,7 @@
         <v>11445</v>
       </c>
     </row>
-    <row r="443" spans="1:15" ht="15.75" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="443" spans="1:15" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A443" s="125"/>
       <c r="B443" s="133" t="s">
         <v>97</v>
@@ -17487,7 +17487,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="444" spans="1:15" ht="15.75" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="444" spans="1:15" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A444" s="125"/>
       <c r="B444" s="133" t="s">
         <v>98</v>
@@ -17513,7 +17513,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="445" spans="1:15" ht="15.75" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="445" spans="1:15" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A445" s="125"/>
       <c r="B445" s="133" t="s">
         <v>99</v>
@@ -17538,7 +17538,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="446" spans="1:15" ht="15.75" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="446" spans="1:15" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A446" s="125"/>
       <c r="B446" s="135"/>
       <c r="C446" s="135"/>
@@ -17565,7 +17565,7 @@
         <v>11445</v>
       </c>
     </row>
-    <row r="447" spans="1:15" ht="15.75" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="447" spans="1:15" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A447" s="125"/>
       <c r="B447" s="135"/>
       <c r="C447" s="135"/>
@@ -17582,7 +17582,7 @@
       <c r="N447" s="135"/>
       <c r="O447" s="138"/>
     </row>
-    <row r="448" spans="1:15" ht="15.75" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="448" spans="1:15" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A448" s="125"/>
       <c r="B448" s="135"/>
       <c r="C448" s="133" t="s">
@@ -17602,7 +17602,7 @@
       <c r="N448" s="135"/>
       <c r="O448" s="138"/>
     </row>
-    <row r="449" spans="1:15" ht="15.75" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="449" spans="1:15" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A449" s="125"/>
       <c r="B449" s="135"/>
       <c r="C449" s="135"/>
@@ -17628,7 +17628,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="450" spans="1:15" ht="15.75" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="450" spans="1:15" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A450" s="125"/>
       <c r="B450" s="135"/>
       <c r="C450" s="135"/>
@@ -17654,7 +17654,7 @@
         <v>343.34999999999997</v>
       </c>
     </row>
-    <row r="451" spans="1:15" ht="15.75" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="451" spans="1:15" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A451" s="125"/>
       <c r="B451" s="135"/>
       <c r="C451" s="135"/>
@@ -17680,7 +17680,7 @@
         <v>114.45</v>
       </c>
     </row>
-    <row r="452" spans="1:15" ht="15.75" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="452" spans="1:15" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A452" s="125"/>
       <c r="B452" s="135"/>
       <c r="C452" s="135"/>
@@ -17703,7 +17703,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="453" spans="1:15" ht="15.75" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="453" spans="1:15" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A453" s="125"/>
       <c r="B453" s="135"/>
       <c r="C453" s="135"/>
@@ -17726,7 +17726,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="454" spans="1:15" ht="15.75" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="454" spans="1:15" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A454" s="125"/>
       <c r="B454" s="135"/>
       <c r="C454" s="135"/>
@@ -17749,7 +17749,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="455" spans="1:15" ht="15.75" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="455" spans="1:15" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A455" s="125"/>
       <c r="B455" s="135"/>
       <c r="C455" s="135"/>
@@ -17776,7 +17776,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="456" spans="1:15" ht="15.75" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="456" spans="1:15" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A456" s="125"/>
       <c r="B456" s="135"/>
       <c r="C456" s="135"/>
@@ -17803,7 +17803,7 @@
         <v>457.79999999999995</v>
       </c>
     </row>
-    <row r="457" spans="1:15" ht="15.75" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="457" spans="1:15" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A457" s="125"/>
       <c r="B457" s="135"/>
       <c r="C457" s="135"/>
@@ -17820,7 +17820,7 @@
       <c r="N457" s="135"/>
       <c r="O457" s="138"/>
     </row>
-    <row r="458" spans="1:15" ht="15.75" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="458" spans="1:15" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A458" s="125"/>
       <c r="B458" s="135"/>
       <c r="C458" s="133" t="s">
@@ -17847,7 +17847,7 @@
         <v>10987.2</v>
       </c>
     </row>
-    <row r="459" spans="1:15" ht="15.75" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="459" spans="1:15" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A459" s="125"/>
       <c r="B459" s="135"/>
       <c r="C459" s="133"/>
@@ -17864,7 +17864,7 @@
       <c r="N459" s="135"/>
       <c r="O459" s="138"/>
     </row>
-    <row r="460" spans="1:15" ht="15.75" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="460" spans="1:15" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A460" s="125"/>
       <c r="B460" s="135"/>
       <c r="C460" s="135"/>
@@ -17881,7 +17881,7 @@
       <c r="N460" s="135"/>
       <c r="O460" s="138"/>
     </row>
-    <row r="461" spans="1:15" ht="15.75" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="461" spans="1:15" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A461" s="125"/>
       <c r="B461" s="135"/>
       <c r="C461" s="135"/>
@@ -17902,7 +17902,7 @@
       <c r="N461" s="135"/>
       <c r="O461" s="138"/>
     </row>
-    <row r="462" spans="1:15" ht="38.1" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="462" spans="1:15" ht="38.1" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A462" s="125"/>
       <c r="B462" s="247" t="s">
         <v>91</v>
@@ -17923,7 +17923,7 @@
       <c r="N462" s="247"/>
       <c r="O462" s="247"/>
     </row>
-    <row r="463" spans="1:15" ht="15" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="463" spans="1:15" ht="15" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A463" s="125"/>
       <c r="B463" s="126"/>
       <c r="C463" s="128"/>
@@ -17940,7 +17940,7 @@
       <c r="N463" s="128"/>
       <c r="O463" s="128"/>
     </row>
-    <row r="464" spans="1:15" ht="18.600000000000001" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="464" spans="1:15" ht="18.600000000000001" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A464" s="125"/>
       <c r="B464" s="248" t="s">
         <v>92</v>
@@ -17961,7 +17961,7 @@
       <c r="N464" s="248"/>
       <c r="O464" s="248"/>
     </row>
-    <row r="465" spans="1:15" ht="15" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="465" spans="1:15" ht="15" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A465" s="125"/>
       <c r="B465" s="131">
         <f>+B437+1</f>
@@ -17983,7 +17983,7 @@
       <c r="N465" s="132"/>
       <c r="O465" s="132"/>
     </row>
-    <row r="466" spans="1:15" ht="18.600000000000001" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="466" spans="1:15" ht="18.600000000000001" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A466" s="125"/>
       <c r="B466" s="133" t="s">
         <v>93</v>
@@ -18015,7 +18015,7 @@
       </c>
       <c r="O466" s="136"/>
     </row>
-    <row r="467" spans="1:15" ht="18.600000000000001" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="467" spans="1:15" ht="18.600000000000001" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A467" s="125"/>
       <c r="B467" s="133" t="s">
         <v>94</v>
@@ -18041,7 +18041,7 @@
       <c r="M467" s="135"/>
       <c r="O467" s="135"/>
     </row>
-    <row r="468" spans="1:15" ht="15.75" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="468" spans="1:15" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A468" s="125"/>
       <c r="B468" s="133" t="s">
         <v>95</v>
@@ -18068,7 +18068,7 @@
       <c r="N468" s="135"/>
       <c r="O468" s="135"/>
     </row>
-    <row r="469" spans="1:15" ht="15.75" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="469" spans="1:15" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A469" s="125"/>
       <c r="B469" s="133"/>
       <c r="C469" s="135"/>
@@ -18085,7 +18085,7 @@
       <c r="N469" s="135"/>
       <c r="O469" s="135"/>
     </row>
-    <row r="470" spans="1:15" ht="15.75" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="470" spans="1:15" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A470" s="125"/>
       <c r="B470" s="133" t="s">
         <v>96</v>
@@ -18112,7 +18112,7 @@
         <v>10955</v>
       </c>
     </row>
-    <row r="471" spans="1:15" ht="15.75" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="471" spans="1:15" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A471" s="125"/>
       <c r="B471" s="133" t="s">
         <v>97</v>
@@ -18139,7 +18139,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="472" spans="1:15" ht="15.75" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="472" spans="1:15" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A472" s="125"/>
       <c r="B472" s="133" t="s">
         <v>98</v>
@@ -18165,7 +18165,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="473" spans="1:15" ht="15.75" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="473" spans="1:15" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A473" s="125"/>
       <c r="B473" s="133" t="s">
         <v>99</v>
@@ -18190,7 +18190,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="474" spans="1:15" ht="15.75" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="474" spans="1:15" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A474" s="125"/>
       <c r="B474" s="135"/>
       <c r="C474" s="135"/>
@@ -18217,7 +18217,7 @@
         <v>10955</v>
       </c>
     </row>
-    <row r="475" spans="1:15" ht="15.75" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="475" spans="1:15" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A475" s="125"/>
       <c r="B475" s="135"/>
       <c r="C475" s="135"/>
@@ -18234,7 +18234,7 @@
       <c r="N475" s="135"/>
       <c r="O475" s="138"/>
     </row>
-    <row r="476" spans="1:15" ht="15.75" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="476" spans="1:15" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A476" s="125"/>
       <c r="B476" s="135"/>
       <c r="C476" s="133" t="s">
@@ -18254,7 +18254,7 @@
       <c r="M476" s="135"/>
       <c r="O476" s="138"/>
     </row>
-    <row r="477" spans="1:15" ht="15.75" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="477" spans="1:15" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A477" s="125"/>
       <c r="B477" s="135"/>
       <c r="C477" s="135"/>
@@ -18280,7 +18280,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="478" spans="1:15" ht="15.75" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="478" spans="1:15" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A478" s="125"/>
       <c r="B478" s="135"/>
       <c r="C478" s="135"/>
@@ -18306,7 +18306,7 @@
         <v>328.65</v>
       </c>
     </row>
-    <row r="479" spans="1:15" ht="15.75" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="479" spans="1:15" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A479" s="125"/>
       <c r="B479" s="135"/>
       <c r="C479" s="135"/>
@@ -18332,7 +18332,7 @@
         <v>109.55</v>
       </c>
     </row>
-    <row r="480" spans="1:15" ht="15.75" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="480" spans="1:15" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A480" s="125"/>
       <c r="B480" s="135"/>
       <c r="C480" s="135"/>
@@ -18355,7 +18355,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="481" spans="1:15" ht="15.75" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="481" spans="1:15" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A481" s="125"/>
       <c r="B481" s="135"/>
       <c r="C481" s="135"/>
@@ -18378,7 +18378,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="482" spans="1:15" ht="15.75" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="482" spans="1:15" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A482" s="125"/>
       <c r="B482" s="135"/>
       <c r="C482" s="135"/>
@@ -18401,7 +18401,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="483" spans="1:15" ht="15.75" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="483" spans="1:15" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A483" s="125"/>
       <c r="B483" s="135"/>
       <c r="C483" s="135"/>
@@ -18428,7 +18428,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="484" spans="1:15" ht="15.75" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="484" spans="1:15" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A484" s="125"/>
       <c r="B484" s="135"/>
       <c r="C484" s="135"/>
@@ -18452,7 +18452,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="485" spans="1:15" ht="15.75" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="485" spans="1:15" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A485" s="125"/>
       <c r="B485" s="135"/>
       <c r="C485" s="135"/>
@@ -18479,7 +18479,7 @@
         <v>438.2</v>
       </c>
     </row>
-    <row r="486" spans="1:15" ht="15.75" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="486" spans="1:15" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A486" s="125"/>
       <c r="B486" s="135"/>
       <c r="C486" s="135"/>
@@ -18496,7 +18496,7 @@
       <c r="N486" s="135"/>
       <c r="O486" s="138"/>
     </row>
-    <row r="487" spans="1:15" ht="15.75" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="487" spans="1:15" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A487" s="125"/>
       <c r="B487" s="135"/>
       <c r="C487" s="133" t="s">
@@ -18523,7 +18523,7 @@
         <v>10516.8</v>
       </c>
     </row>
-    <row r="488" spans="1:15" ht="15.75" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="488" spans="1:15" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A488" s="125"/>
       <c r="B488" s="135"/>
       <c r="C488" s="133"/>
@@ -18540,7 +18540,7 @@
       <c r="N488" s="135"/>
       <c r="O488" s="138"/>
     </row>
-    <row r="489" spans="1:15" ht="15.75" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="489" spans="1:15" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A489" s="125"/>
       <c r="B489" s="135"/>
       <c r="C489" s="135"/>
@@ -18557,7 +18557,7 @@
       <c r="N489" s="135"/>
       <c r="O489" s="138"/>
     </row>
-    <row r="490" spans="1:15" ht="15.75" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="490" spans="1:15" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A490" s="125"/>
       <c r="B490" s="135"/>
       <c r="C490" s="135"/>
@@ -18578,7 +18578,7 @@
       <c r="N490" s="135"/>
       <c r="O490" s="138"/>
     </row>
-    <row r="491" spans="1:15" ht="38.1" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="491" spans="1:15" ht="38.1" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A491" s="125"/>
       <c r="B491" s="247" t="s">
         <v>91</v>
@@ -18599,7 +18599,7 @@
       <c r="N491" s="247"/>
       <c r="O491" s="247"/>
     </row>
-    <row r="492" spans="1:15" ht="15" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="492" spans="1:15" ht="15" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A492" s="125"/>
       <c r="B492" s="126"/>
       <c r="C492" s="128"/>
@@ -18616,7 +18616,7 @@
       <c r="N492" s="128"/>
       <c r="O492" s="128"/>
     </row>
-    <row r="493" spans="1:15" ht="18.600000000000001" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="493" spans="1:15" ht="18.600000000000001" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A493" s="125"/>
       <c r="B493" s="248" t="s">
         <v>92</v>
@@ -18637,7 +18637,7 @@
       <c r="N493" s="248"/>
       <c r="O493" s="248"/>
     </row>
-    <row r="494" spans="1:15" ht="15" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="494" spans="1:15" ht="15" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A494" s="125"/>
       <c r="B494" s="131">
         <f>+B465+1</f>
@@ -18660,7 +18660,7 @@
       <c r="N494" s="132"/>
       <c r="O494" s="132"/>
     </row>
-    <row r="495" spans="1:15" ht="18.600000000000001" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="495" spans="1:15" ht="18.600000000000001" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A495" s="125"/>
       <c r="B495" s="133" t="s">
         <v>93</v>
@@ -18692,7 +18692,7 @@
       </c>
       <c r="O495" s="136"/>
     </row>
-    <row r="496" spans="1:15" ht="18.600000000000001" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="496" spans="1:15" ht="18.600000000000001" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A496" s="125"/>
       <c r="B496" s="133" t="s">
         <v>94</v>
@@ -18718,7 +18718,7 @@
       <c r="M496" s="135"/>
       <c r="O496" s="135"/>
     </row>
-    <row r="497" spans="1:15" ht="15.75" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="497" spans="1:15" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A497" s="125"/>
       <c r="B497" s="133" t="s">
         <v>95</v>
@@ -18745,7 +18745,7 @@
       <c r="N497" s="135"/>
       <c r="O497" s="135"/>
     </row>
-    <row r="498" spans="1:15" ht="15.75" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="498" spans="1:15" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A498" s="125"/>
       <c r="B498" s="133"/>
       <c r="C498" s="135"/>
@@ -18762,7 +18762,7 @@
       <c r="N498" s="135"/>
       <c r="O498" s="135"/>
     </row>
-    <row r="499" spans="1:15" ht="15.75" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="499" spans="1:15" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A499" s="125"/>
       <c r="B499" s="133" t="s">
         <v>96</v>
@@ -18789,7 +18789,7 @@
         <v>14225.000000000002</v>
       </c>
     </row>
-    <row r="500" spans="1:15" ht="15.75" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="500" spans="1:15" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A500" s="125"/>
       <c r="B500" s="133" t="s">
         <v>97</v>
@@ -18816,7 +18816,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="501" spans="1:15" ht="15.75" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="501" spans="1:15" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A501" s="125"/>
       <c r="B501" s="133" t="s">
         <v>98</v>
@@ -18842,7 +18842,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="502" spans="1:15" ht="15.75" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="502" spans="1:15" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A502" s="125"/>
       <c r="B502" s="133" t="s">
         <v>99</v>
@@ -18868,7 +18868,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="503" spans="1:15" ht="15.75" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="503" spans="1:15" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A503" s="125"/>
       <c r="B503" s="135"/>
       <c r="C503" s="135"/>
@@ -18895,7 +18895,7 @@
         <v>14225.000000000002</v>
       </c>
     </row>
-    <row r="504" spans="1:15" ht="15.75" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="504" spans="1:15" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A504" s="125"/>
       <c r="B504" s="135"/>
       <c r="C504" s="135"/>
@@ -18912,7 +18912,7 @@
       <c r="N504" s="135"/>
       <c r="O504" s="138"/>
     </row>
-    <row r="505" spans="1:15" ht="15.75" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="505" spans="1:15" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A505" s="125"/>
       <c r="B505" s="135"/>
       <c r="C505" s="133" t="s">
@@ -18932,7 +18932,7 @@
       <c r="M505" s="135"/>
       <c r="O505" s="138"/>
     </row>
-    <row r="506" spans="1:15" ht="15.75" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="506" spans="1:15" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A506" s="125"/>
       <c r="B506" s="135"/>
       <c r="C506" s="135"/>
@@ -18958,7 +18958,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="507" spans="1:15" ht="15.75" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="507" spans="1:15" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A507" s="125"/>
       <c r="B507" s="135"/>
       <c r="C507" s="135"/>
@@ -18984,7 +18984,7 @@
         <v>426.75000000000006</v>
       </c>
     </row>
-    <row r="508" spans="1:15" ht="15.75" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="508" spans="1:15" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A508" s="125"/>
       <c r="B508" s="135"/>
       <c r="C508" s="135"/>
@@ -19010,7 +19010,7 @@
         <v>142.25000000000003</v>
       </c>
     </row>
-    <row r="509" spans="1:15" ht="15.75" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="509" spans="1:15" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A509" s="125"/>
       <c r="B509" s="135"/>
       <c r="C509" s="135"/>
@@ -19033,7 +19033,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="510" spans="1:15" ht="15.75" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="510" spans="1:15" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A510" s="125"/>
       <c r="B510" s="135"/>
       <c r="C510" s="135"/>
@@ -19056,7 +19056,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="511" spans="1:15" ht="15.75" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="511" spans="1:15" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A511" s="125"/>
       <c r="B511" s="135"/>
       <c r="C511" s="135"/>
@@ -19079,7 +19079,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="512" spans="1:15" ht="15.75" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="512" spans="1:15" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A512" s="125"/>
       <c r="B512" s="135"/>
       <c r="C512" s="135"/>
@@ -19106,7 +19106,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="513" spans="1:15" ht="15.75" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="513" spans="1:15" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A513" s="125"/>
       <c r="B513" s="135"/>
       <c r="C513" s="135"/>
@@ -19130,7 +19130,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="514" spans="1:15" ht="15.75" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="514" spans="1:15" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A514" s="125"/>
       <c r="B514" s="135"/>
       <c r="C514" s="135"/>
@@ -19157,7 +19157,7 @@
         <v>569.00000000000011</v>
       </c>
     </row>
-    <row r="515" spans="1:15" ht="15.75" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="515" spans="1:15" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A515" s="125"/>
       <c r="B515" s="135"/>
       <c r="C515" s="135"/>
@@ -19174,7 +19174,7 @@
       <c r="N515" s="135"/>
       <c r="O515" s="138"/>
     </row>
-    <row r="516" spans="1:15" ht="15.75" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="516" spans="1:15" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A516" s="125"/>
       <c r="B516" s="135"/>
       <c r="C516" s="133" t="s">
@@ -19201,7 +19201,7 @@
         <v>13656.000000000002</v>
       </c>
     </row>
-    <row r="517" spans="1:15" ht="15.75" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="517" spans="1:15" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A517" s="125"/>
       <c r="B517" s="135"/>
       <c r="C517" s="133"/>
@@ -19218,7 +19218,7 @@
       <c r="N517" s="135"/>
       <c r="O517" s="138"/>
     </row>
-    <row r="518" spans="1:15" ht="15.75" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="518" spans="1:15" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A518" s="125"/>
       <c r="B518" s="135"/>
       <c r="C518" s="135"/>
@@ -19235,7 +19235,7 @@
       <c r="N518" s="135"/>
       <c r="O518" s="138"/>
     </row>
-    <row r="519" spans="1:15" ht="15.75" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="519" spans="1:15" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A519" s="125"/>
       <c r="B519" s="135"/>
       <c r="C519" s="135"/>
@@ -19256,7 +19256,7 @@
       <c r="N519" s="135"/>
       <c r="O519" s="138"/>
     </row>
-    <row r="520" spans="1:15" ht="38.1" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="520" spans="1:15" ht="38.1" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A520" s="125"/>
       <c r="B520" s="247" t="s">
         <v>91</v>
@@ -19277,7 +19277,7 @@
       <c r="N520" s="247"/>
       <c r="O520" s="247"/>
     </row>
-    <row r="521" spans="1:15" ht="15" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="521" spans="1:15" ht="15" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A521" s="125"/>
       <c r="B521" s="126"/>
       <c r="C521" s="128"/>
@@ -19294,7 +19294,7 @@
       <c r="N521" s="128"/>
       <c r="O521" s="128"/>
     </row>
-    <row r="522" spans="1:15" ht="18.600000000000001" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="522" spans="1:15" ht="18.600000000000001" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A522" s="125"/>
       <c r="B522" s="248" t="s">
         <v>92</v>
@@ -19315,7 +19315,7 @@
       <c r="N522" s="248"/>
       <c r="O522" s="248"/>
     </row>
-    <row r="523" spans="1:15" ht="15" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="523" spans="1:15" ht="15" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A523" s="125"/>
       <c r="B523" s="131">
         <f>+'Folha de salarios'!A28</f>
@@ -19337,7 +19337,7 @@
       <c r="N523" s="132"/>
       <c r="O523" s="132"/>
     </row>
-    <row r="524" spans="1:15" ht="18.600000000000001" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="524" spans="1:15" ht="18.600000000000001" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A524" s="125"/>
       <c r="B524" s="133" t="s">
         <v>93</v>
@@ -19369,7 +19369,7 @@
       </c>
       <c r="O524" s="136"/>
     </row>
-    <row r="525" spans="1:15" ht="18.600000000000001" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="525" spans="1:15" ht="18.600000000000001" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A525" s="125"/>
       <c r="B525" s="133" t="s">
         <v>94</v>
@@ -19395,7 +19395,7 @@
       <c r="M525" s="135"/>
       <c r="O525" s="135"/>
     </row>
-    <row r="526" spans="1:15" ht="15.75" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="526" spans="1:15" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A526" s="125"/>
       <c r="B526" s="133" t="s">
         <v>95</v>
@@ -19422,7 +19422,7 @@
       <c r="N526" s="135"/>
       <c r="O526" s="135"/>
     </row>
-    <row r="527" spans="1:15" ht="15.75" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="527" spans="1:15" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A527" s="125"/>
       <c r="B527" s="133"/>
       <c r="C527" s="135"/>
@@ -19439,7 +19439,7 @@
       <c r="N527" s="135"/>
       <c r="O527" s="135"/>
     </row>
-    <row r="528" spans="1:15" ht="15.75" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="528" spans="1:15" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A528" s="125"/>
       <c r="B528" s="133" t="s">
         <v>96</v>
@@ -19466,7 +19466,7 @@
         <v>11445</v>
       </c>
     </row>
-    <row r="529" spans="1:15" ht="15.75" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="529" spans="1:15" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A529" s="125"/>
       <c r="B529" s="133" t="s">
         <v>97</v>
@@ -19493,7 +19493,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="530" spans="1:15" ht="15.75" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="530" spans="1:15" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A530" s="125"/>
       <c r="B530" s="133" t="s">
         <v>98</v>
@@ -19519,7 +19519,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="531" spans="1:15" ht="15.75" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="531" spans="1:15" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A531" s="125"/>
       <c r="B531" s="133" t="s">
         <v>99</v>
@@ -19544,7 +19544,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="532" spans="1:15" ht="15.75" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="532" spans="1:15" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A532" s="125"/>
       <c r="B532" s="135"/>
       <c r="C532" s="135"/>
@@ -19571,7 +19571,7 @@
         <v>11445</v>
       </c>
     </row>
-    <row r="533" spans="1:15" ht="15.75" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="533" spans="1:15" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A533" s="125"/>
       <c r="B533" s="135"/>
       <c r="C533" s="135"/>
@@ -19588,7 +19588,7 @@
       <c r="N533" s="135"/>
       <c r="O533" s="138"/>
     </row>
-    <row r="534" spans="1:15" ht="15.75" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="534" spans="1:15" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A534" s="125"/>
       <c r="B534" s="135"/>
       <c r="C534" s="133" t="s">
@@ -19608,7 +19608,7 @@
       <c r="N534" s="135"/>
       <c r="O534" s="138"/>
     </row>
-    <row r="535" spans="1:15" ht="15.75" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="535" spans="1:15" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A535" s="125"/>
       <c r="B535" s="135"/>
       <c r="C535" s="135"/>
@@ -19634,7 +19634,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="536" spans="1:15" ht="15.75" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="536" spans="1:15" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A536" s="125"/>
       <c r="B536" s="135"/>
       <c r="C536" s="135"/>
@@ -19660,7 +19660,7 @@
         <v>343.34999999999997</v>
       </c>
     </row>
-    <row r="537" spans="1:15" ht="15.75" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="537" spans="1:15" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A537" s="125"/>
       <c r="B537" s="135"/>
       <c r="C537" s="135"/>
@@ -19686,7 +19686,7 @@
         <v>114.45</v>
       </c>
     </row>
-    <row r="538" spans="1:15" ht="15.75" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="538" spans="1:15" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A538" s="125"/>
       <c r="B538" s="135"/>
       <c r="C538" s="135"/>
@@ -19709,7 +19709,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="539" spans="1:15" ht="15.75" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="539" spans="1:15" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A539" s="125"/>
       <c r="B539" s="135"/>
       <c r="C539" s="135"/>
@@ -19732,7 +19732,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="540" spans="1:15" ht="15.75" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="540" spans="1:15" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A540" s="125"/>
       <c r="B540" s="135"/>
       <c r="C540" s="135"/>
@@ -19755,7 +19755,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="541" spans="1:15" ht="15.75" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="541" spans="1:15" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A541" s="125"/>
       <c r="B541" s="135"/>
       <c r="C541" s="135"/>
@@ -19782,7 +19782,7 @@
         <v>1500</v>
       </c>
     </row>
-    <row r="542" spans="1:15" ht="15.75" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="542" spans="1:15" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A542" s="125"/>
       <c r="B542" s="135"/>
       <c r="C542" s="135"/>
@@ -19808,7 +19808,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="543" spans="1:15" ht="15.75" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="543" spans="1:15" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A543" s="125"/>
       <c r="B543" s="135"/>
       <c r="C543" s="135"/>
@@ -19835,7 +19835,7 @@
         <v>1957.8</v>
       </c>
     </row>
-    <row r="544" spans="1:15" ht="15.75" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="544" spans="1:15" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A544" s="125"/>
       <c r="B544" s="135"/>
       <c r="C544" s="135"/>
@@ -19852,7 +19852,7 @@
       <c r="N544" s="135"/>
       <c r="O544" s="138"/>
     </row>
-    <row r="545" spans="1:15" ht="15.75" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="545" spans="1:15" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A545" s="125"/>
       <c r="B545" s="135"/>
       <c r="C545" s="133" t="s">
@@ -19879,7 +19879,7 @@
         <v>9487.2000000000007</v>
       </c>
     </row>
-    <row r="546" spans="1:15" ht="15.75" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="546" spans="1:15" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A546" s="125"/>
       <c r="B546" s="135"/>
       <c r="C546" s="133"/>
@@ -19896,7 +19896,7 @@
       <c r="N546" s="135"/>
       <c r="O546" s="138"/>
     </row>
-    <row r="547" spans="1:15" ht="15.75" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="547" spans="1:15" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A547" s="125"/>
       <c r="B547" s="135"/>
       <c r="C547" s="135"/>
@@ -19913,7 +19913,7 @@
       <c r="N547" s="135"/>
       <c r="O547" s="138"/>
     </row>
-    <row r="548" spans="1:15" ht="15.75" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="548" spans="1:15" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A548" s="125"/>
       <c r="B548" s="135"/>
       <c r="C548" s="135"/>
@@ -19934,7 +19934,7 @@
       <c r="N548" s="135"/>
       <c r="O548" s="138"/>
     </row>
-    <row r="549" spans="1:15" ht="38.1" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="549" spans="1:15" ht="38.1" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A549" s="125"/>
       <c r="B549" s="247" t="s">
         <v>91</v>
@@ -19955,7 +19955,7 @@
       <c r="N549" s="247"/>
       <c r="O549" s="247"/>
     </row>
-    <row r="550" spans="1:15" ht="15" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="550" spans="1:15" ht="15" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A550" s="125"/>
       <c r="B550" s="126"/>
       <c r="C550" s="128"/>
@@ -19972,7 +19972,7 @@
       <c r="N550" s="128"/>
       <c r="O550" s="128"/>
     </row>
-    <row r="551" spans="1:15" ht="18.600000000000001" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="551" spans="1:15" ht="18.600000000000001" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A551" s="125"/>
       <c r="B551" s="248" t="s">
         <v>92</v>
@@ -19993,7 +19993,7 @@
       <c r="N551" s="248"/>
       <c r="O551" s="248"/>
     </row>
-    <row r="552" spans="1:15" ht="15" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="552" spans="1:15" ht="15" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A552" s="125"/>
       <c r="B552" s="131">
         <f>+B523+1</f>
@@ -20015,7 +20015,7 @@
       <c r="N552" s="132"/>
       <c r="O552" s="132"/>
     </row>
-    <row r="553" spans="1:15" ht="18.600000000000001" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="553" spans="1:15" ht="18.600000000000001" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A553" s="125"/>
       <c r="B553" s="133" t="s">
         <v>93</v>
@@ -20047,7 +20047,7 @@
       </c>
       <c r="O553" s="136"/>
     </row>
-    <row r="554" spans="1:15" ht="18.600000000000001" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="554" spans="1:15" ht="18.600000000000001" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A554" s="125"/>
       <c r="B554" s="133" t="s">
         <v>94</v>
@@ -20073,7 +20073,7 @@
       <c r="M554" s="135"/>
       <c r="O554" s="135"/>
     </row>
-    <row r="555" spans="1:15" ht="15.75" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="555" spans="1:15" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A555" s="125"/>
       <c r="B555" s="133" t="s">
         <v>95</v>
@@ -20100,7 +20100,7 @@
       <c r="N555" s="135"/>
       <c r="O555" s="135"/>
     </row>
-    <row r="556" spans="1:15" ht="15.75" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="556" spans="1:15" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A556" s="125"/>
       <c r="B556" s="133"/>
       <c r="C556" s="135"/>
@@ -20117,7 +20117,7 @@
       <c r="N556" s="135"/>
       <c r="O556" s="135"/>
     </row>
-    <row r="557" spans="1:15" ht="15.75" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="557" spans="1:15" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A557" s="125"/>
       <c r="B557" s="133" t="s">
         <v>96</v>
@@ -20144,7 +20144,7 @@
         <v>14225.000000000002</v>
       </c>
     </row>
-    <row r="558" spans="1:15" ht="15.75" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="558" spans="1:15" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A558" s="125"/>
       <c r="B558" s="133" t="s">
         <v>97</v>
@@ -20171,7 +20171,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="559" spans="1:15" ht="15.75" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="559" spans="1:15" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A559" s="125"/>
       <c r="B559" s="133" t="s">
         <v>98</v>
@@ -20197,7 +20197,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="560" spans="1:15" ht="15.75" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="560" spans="1:15" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A560" s="125"/>
       <c r="B560" s="133" t="s">
         <v>99</v>
@@ -20222,7 +20222,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="561" spans="1:15" ht="15.75" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="561" spans="1:15" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A561" s="125"/>
       <c r="B561" s="135"/>
       <c r="C561" s="135"/>
@@ -20249,7 +20249,7 @@
         <v>14225.000000000002</v>
       </c>
     </row>
-    <row r="562" spans="1:15" ht="15.75" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="562" spans="1:15" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A562" s="125"/>
       <c r="B562" s="135"/>
       <c r="C562" s="135"/>
@@ -20266,7 +20266,7 @@
       <c r="N562" s="135"/>
       <c r="O562" s="138"/>
     </row>
-    <row r="563" spans="1:15" ht="15.75" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="563" spans="1:15" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A563" s="125"/>
       <c r="B563" s="135"/>
       <c r="C563" s="133" t="s">
@@ -20286,7 +20286,7 @@
       <c r="N563" s="135"/>
       <c r="O563" s="138"/>
     </row>
-    <row r="564" spans="1:15" ht="15.75" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="564" spans="1:15" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A564" s="125"/>
       <c r="B564" s="135"/>
       <c r="C564" s="135"/>
@@ -20312,7 +20312,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="565" spans="1:15" ht="15.75" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="565" spans="1:15" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A565" s="125"/>
       <c r="B565" s="135"/>
       <c r="C565" s="135"/>
@@ -20338,7 +20338,7 @@
         <v>426.75000000000006</v>
       </c>
     </row>
-    <row r="566" spans="1:15" ht="15.75" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="566" spans="1:15" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A566" s="125"/>
       <c r="B566" s="135"/>
       <c r="C566" s="135"/>
@@ -20364,7 +20364,7 @@
         <v>142.25000000000003</v>
       </c>
     </row>
-    <row r="567" spans="1:15" ht="15.75" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="567" spans="1:15" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A567" s="125"/>
       <c r="B567" s="135"/>
       <c r="C567" s="135"/>
@@ -20387,7 +20387,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="568" spans="1:15" ht="15.75" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="568" spans="1:15" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A568" s="125"/>
       <c r="B568" s="135"/>
       <c r="C568" s="135"/>
@@ -20410,7 +20410,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="569" spans="1:15" ht="15.75" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="569" spans="1:15" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A569" s="125"/>
       <c r="B569" s="135"/>
       <c r="C569" s="135"/>
@@ -20433,7 +20433,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="570" spans="1:15" ht="15.75" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="570" spans="1:15" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A570" s="125"/>
       <c r="B570" s="135"/>
       <c r="C570" s="135"/>
@@ -20460,7 +20460,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="571" spans="1:15" ht="15.75" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="571" spans="1:15" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A571" s="125"/>
       <c r="B571" s="135"/>
       <c r="C571" s="135"/>
@@ -20486,7 +20486,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="572" spans="1:15" ht="15.75" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="572" spans="1:15" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A572" s="125"/>
       <c r="B572" s="135"/>
       <c r="C572" s="135"/>
@@ -20513,7 +20513,7 @@
         <v>569.00000000000011</v>
       </c>
     </row>
-    <row r="573" spans="1:15" ht="15.75" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="573" spans="1:15" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A573" s="125"/>
       <c r="B573" s="135"/>
       <c r="C573" s="135"/>
@@ -20530,7 +20530,7 @@
       <c r="N573" s="135"/>
       <c r="O573" s="138"/>
     </row>
-    <row r="574" spans="1:15" ht="15.75" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="574" spans="1:15" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A574" s="125"/>
       <c r="B574" s="135"/>
       <c r="C574" s="133" t="s">
@@ -20557,7 +20557,7 @@
         <v>13656.000000000002</v>
       </c>
     </row>
-    <row r="575" spans="1:15" ht="15.75" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="575" spans="1:15" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A575" s="125"/>
       <c r="B575" s="135"/>
       <c r="C575" s="133"/>
@@ -20574,7 +20574,7 @@
       <c r="N575" s="135"/>
       <c r="O575" s="138"/>
     </row>
-    <row r="576" spans="1:15" ht="15.75" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="576" spans="1:15" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A576" s="125"/>
       <c r="B576" s="135"/>
       <c r="C576" s="135"/>
@@ -20591,7 +20591,7 @@
       <c r="N576" s="135"/>
       <c r="O576" s="138"/>
     </row>
-    <row r="577" spans="1:15" ht="15.75" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="577" spans="1:15" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A577" s="125"/>
       <c r="B577" s="135"/>
       <c r="C577" s="135"/>
@@ -20612,7 +20612,7 @@
       <c r="N577" s="135"/>
       <c r="O577" s="138"/>
     </row>
-    <row r="578" spans="1:15" ht="38.1" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="578" spans="1:15" ht="38.1" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A578" s="125"/>
       <c r="B578" s="247" t="s">
         <v>91</v>
@@ -20633,7 +20633,7 @@
       <c r="N578" s="247"/>
       <c r="O578" s="247"/>
     </row>
-    <row r="579" spans="1:15" ht="15" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="579" spans="1:15" ht="15" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A579" s="125"/>
       <c r="B579" s="126"/>
       <c r="C579" s="128"/>
@@ -20650,7 +20650,7 @@
       <c r="N579" s="128"/>
       <c r="O579" s="128"/>
     </row>
-    <row r="580" spans="1:15" ht="18.600000000000001" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="580" spans="1:15" ht="18.600000000000001" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A580" s="125"/>
       <c r="B580" s="248" t="s">
         <v>92</v>
@@ -20671,7 +20671,7 @@
       <c r="N580" s="248"/>
       <c r="O580" s="248"/>
     </row>
-    <row r="581" spans="1:15" ht="15" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="581" spans="1:15" ht="15" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A581" s="125"/>
       <c r="B581" s="131">
         <f>+B552+1</f>
@@ -20693,7 +20693,7 @@
       <c r="N581" s="132"/>
       <c r="O581" s="132"/>
     </row>
-    <row r="582" spans="1:15" ht="18.600000000000001" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="582" spans="1:15" ht="18.600000000000001" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A582" s="125"/>
       <c r="B582" s="133" t="s">
         <v>93</v>
@@ -20725,7 +20725,7 @@
       </c>
       <c r="O582" s="136"/>
     </row>
-    <row r="583" spans="1:15" ht="18.600000000000001" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="583" spans="1:15" ht="18.600000000000001" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A583" s="125"/>
       <c r="B583" s="133" t="s">
         <v>94</v>
@@ -20751,7 +20751,7 @@
       <c r="M583" s="135"/>
       <c r="O583" s="135"/>
     </row>
-    <row r="584" spans="1:15" ht="15.75" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="584" spans="1:15" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A584" s="125"/>
       <c r="B584" s="133" t="s">
         <v>95</v>
@@ -20778,7 +20778,7 @@
       <c r="N584" s="135"/>
       <c r="O584" s="135"/>
     </row>
-    <row r="585" spans="1:15" ht="15.75" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="585" spans="1:15" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A585" s="125"/>
       <c r="B585" s="133"/>
       <c r="C585" s="135"/>
@@ -20795,7 +20795,7 @@
       <c r="N585" s="135"/>
       <c r="O585" s="135"/>
     </row>
-    <row r="586" spans="1:15" ht="15.75" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="586" spans="1:15" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A586" s="125"/>
       <c r="B586" s="133" t="s">
         <v>96</v>
@@ -20822,7 +20822,7 @@
         <v>10955</v>
       </c>
     </row>
-    <row r="587" spans="1:15" ht="15.75" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="587" spans="1:15" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A587" s="125"/>
       <c r="B587" s="133" t="s">
         <v>97</v>
@@ -20849,7 +20849,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="588" spans="1:15" ht="15.75" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="588" spans="1:15" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A588" s="125"/>
       <c r="B588" s="133" t="s">
         <v>98</v>
@@ -20875,7 +20875,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="589" spans="1:15" ht="15.75" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="589" spans="1:15" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A589" s="125"/>
       <c r="B589" s="133" t="s">
         <v>99</v>
@@ -20900,7 +20900,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="590" spans="1:15" ht="15.75" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="590" spans="1:15" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A590" s="125"/>
       <c r="B590" s="135"/>
       <c r="C590" s="135"/>
@@ -20927,7 +20927,7 @@
         <v>10955</v>
       </c>
     </row>
-    <row r="591" spans="1:15" ht="15.75" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="591" spans="1:15" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A591" s="125"/>
       <c r="B591" s="135"/>
       <c r="C591" s="135"/>
@@ -20944,7 +20944,7 @@
       <c r="N591" s="135"/>
       <c r="O591" s="138"/>
     </row>
-    <row r="592" spans="1:15" ht="15.75" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="592" spans="1:15" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A592" s="125"/>
       <c r="B592" s="135"/>
       <c r="C592" s="133" t="s">
@@ -20964,7 +20964,7 @@
       <c r="N592" s="135"/>
       <c r="O592" s="138"/>
     </row>
-    <row r="593" spans="1:15" ht="15.75" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="593" spans="1:15" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A593" s="125"/>
       <c r="B593" s="135"/>
       <c r="C593" s="135"/>
@@ -20990,7 +20990,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="594" spans="1:15" ht="15.75" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="594" spans="1:15" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A594" s="125"/>
       <c r="B594" s="135"/>
       <c r="C594" s="135"/>
@@ -21016,7 +21016,7 @@
         <v>328.65</v>
       </c>
     </row>
-    <row r="595" spans="1:15" ht="15.75" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="595" spans="1:15" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A595" s="125"/>
       <c r="B595" s="135"/>
       <c r="C595" s="135"/>
@@ -21042,7 +21042,7 @@
         <v>109.55</v>
       </c>
     </row>
-    <row r="596" spans="1:15" ht="15.75" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="596" spans="1:15" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A596" s="125"/>
       <c r="B596" s="135"/>
       <c r="C596" s="135"/>
@@ -21065,7 +21065,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="597" spans="1:15" ht="15.75" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="597" spans="1:15" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A597" s="125"/>
       <c r="B597" s="135"/>
       <c r="C597" s="135"/>
@@ -21088,7 +21088,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="598" spans="1:15" ht="15.75" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="598" spans="1:15" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A598" s="125"/>
       <c r="B598" s="135"/>
       <c r="C598" s="135"/>
@@ -21111,7 +21111,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="599" spans="1:15" ht="15.75" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="599" spans="1:15" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A599" s="125"/>
       <c r="B599" s="135"/>
       <c r="C599" s="135"/>
@@ -21138,7 +21138,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="600" spans="1:15" ht="15.75" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="600" spans="1:15" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A600" s="125"/>
       <c r="B600" s="135"/>
       <c r="C600" s="135"/>
@@ -21164,7 +21164,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="601" spans="1:15" ht="15.75" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="601" spans="1:15" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A601" s="125"/>
       <c r="B601" s="135"/>
       <c r="C601" s="135"/>
@@ -21191,7 +21191,7 @@
         <v>438.2</v>
       </c>
     </row>
-    <row r="602" spans="1:15" ht="15.75" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="602" spans="1:15" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A602" s="125"/>
       <c r="B602" s="135"/>
       <c r="C602" s="135"/>
@@ -21208,7 +21208,7 @@
       <c r="N602" s="135"/>
       <c r="O602" s="138"/>
     </row>
-    <row r="603" spans="1:15" ht="15.75" customHeight="1" thickBot="1" x14ac:dyDescent="0.35">
+    <row r="603" spans="1:15" ht="15.75" customHeight="1" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A603" s="125"/>
       <c r="B603" s="135"/>
       <c r="C603" s="133" t="s">
@@ -21235,7 +21235,7 @@
         <v>10516.8</v>
       </c>
     </row>
-    <row r="604" spans="1:15" ht="15.75" customHeight="1" thickTop="1" x14ac:dyDescent="0.3">
+    <row r="604" spans="1:15" ht="15.75" customHeight="1" thickTop="1" x14ac:dyDescent="0.25">
       <c r="A604" s="125"/>
       <c r="B604" s="135"/>
       <c r="C604" s="133"/>
@@ -21252,7 +21252,7 @@
       <c r="N604" s="135"/>
       <c r="O604" s="138"/>
     </row>
-    <row r="605" spans="1:15" ht="15.75" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="605" spans="1:15" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A605" s="125"/>
       <c r="B605" s="135"/>
       <c r="C605" s="135"/>
@@ -21269,7 +21269,7 @@
       <c r="N605" s="135"/>
       <c r="O605" s="138"/>
     </row>
-    <row r="606" spans="1:15" ht="15.75" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="606" spans="1:15" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A606" s="125"/>
       <c r="B606" s="135"/>
       <c r="C606" s="135"/>
@@ -21290,7 +21290,7 @@
       <c r="N606" s="135"/>
       <c r="O606" s="138"/>
     </row>
-    <row r="607" spans="1:15" ht="38.1" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="607" spans="1:15" ht="38.1" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A607" s="125"/>
       <c r="B607" s="247" t="s">
         <v>91</v>
@@ -21311,7 +21311,7 @@
       <c r="N607" s="247"/>
       <c r="O607" s="247"/>
     </row>
-    <row r="608" spans="1:15" ht="15" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="608" spans="1:15" ht="15" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A608" s="125"/>
       <c r="B608" s="126"/>
       <c r="C608" s="128"/>
@@ -21328,7 +21328,7 @@
       <c r="N608" s="128"/>
       <c r="O608" s="128"/>
     </row>
-    <row r="609" spans="1:15" ht="18.600000000000001" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="609" spans="1:15" ht="18.600000000000001" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A609" s="125"/>
       <c r="B609" s="248" t="s">
         <v>92</v>
@@ -21349,7 +21349,7 @@
       <c r="N609" s="248"/>
       <c r="O609" s="248"/>
     </row>
-    <row r="610" spans="1:15" ht="15" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="610" spans="1:15" ht="15" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A610" s="125"/>
       <c r="B610" s="131">
         <f>+B581+1</f>
@@ -21371,7 +21371,7 @@
       <c r="N610" s="132"/>
       <c r="O610" s="132"/>
     </row>
-    <row r="611" spans="1:15" ht="18.600000000000001" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="611" spans="1:15" ht="18.600000000000001" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A611" s="125"/>
       <c r="B611" s="133" t="s">
         <v>93</v>
@@ -21403,7 +21403,7 @@
       </c>
       <c r="O611" s="136"/>
     </row>
-    <row r="612" spans="1:15" ht="18.600000000000001" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="612" spans="1:15" ht="18.600000000000001" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A612" s="125"/>
       <c r="B612" s="133" t="s">
         <v>94</v>
@@ -21429,7 +21429,7 @@
       <c r="M612" s="135"/>
       <c r="O612" s="135"/>
     </row>
-    <row r="613" spans="1:15" ht="15.75" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="613" spans="1:15" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A613" s="125"/>
       <c r="B613" s="133" t="s">
         <v>95</v>
@@ -21456,7 +21456,7 @@
       <c r="N613" s="135"/>
       <c r="O613" s="135"/>
     </row>
-    <row r="614" spans="1:15" ht="15.75" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="614" spans="1:15" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A614" s="125"/>
       <c r="B614" s="133"/>
       <c r="C614" s="135"/>
@@ -21473,7 +21473,7 @@
       <c r="N614" s="135"/>
       <c r="O614" s="135"/>
     </row>
-    <row r="615" spans="1:15" ht="15.75" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="615" spans="1:15" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A615" s="125"/>
       <c r="B615" s="133" t="s">
         <v>96</v>
@@ -21500,7 +21500,7 @@
         <v>#REF!</v>
       </c>
     </row>
-    <row r="616" spans="1:15" ht="15.75" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="616" spans="1:15" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A616" s="125"/>
       <c r="B616" s="133" t="s">
         <v>97</v>
@@ -21527,7 +21527,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="617" spans="1:15" ht="15.75" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="617" spans="1:15" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A617" s="125"/>
       <c r="B617" s="133" t="s">
         <v>98</v>
@@ -21554,7 +21554,7 @@
         <v>#REF!</v>
       </c>
     </row>
-    <row r="618" spans="1:15" ht="15.75" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="618" spans="1:15" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A618" s="125"/>
       <c r="B618" s="133" t="s">
         <v>99</v>
@@ -21581,7 +21581,7 @@
         <v>#REF!</v>
       </c>
     </row>
-    <row r="619" spans="1:15" ht="15.75" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="619" spans="1:15" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A619" s="125"/>
       <c r="B619" s="135"/>
       <c r="C619" s="135"/>
@@ -21608,7 +21608,7 @@
         <v>#REF!</v>
       </c>
     </row>
-    <row r="620" spans="1:15" ht="15.75" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="620" spans="1:15" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A620" s="125"/>
       <c r="B620" s="135"/>
       <c r="C620" s="135"/>
@@ -21625,7 +21625,7 @@
       <c r="N620" s="135"/>
       <c r="O620" s="138"/>
     </row>
-    <row r="621" spans="1:15" ht="15.75" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="621" spans="1:15" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A621" s="125"/>
       <c r="B621" s="135"/>
       <c r="C621" s="133" t="s">
@@ -21645,7 +21645,7 @@
       <c r="N621" s="135"/>
       <c r="O621" s="138"/>
     </row>
-    <row r="622" spans="1:15" ht="15.75" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="622" spans="1:15" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A622" s="125"/>
       <c r="B622" s="135"/>
       <c r="C622" s="135"/>
@@ -21671,7 +21671,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="623" spans="1:15" ht="15.75" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="623" spans="1:15" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A623" s="125"/>
       <c r="B623" s="135"/>
       <c r="C623" s="135"/>
@@ -21697,7 +21697,7 @@
         <v>#REF!</v>
       </c>
     </row>
-    <row r="624" spans="1:15" ht="15.75" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="624" spans="1:15" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A624" s="125"/>
       <c r="B624" s="135"/>
       <c r="C624" s="135"/>
@@ -21723,7 +21723,7 @@
         <v>#REF!</v>
       </c>
     </row>
-    <row r="625" spans="1:15" ht="15.75" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="625" spans="1:15" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A625" s="125"/>
       <c r="B625" s="135"/>
       <c r="C625" s="135"/>
@@ -21746,7 +21746,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="626" spans="1:15" ht="15.75" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="626" spans="1:15" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A626" s="125"/>
       <c r="B626" s="135"/>
       <c r="C626" s="135"/>
@@ -21771,7 +21771,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="627" spans="1:15" ht="15.75" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="627" spans="1:15" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A627" s="125"/>
       <c r="B627" s="135"/>
       <c r="C627" s="135"/>
@@ -21794,7 +21794,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="628" spans="1:15" ht="15.75" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="628" spans="1:15" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A628" s="125"/>
       <c r="B628" s="135"/>
       <c r="C628" s="135"/>
@@ -21821,7 +21821,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="629" spans="1:15" ht="15.75" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="629" spans="1:15" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A629" s="125"/>
       <c r="B629" s="135"/>
       <c r="C629" s="135"/>
@@ -21847,7 +21847,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="630" spans="1:15" ht="15.75" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="630" spans="1:15" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A630" s="125"/>
       <c r="B630" s="135"/>
       <c r="C630" s="135"/>
@@ -21874,7 +21874,7 @@
         <v>#REF!</v>
       </c>
     </row>
-    <row r="631" spans="1:15" ht="15.75" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="631" spans="1:15" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A631" s="125"/>
       <c r="B631" s="135"/>
       <c r="C631" s="135"/>
@@ -21891,7 +21891,7 @@
       <c r="N631" s="135"/>
       <c r="O631" s="138"/>
     </row>
-    <row r="632" spans="1:15" ht="15.75" customHeight="1" thickBot="1" x14ac:dyDescent="0.35">
+    <row r="632" spans="1:15" ht="15.75" customHeight="1" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A632" s="125"/>
       <c r="B632" s="135"/>
       <c r="C632" s="133" t="s">
@@ -21918,7 +21918,7 @@
         <v>#REF!</v>
       </c>
     </row>
-    <row r="633" spans="1:15" ht="15.75" customHeight="1" thickTop="1" x14ac:dyDescent="0.3">
+    <row r="633" spans="1:15" ht="15.75" customHeight="1" thickTop="1" x14ac:dyDescent="0.25">
       <c r="A633" s="125"/>
       <c r="B633" s="135"/>
       <c r="C633" s="133"/>
@@ -21935,7 +21935,7 @@
       <c r="N633" s="135"/>
       <c r="O633" s="138"/>
     </row>
-    <row r="634" spans="1:15" ht="15.75" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="634" spans="1:15" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A634" s="125"/>
       <c r="B634" s="135"/>
       <c r="C634" s="135"/>
@@ -21952,7 +21952,7 @@
       <c r="N634" s="135"/>
       <c r="O634" s="138"/>
     </row>
-    <row r="635" spans="1:15" ht="15.75" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="635" spans="1:15" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A635" s="125"/>
       <c r="B635" s="135"/>
       <c r="C635" s="135"/>
@@ -21973,7 +21973,7 @@
       <c r="N635" s="135"/>
       <c r="O635" s="138"/>
     </row>
-    <row r="636" spans="1:15" ht="38.1" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="636" spans="1:15" ht="38.1" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A636" s="125"/>
       <c r="B636" s="247" t="s">
         <v>91</v>
@@ -21994,7 +21994,7 @@
       <c r="N636" s="247"/>
       <c r="O636" s="247"/>
     </row>
-    <row r="637" spans="1:15" ht="15" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="637" spans="1:15" ht="15" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A637" s="125"/>
       <c r="B637" s="126"/>
       <c r="C637" s="128"/>
@@ -22011,7 +22011,7 @@
       <c r="N637" s="128"/>
       <c r="O637" s="128"/>
     </row>
-    <row r="638" spans="1:15" ht="18.600000000000001" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="638" spans="1:15" ht="18.600000000000001" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A638" s="125"/>
       <c r="B638" s="248" t="s">
         <v>92</v>
@@ -22032,7 +22032,7 @@
       <c r="N638" s="248"/>
       <c r="O638" s="248"/>
     </row>
-    <row r="639" spans="1:15" ht="15" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="639" spans="1:15" ht="15" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A639" s="125"/>
       <c r="B639" s="131">
         <f>+B610+1</f>
@@ -22054,7 +22054,7 @@
       <c r="N639" s="132"/>
       <c r="O639" s="132"/>
     </row>
-    <row r="640" spans="1:15" ht="18.600000000000001" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="640" spans="1:15" ht="18.600000000000001" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A640" s="125"/>
       <c r="B640" s="133" t="s">
         <v>93</v>
@@ -22086,7 +22086,7 @@
       </c>
       <c r="O640" s="136"/>
     </row>
-    <row r="641" spans="1:15" ht="18.600000000000001" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="641" spans="1:15" ht="18.600000000000001" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A641" s="125"/>
       <c r="B641" s="133" t="s">
         <v>94</v>
@@ -22112,7 +22112,7 @@
       <c r="M641" s="135"/>
       <c r="O641" s="135"/>
     </row>
-    <row r="642" spans="1:15" ht="15.75" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="642" spans="1:15" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A642" s="125"/>
       <c r="B642" s="133" t="s">
         <v>95</v>
@@ -22139,7 +22139,7 @@
       <c r="N642" s="135"/>
       <c r="O642" s="135"/>
     </row>
-    <row r="643" spans="1:15" ht="15.75" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="643" spans="1:15" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A643" s="125"/>
       <c r="B643" s="133"/>
       <c r="C643" s="135"/>
@@ -22156,7 +22156,7 @@
       <c r="N643" s="135"/>
       <c r="O643" s="135"/>
     </row>
-    <row r="644" spans="1:15" ht="15.75" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="644" spans="1:15" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A644" s="125"/>
       <c r="B644" s="133" t="s">
         <v>96</v>
@@ -22183,7 +22183,7 @@
         <v>#REF!</v>
       </c>
     </row>
-    <row r="645" spans="1:15" ht="15.75" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="645" spans="1:15" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A645" s="125"/>
       <c r="B645" s="133" t="s">
         <v>97</v>
@@ -22210,7 +22210,7 @@
         <v>#REF!</v>
       </c>
     </row>
-    <row r="646" spans="1:15" ht="15.75" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="646" spans="1:15" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A646" s="125"/>
       <c r="B646" s="133" t="s">
         <v>98</v>
@@ -22237,7 +22237,7 @@
         <v>#REF!</v>
       </c>
     </row>
-    <row r="647" spans="1:15" ht="15.75" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="647" spans="1:15" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A647" s="125"/>
       <c r="B647" s="133" t="s">
         <v>99</v>
@@ -22264,7 +22264,7 @@
         <v>#REF!</v>
       </c>
     </row>
-    <row r="648" spans="1:15" ht="15.75" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="648" spans="1:15" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A648" s="125"/>
       <c r="B648" s="135"/>
       <c r="C648" s="135"/>
@@ -22291,7 +22291,7 @@
         <v>#REF!</v>
       </c>
     </row>
-    <row r="649" spans="1:15" ht="15.75" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="649" spans="1:15" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A649" s="125"/>
       <c r="B649" s="135"/>
       <c r="C649" s="135"/>
@@ -22308,7 +22308,7 @@
       <c r="N649" s="135"/>
       <c r="O649" s="138"/>
     </row>
-    <row r="650" spans="1:15" ht="15.75" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="650" spans="1:15" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A650" s="125"/>
       <c r="B650" s="135"/>
       <c r="C650" s="133" t="s">
@@ -22328,7 +22328,7 @@
       <c r="N650" s="135"/>
       <c r="O650" s="138"/>
     </row>
-    <row r="651" spans="1:15" ht="15.75" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="651" spans="1:15" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A651" s="125"/>
       <c r="B651" s="135"/>
       <c r="C651" s="135"/>
@@ -22354,7 +22354,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="652" spans="1:15" ht="15.75" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="652" spans="1:15" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A652" s="125"/>
       <c r="B652" s="135"/>
       <c r="C652" s="135"/>
@@ -22380,7 +22380,7 @@
         <v>#REF!</v>
       </c>
     </row>
-    <row r="653" spans="1:15" ht="15.75" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="653" spans="1:15" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A653" s="125"/>
       <c r="B653" s="135"/>
       <c r="C653" s="135"/>
@@ -22406,7 +22406,7 @@
         <v>#REF!</v>
       </c>
     </row>
-    <row r="654" spans="1:15" ht="15.75" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="654" spans="1:15" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A654" s="125"/>
       <c r="B654" s="135"/>
       <c r="C654" s="135"/>
@@ -22429,7 +22429,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="655" spans="1:15" ht="15.75" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="655" spans="1:15" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A655" s="125"/>
       <c r="B655" s="135"/>
       <c r="C655" s="135"/>
@@ -22452,7 +22452,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="656" spans="1:15" ht="15.75" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="656" spans="1:15" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A656" s="125"/>
       <c r="B656" s="135"/>
       <c r="C656" s="135"/>
@@ -22475,7 +22475,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="657" spans="1:15" ht="15.75" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="657" spans="1:15" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A657" s="125"/>
       <c r="B657" s="135"/>
       <c r="C657" s="135"/>
@@ -22502,7 +22502,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="658" spans="1:15" ht="15.75" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="658" spans="1:15" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A658" s="125"/>
       <c r="B658" s="135"/>
       <c r="C658" s="135"/>
@@ -22528,7 +22528,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="659" spans="1:15" ht="15.75" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="659" spans="1:15" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A659" s="125"/>
       <c r="B659" s="135"/>
       <c r="C659" s="135"/>
@@ -22555,7 +22555,7 @@
         <v>#REF!</v>
       </c>
     </row>
-    <row r="660" spans="1:15" ht="15.75" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="660" spans="1:15" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A660" s="125"/>
       <c r="B660" s="135"/>
       <c r="C660" s="135"/>
@@ -22572,7 +22572,7 @@
       <c r="N660" s="135"/>
       <c r="O660" s="138"/>
     </row>
-    <row r="661" spans="1:15" ht="15.75" customHeight="1" thickBot="1" x14ac:dyDescent="0.35">
+    <row r="661" spans="1:15" ht="15.75" customHeight="1" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A661" s="125"/>
       <c r="B661" s="135"/>
       <c r="C661" s="133" t="s">
@@ -22599,7 +22599,7 @@
         <v>#REF!</v>
       </c>
     </row>
-    <row r="662" spans="1:15" ht="15.75" customHeight="1" thickTop="1" x14ac:dyDescent="0.3">
+    <row r="662" spans="1:15" ht="15.75" customHeight="1" thickTop="1" x14ac:dyDescent="0.25">
       <c r="A662" s="125"/>
       <c r="B662" s="135"/>
       <c r="C662" s="133"/>
@@ -22616,7 +22616,7 @@
       <c r="N662" s="135"/>
       <c r="O662" s="138"/>
     </row>
-    <row r="663" spans="1:15" ht="15.75" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="663" spans="1:15" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A663" s="125"/>
       <c r="B663" s="135"/>
       <c r="C663" s="135"/>
@@ -22633,7 +22633,7 @@
       <c r="N663" s="135"/>
       <c r="O663" s="138"/>
     </row>
-    <row r="664" spans="1:15" ht="15.75" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="664" spans="1:15" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A664" s="125"/>
       <c r="B664" s="135"/>
       <c r="C664" s="135"/>
@@ -22654,7 +22654,7 @@
       <c r="N664" s="135"/>
       <c r="O664" s="138"/>
     </row>
-    <row r="665" spans="1:15" ht="38.1" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="665" spans="1:15" ht="38.1" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A665" s="125"/>
       <c r="B665" s="247" t="s">
         <v>91</v>
@@ -22675,7 +22675,7 @@
       <c r="N665" s="247"/>
       <c r="O665" s="247"/>
     </row>
-    <row r="666" spans="1:15" ht="15" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="666" spans="1:15" ht="15" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A666" s="125"/>
       <c r="B666" s="126"/>
       <c r="C666" s="128"/>
@@ -22692,7 +22692,7 @@
       <c r="N666" s="128"/>
       <c r="O666" s="128"/>
     </row>
-    <row r="667" spans="1:15" ht="18.600000000000001" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="667" spans="1:15" ht="18.600000000000001" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A667" s="125"/>
       <c r="B667" s="248" t="s">
         <v>92</v>
@@ -22713,7 +22713,7 @@
       <c r="N667" s="248"/>
       <c r="O667" s="248"/>
     </row>
-    <row r="668" spans="1:15" ht="15" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="668" spans="1:15" ht="15" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A668" s="125"/>
       <c r="B668" s="131">
         <f>+B639+1</f>
@@ -22735,7 +22735,7 @@
       <c r="N668" s="132"/>
       <c r="O668" s="132"/>
     </row>
-    <row r="669" spans="1:15" ht="18.600000000000001" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="669" spans="1:15" ht="18.600000000000001" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A669" s="125"/>
       <c r="B669" s="133" t="s">
         <v>93</v>
@@ -22767,7 +22767,7 @@
       </c>
       <c r="O669" s="136"/>
     </row>
-    <row r="670" spans="1:15" ht="18.600000000000001" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="670" spans="1:15" ht="18.600000000000001" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A670" s="125"/>
       <c r="B670" s="133" t="s">
         <v>94</v>
@@ -22793,7 +22793,7 @@
       <c r="M670" s="135"/>
       <c r="O670" s="135"/>
     </row>
-    <row r="671" spans="1:15" ht="15.75" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="671" spans="1:15" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A671" s="125"/>
       <c r="B671" s="133" t="s">
         <v>95</v>
@@ -22820,7 +22820,7 @@
       <c r="N671" s="135"/>
       <c r="O671" s="135"/>
     </row>
-    <row r="672" spans="1:15" ht="15.75" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="672" spans="1:15" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A672" s="125"/>
       <c r="B672" s="133"/>
       <c r="C672" s="135"/>
@@ -22837,7 +22837,7 @@
       <c r="N672" s="135"/>
       <c r="O672" s="135"/>
     </row>
-    <row r="673" spans="1:15" ht="15.75" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="673" spans="1:15" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A673" s="125"/>
       <c r="B673" s="133" t="s">
         <v>96</v>
@@ -22864,7 +22864,7 @@
         <v>#REF!</v>
       </c>
     </row>
-    <row r="674" spans="1:15" ht="15.75" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="674" spans="1:15" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A674" s="125"/>
       <c r="B674" s="133" t="s">
         <v>97</v>
@@ -22891,7 +22891,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="675" spans="1:15" ht="15.75" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="675" spans="1:15" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A675" s="125"/>
       <c r="B675" s="133" t="s">
         <v>98</v>
@@ -22918,7 +22918,7 @@
         <v>#REF!</v>
       </c>
     </row>
-    <row r="676" spans="1:15" ht="15.75" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="676" spans="1:15" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A676" s="125"/>
       <c r="B676" s="133" t="s">
         <v>99</v>
@@ -22945,7 +22945,7 @@
         <v>#REF!</v>
       </c>
     </row>
-    <row r="677" spans="1:15" ht="15.75" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="677" spans="1:15" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A677" s="125"/>
       <c r="B677" s="135"/>
       <c r="C677" s="135"/>
@@ -22972,7 +22972,7 @@
         <v>#REF!</v>
       </c>
     </row>
-    <row r="678" spans="1:15" ht="15.75" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="678" spans="1:15" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A678" s="125"/>
       <c r="B678" s="135"/>
       <c r="C678" s="135"/>
@@ -22989,7 +22989,7 @@
       <c r="N678" s="135"/>
       <c r="O678" s="138"/>
     </row>
-    <row r="679" spans="1:15" ht="15.75" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="679" spans="1:15" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A679" s="125"/>
       <c r="B679" s="135"/>
       <c r="C679" s="133" t="s">
@@ -23009,7 +23009,7 @@
       <c r="N679" s="135"/>
       <c r="O679" s="138"/>
     </row>
-    <row r="680" spans="1:15" ht="15.75" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="680" spans="1:15" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A680" s="125"/>
       <c r="B680" s="135"/>
       <c r="C680" s="135"/>
@@ -23035,7 +23035,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="681" spans="1:15" ht="15.75" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="681" spans="1:15" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A681" s="125"/>
       <c r="B681" s="135"/>
       <c r="C681" s="135"/>
@@ -23061,7 +23061,7 @@
         <v>#REF!</v>
       </c>
     </row>
-    <row r="682" spans="1:15" ht="15.75" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="682" spans="1:15" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A682" s="125"/>
       <c r="B682" s="135"/>
       <c r="C682" s="135"/>
@@ -23087,7 +23087,7 @@
         <v>#REF!</v>
       </c>
     </row>
-    <row r="683" spans="1:15" ht="15.75" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="683" spans="1:15" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A683" s="125"/>
       <c r="B683" s="135"/>
       <c r="C683" s="135"/>
@@ -23110,7 +23110,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="684" spans="1:15" ht="15.75" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="684" spans="1:15" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A684" s="125"/>
       <c r="B684" s="135"/>
       <c r="C684" s="135"/>
@@ -23133,7 +23133,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="685" spans="1:15" ht="15.75" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="685" spans="1:15" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A685" s="125"/>
       <c r="B685" s="135"/>
       <c r="C685" s="135"/>
@@ -23156,7 +23156,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="686" spans="1:15" ht="15.75" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="686" spans="1:15" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A686" s="125"/>
       <c r="B686" s="135"/>
       <c r="C686" s="135"/>
@@ -23183,7 +23183,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="687" spans="1:15" ht="15.75" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="687" spans="1:15" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A687" s="125"/>
       <c r="B687" s="135"/>
       <c r="C687" s="135"/>
@@ -23209,7 +23209,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="688" spans="1:15" ht="15.75" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="688" spans="1:15" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A688" s="125"/>
       <c r="B688" s="135"/>
       <c r="C688" s="135"/>
@@ -23236,7 +23236,7 @@
         <v>#REF!</v>
       </c>
     </row>
-    <row r="689" spans="1:15" ht="15.75" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="689" spans="1:15" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A689" s="125"/>
       <c r="B689" s="135"/>
       <c r="C689" s="135"/>
@@ -23253,7 +23253,7 @@
       <c r="N689" s="135"/>
       <c r="O689" s="138"/>
     </row>
-    <row r="690" spans="1:15" ht="15.75" customHeight="1" thickBot="1" x14ac:dyDescent="0.35">
+    <row r="690" spans="1:15" ht="15.75" customHeight="1" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A690" s="125"/>
       <c r="B690" s="135"/>
       <c r="C690" s="133" t="s">
@@ -23280,7 +23280,7 @@
         <v>#REF!</v>
       </c>
     </row>
-    <row r="691" spans="1:15" ht="15.75" customHeight="1" thickTop="1" x14ac:dyDescent="0.3">
+    <row r="691" spans="1:15" ht="15.75" customHeight="1" thickTop="1" x14ac:dyDescent="0.25">
       <c r="A691" s="125"/>
       <c r="B691" s="135"/>
       <c r="C691" s="133"/>
@@ -23297,7 +23297,7 @@
       <c r="N691" s="135"/>
       <c r="O691" s="138"/>
     </row>
-    <row r="692" spans="1:15" ht="15.75" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="692" spans="1:15" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A692" s="125"/>
       <c r="B692" s="135"/>
       <c r="C692" s="135"/>
@@ -23314,7 +23314,7 @@
       <c r="N692" s="135"/>
       <c r="O692" s="138"/>
     </row>
-    <row r="693" spans="1:15" ht="15.75" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="693" spans="1:15" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A693" s="125"/>
       <c r="B693" s="135"/>
       <c r="C693" s="135"/>
@@ -23335,7 +23335,7 @@
       <c r="N693" s="135"/>
       <c r="O693" s="138"/>
     </row>
-    <row r="694" spans="1:15" ht="38.1" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="694" spans="1:15" ht="38.1" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A694" s="125"/>
       <c r="B694" s="247" t="s">
         <v>91</v>
@@ -23356,7 +23356,7 @@
       <c r="N694" s="247"/>
       <c r="O694" s="247"/>
     </row>
-    <row r="695" spans="1:15" ht="15" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="695" spans="1:15" ht="15" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A695" s="125"/>
       <c r="B695" s="126"/>
       <c r="C695" s="128"/>
@@ -23373,7 +23373,7 @@
       <c r="N695" s="128"/>
       <c r="O695" s="128"/>
     </row>
-    <row r="696" spans="1:15" ht="18.600000000000001" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="696" spans="1:15" ht="18.600000000000001" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A696" s="125"/>
       <c r="B696" s="248" t="s">
         <v>92</v>
@@ -23394,7 +23394,7 @@
       <c r="N696" s="248"/>
       <c r="O696" s="248"/>
     </row>
-    <row r="697" spans="1:15" ht="15" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="697" spans="1:15" ht="15" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A697" s="125"/>
       <c r="B697" s="131">
         <f>+B668+1</f>
@@ -23416,7 +23416,7 @@
       <c r="N697" s="132"/>
       <c r="O697" s="132"/>
     </row>
-    <row r="698" spans="1:15" ht="18.600000000000001" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="698" spans="1:15" ht="18.600000000000001" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A698" s="125"/>
       <c r="B698" s="133" t="s">
         <v>93</v>
@@ -23448,7 +23448,7 @@
       </c>
       <c r="O698" s="136"/>
     </row>
-    <row r="699" spans="1:15" ht="18.600000000000001" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="699" spans="1:15" ht="18.600000000000001" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A699" s="125"/>
       <c r="B699" s="133" t="s">
         <v>94</v>
@@ -23474,7 +23474,7 @@
       <c r="M699" s="135"/>
       <c r="O699" s="135"/>
     </row>
-    <row r="700" spans="1:15" ht="15.75" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="700" spans="1:15" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A700" s="125"/>
       <c r="B700" s="133" t="s">
         <v>95</v>
@@ -23501,7 +23501,7 @@
       <c r="N700" s="135"/>
       <c r="O700" s="135"/>
     </row>
-    <row r="701" spans="1:15" ht="15.75" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="701" spans="1:15" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A701" s="125"/>
       <c r="B701" s="133"/>
       <c r="C701" s="135"/>
@@ -23518,7 +23518,7 @@
       <c r="N701" s="135"/>
       <c r="O701" s="135"/>
     </row>
-    <row r="702" spans="1:15" ht="15.75" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="702" spans="1:15" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A702" s="125"/>
       <c r="B702" s="133" t="s">
         <v>96</v>
@@ -23545,7 +23545,7 @@
         <v>#REF!</v>
       </c>
     </row>
-    <row r="703" spans="1:15" ht="15.75" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="703" spans="1:15" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A703" s="125"/>
       <c r="B703" s="133" t="s">
         <v>97</v>
@@ -23572,7 +23572,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="704" spans="1:15" ht="15.75" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="704" spans="1:15" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A704" s="125"/>
       <c r="B704" s="133" t="s">
         <v>98</v>
@@ -23599,7 +23599,7 @@
         <v>#REF!</v>
       </c>
     </row>
-    <row r="705" spans="1:15" ht="15.75" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="705" spans="1:15" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A705" s="125"/>
       <c r="B705" s="133" t="s">
         <v>99</v>
@@ -23626,7 +23626,7 @@
         <v>#REF!</v>
       </c>
     </row>
-    <row r="706" spans="1:15" ht="15.75" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="706" spans="1:15" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A706" s="125"/>
       <c r="B706" s="135"/>
       <c r="C706" s="135"/>
@@ -23653,7 +23653,7 @@
         <v>#REF!</v>
       </c>
     </row>
-    <row r="707" spans="1:15" ht="15.75" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="707" spans="1:15" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A707" s="125"/>
       <c r="B707" s="135"/>
       <c r="C707" s="135"/>
@@ -23670,7 +23670,7 @@
       <c r="N707" s="135"/>
       <c r="O707" s="138"/>
     </row>
-    <row r="708" spans="1:15" ht="15.75" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="708" spans="1:15" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A708" s="125"/>
       <c r="B708" s="135"/>
       <c r="C708" s="133" t="s">
@@ -23690,7 +23690,7 @@
       <c r="N708" s="135"/>
       <c r="O708" s="138"/>
     </row>
-    <row r="709" spans="1:15" ht="15.75" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="709" spans="1:15" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A709" s="125"/>
       <c r="B709" s="135"/>
       <c r="C709" s="135"/>
@@ -23716,7 +23716,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="710" spans="1:15" ht="15.75" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="710" spans="1:15" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A710" s="125"/>
       <c r="B710" s="135"/>
       <c r="C710" s="135"/>
@@ -23742,7 +23742,7 @@
         <v>#REF!</v>
       </c>
     </row>
-    <row r="711" spans="1:15" ht="15.75" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="711" spans="1:15" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A711" s="125"/>
       <c r="B711" s="135"/>
       <c r="C711" s="135"/>
@@ -23768,7 +23768,7 @@
         <v>#REF!</v>
       </c>
     </row>
-    <row r="712" spans="1:15" ht="15.75" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="712" spans="1:15" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A712" s="125"/>
       <c r="B712" s="135"/>
       <c r="C712" s="135"/>
@@ -23791,7 +23791,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="713" spans="1:15" ht="15.75" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="713" spans="1:15" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A713" s="125"/>
       <c r="B713" s="135"/>
       <c r="C713" s="135"/>
@@ -23814,7 +23814,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="714" spans="1:15" ht="15.75" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="714" spans="1:15" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A714" s="125"/>
       <c r="B714" s="135"/>
       <c r="C714" s="135"/>
@@ -23837,7 +23837,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="715" spans="1:15" ht="15.75" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="715" spans="1:15" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A715" s="125"/>
       <c r="B715" s="135"/>
       <c r="C715" s="135"/>
@@ -23864,7 +23864,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="716" spans="1:15" ht="15.75" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="716" spans="1:15" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A716" s="125"/>
       <c r="B716" s="135"/>
       <c r="C716" s="135"/>
@@ -23890,7 +23890,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="717" spans="1:15" ht="15.75" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="717" spans="1:15" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A717" s="125"/>
       <c r="B717" s="135"/>
       <c r="C717" s="135"/>
@@ -23917,7 +23917,7 @@
         <v>#REF!</v>
       </c>
     </row>
-    <row r="718" spans="1:15" ht="15.75" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="718" spans="1:15" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A718" s="125"/>
       <c r="B718" s="135"/>
       <c r="C718" s="135"/>
@@ -23934,7 +23934,7 @@
       <c r="N718" s="135"/>
       <c r="O718" s="138"/>
     </row>
-    <row r="719" spans="1:15" ht="15.75" customHeight="1" thickBot="1" x14ac:dyDescent="0.35">
+    <row r="719" spans="1:15" ht="15.75" customHeight="1" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A719" s="125"/>
       <c r="B719" s="135"/>
       <c r="C719" s="133" t="s">
@@ -23961,7 +23961,7 @@
         <v>#REF!</v>
       </c>
     </row>
-    <row r="720" spans="1:15" ht="15.75" customHeight="1" thickTop="1" x14ac:dyDescent="0.3">
+    <row r="720" spans="1:15" ht="15.75" customHeight="1" thickTop="1" x14ac:dyDescent="0.25">
       <c r="A720" s="125"/>
       <c r="B720" s="135"/>
       <c r="C720" s="133"/>
@@ -23978,7 +23978,7 @@
       <c r="N720" s="135"/>
       <c r="O720" s="138"/>
     </row>
-    <row r="721" spans="1:15" ht="15.75" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="721" spans="1:15" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A721" s="125"/>
       <c r="B721" s="135"/>
       <c r="C721" s="135"/>
@@ -23995,7 +23995,7 @@
       <c r="N721" s="135"/>
       <c r="O721" s="138"/>
     </row>
-    <row r="722" spans="1:15" ht="15.75" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="722" spans="1:15" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A722" s="125"/>
       <c r="B722" s="135"/>
       <c r="C722" s="135"/>
@@ -24018,6 +24018,90 @@
     </row>
   </sheetData>
   <mergeCells count="100">
+    <mergeCell ref="B694:G694"/>
+    <mergeCell ref="J694:O694"/>
+    <mergeCell ref="B696:G696"/>
+    <mergeCell ref="J696:O696"/>
+    <mergeCell ref="B638:G638"/>
+    <mergeCell ref="J638:O638"/>
+    <mergeCell ref="B665:G665"/>
+    <mergeCell ref="J665:O665"/>
+    <mergeCell ref="B667:G667"/>
+    <mergeCell ref="J667:O667"/>
+    <mergeCell ref="B607:G607"/>
+    <mergeCell ref="J607:O607"/>
+    <mergeCell ref="B609:G609"/>
+    <mergeCell ref="J609:O609"/>
+    <mergeCell ref="B636:G636"/>
+    <mergeCell ref="J636:O636"/>
+    <mergeCell ref="B522:G522"/>
+    <mergeCell ref="J522:O522"/>
+    <mergeCell ref="B549:G549"/>
+    <mergeCell ref="J549:O549"/>
+    <mergeCell ref="B551:G551"/>
+    <mergeCell ref="J551:O551"/>
+    <mergeCell ref="B520:G520"/>
+    <mergeCell ref="J520:O520"/>
+    <mergeCell ref="B493:G493"/>
+    <mergeCell ref="J493:O493"/>
+    <mergeCell ref="B462:G462"/>
+    <mergeCell ref="J462:O462"/>
+    <mergeCell ref="B464:G464"/>
+    <mergeCell ref="J464:O464"/>
+    <mergeCell ref="B491:G491"/>
+    <mergeCell ref="J491:O491"/>
+    <mergeCell ref="B434:G434"/>
+    <mergeCell ref="J434:O434"/>
+    <mergeCell ref="B436:G436"/>
+    <mergeCell ref="J436:O436"/>
+    <mergeCell ref="B376:G376"/>
+    <mergeCell ref="J376:O376"/>
+    <mergeCell ref="B378:G378"/>
+    <mergeCell ref="J378:O378"/>
+    <mergeCell ref="B405:G405"/>
+    <mergeCell ref="J405:O405"/>
+    <mergeCell ref="B407:G407"/>
+    <mergeCell ref="J407:O407"/>
+    <mergeCell ref="B320:G320"/>
+    <mergeCell ref="J320:O320"/>
+    <mergeCell ref="B347:G347"/>
+    <mergeCell ref="J347:O347"/>
+    <mergeCell ref="B349:G349"/>
+    <mergeCell ref="J349:O349"/>
+    <mergeCell ref="B289:G289"/>
+    <mergeCell ref="J289:O289"/>
+    <mergeCell ref="B291:G291"/>
+    <mergeCell ref="J291:O291"/>
+    <mergeCell ref="B318:G318"/>
+    <mergeCell ref="J318:O318"/>
+    <mergeCell ref="B233:G233"/>
+    <mergeCell ref="J233:O233"/>
+    <mergeCell ref="B260:G260"/>
+    <mergeCell ref="J260:O260"/>
+    <mergeCell ref="B262:G262"/>
+    <mergeCell ref="J262:O262"/>
+    <mergeCell ref="B173:G173"/>
+    <mergeCell ref="J173:O173"/>
+    <mergeCell ref="B175:G175"/>
+    <mergeCell ref="J175:O175"/>
+    <mergeCell ref="B231:G231"/>
+    <mergeCell ref="J231:O231"/>
+    <mergeCell ref="B202:G202"/>
+    <mergeCell ref="J202:O202"/>
+    <mergeCell ref="B204:G204"/>
+    <mergeCell ref="J204:O204"/>
+    <mergeCell ref="B118:G118"/>
+    <mergeCell ref="J118:O118"/>
+    <mergeCell ref="B145:G145"/>
+    <mergeCell ref="J145:O145"/>
+    <mergeCell ref="B147:G147"/>
+    <mergeCell ref="J147:O147"/>
+    <mergeCell ref="B88:G88"/>
+    <mergeCell ref="J88:O88"/>
+    <mergeCell ref="B90:G90"/>
+    <mergeCell ref="J90:O90"/>
+    <mergeCell ref="B116:G116"/>
+    <mergeCell ref="J116:O116"/>
     <mergeCell ref="B578:G578"/>
     <mergeCell ref="J578:O578"/>
     <mergeCell ref="B580:G580"/>
@@ -24034,90 +24118,6 @@
     <mergeCell ref="J59:O59"/>
     <mergeCell ref="B61:G61"/>
     <mergeCell ref="J61:O61"/>
-    <mergeCell ref="B88:G88"/>
-    <mergeCell ref="J88:O88"/>
-    <mergeCell ref="B90:G90"/>
-    <mergeCell ref="J90:O90"/>
-    <mergeCell ref="B116:G116"/>
-    <mergeCell ref="J116:O116"/>
-    <mergeCell ref="B118:G118"/>
-    <mergeCell ref="J118:O118"/>
-    <mergeCell ref="B145:G145"/>
-    <mergeCell ref="J145:O145"/>
-    <mergeCell ref="B147:G147"/>
-    <mergeCell ref="J147:O147"/>
-    <mergeCell ref="B173:G173"/>
-    <mergeCell ref="J173:O173"/>
-    <mergeCell ref="B175:G175"/>
-    <mergeCell ref="J175:O175"/>
-    <mergeCell ref="B231:G231"/>
-    <mergeCell ref="J231:O231"/>
-    <mergeCell ref="B202:G202"/>
-    <mergeCell ref="J202:O202"/>
-    <mergeCell ref="B204:G204"/>
-    <mergeCell ref="J204:O204"/>
-    <mergeCell ref="B233:G233"/>
-    <mergeCell ref="J233:O233"/>
-    <mergeCell ref="B260:G260"/>
-    <mergeCell ref="J260:O260"/>
-    <mergeCell ref="B262:G262"/>
-    <mergeCell ref="J262:O262"/>
-    <mergeCell ref="B289:G289"/>
-    <mergeCell ref="J289:O289"/>
-    <mergeCell ref="B291:G291"/>
-    <mergeCell ref="J291:O291"/>
-    <mergeCell ref="B318:G318"/>
-    <mergeCell ref="J318:O318"/>
-    <mergeCell ref="B320:G320"/>
-    <mergeCell ref="J320:O320"/>
-    <mergeCell ref="B347:G347"/>
-    <mergeCell ref="J347:O347"/>
-    <mergeCell ref="B349:G349"/>
-    <mergeCell ref="J349:O349"/>
-    <mergeCell ref="B434:G434"/>
-    <mergeCell ref="J434:O434"/>
-    <mergeCell ref="B436:G436"/>
-    <mergeCell ref="J436:O436"/>
-    <mergeCell ref="B376:G376"/>
-    <mergeCell ref="J376:O376"/>
-    <mergeCell ref="B378:G378"/>
-    <mergeCell ref="J378:O378"/>
-    <mergeCell ref="B405:G405"/>
-    <mergeCell ref="J405:O405"/>
-    <mergeCell ref="B407:G407"/>
-    <mergeCell ref="J407:O407"/>
-    <mergeCell ref="B520:G520"/>
-    <mergeCell ref="J520:O520"/>
-    <mergeCell ref="B493:G493"/>
-    <mergeCell ref="J493:O493"/>
-    <mergeCell ref="B462:G462"/>
-    <mergeCell ref="J462:O462"/>
-    <mergeCell ref="B464:G464"/>
-    <mergeCell ref="J464:O464"/>
-    <mergeCell ref="B491:G491"/>
-    <mergeCell ref="J491:O491"/>
-    <mergeCell ref="B522:G522"/>
-    <mergeCell ref="J522:O522"/>
-    <mergeCell ref="B549:G549"/>
-    <mergeCell ref="J549:O549"/>
-    <mergeCell ref="B551:G551"/>
-    <mergeCell ref="J551:O551"/>
-    <mergeCell ref="B607:G607"/>
-    <mergeCell ref="J607:O607"/>
-    <mergeCell ref="B609:G609"/>
-    <mergeCell ref="J609:O609"/>
-    <mergeCell ref="B636:G636"/>
-    <mergeCell ref="J636:O636"/>
-    <mergeCell ref="B694:G694"/>
-    <mergeCell ref="J694:O694"/>
-    <mergeCell ref="B696:G696"/>
-    <mergeCell ref="J696:O696"/>
-    <mergeCell ref="B638:G638"/>
-    <mergeCell ref="J638:O638"/>
-    <mergeCell ref="B665:G665"/>
-    <mergeCell ref="J665:O665"/>
-    <mergeCell ref="B667:G667"/>
-    <mergeCell ref="J667:O667"/>
   </mergeCells>
   <pageMargins left="0.25" right="0.25" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <pageSetup paperSize="9" orientation="landscape" horizontalDpi="300" verticalDpi="300" r:id="rId1"/>
